--- a/model/ABNB_official_model.xlsx
+++ b/model/ABNB_official_model.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Nights_Engine" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Income_Statement" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sources" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ADR_Engine" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income_Statement" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sources" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,10 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -114,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -144,6 +147,8 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -734,6 +739,244 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ADR $: printed, then the engine path, vs the Street</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>ADR $ (printed, then engine)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ADR_Engine'!$O$4:$AD$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ADR_Engine'!$O$129:$AD$129</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Street ADR $</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ADR_Engine'!$O$4:$AD$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ADR_Engine'!$O$130:$AD$130</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>FX effect on ADR (pp): translation identity vs disclosed</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>FX identity (pp)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ADR_Engine'!$O$4:$AD$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ADR_Engine'!$O$131:$AD$131</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>disclosed FX (pp)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ADR_Engine'!$O$4:$AD$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ADR_Engine'!$O$132:$AD$132</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -819,6 +1062,55 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>133</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>133</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1116,7 +1408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1126,7 +1418,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Airbnb (ABNB) — official model, built line by line. Line 1: nights.</t>
+          <t>Airbnb (ABNB) — official model, built line by line. Line 1: nights. Line 2: ADR.</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1187,7 +1479,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nights: built (DEC-0029 base 146.8m; engine stays read in Nights_Engine block D). All other income-statement lines: to build together, one at a time, each with its rationale file (DEC-0021 / DEC-0026).</t>
+          <t>Nights: built (DEC-0029 base 146.8m). ADR: built (ADR_Engine; pre-registered FX identity promoted, ex-FX mechanism with the bundle lapping on filed dates; proposed DEC-0034/0035 pending Theo). GBV = nights × ADR on Income_Statement row 8. Next: take rate / revenue, together, one at a time.</t>
         </is>
       </c>
     </row>
@@ -1199,10 +1491,14 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Formulas were recalculated in Excel and checked against the engine's Python outputs (block 'Engine reference values'): W1/W2 ratios, band, a, b, 3Q26 read.</t>
-        </is>
-      </c>
-    </row>
+          <t>Nights: formulas recalculated in Excel and checked against the engine (block 'Engine reference values'). ADR: formulas written by adr_engine/workbook.py; open in Excel to recalculate, then tie out block E (walk-forward ratios, FX pp, ADR $).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5069,6 +5365,6753 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AD132"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="9.5" customWidth="1" min="3" max="3"/>
+    <col width="9.5" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="9.5" customWidth="1" min="7" max="7"/>
+    <col width="9.5" customWidth="1" min="8" max="8"/>
+    <col width="9.5" customWidth="1" min="9" max="9"/>
+    <col width="9.5" customWidth="1" min="10" max="10"/>
+    <col width="9.5" customWidth="1" min="11" max="11"/>
+    <col width="9.5" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
+    <col width="9.5" customWidth="1" min="14" max="14"/>
+    <col width="9.5" customWidth="1" min="15" max="15"/>
+    <col width="9.5" customWidth="1" min="16" max="16"/>
+    <col width="9.5" customWidth="1" min="17" max="17"/>
+    <col width="9.5" customWidth="1" min="18" max="18"/>
+    <col width="9.5" customWidth="1" min="19" max="19"/>
+    <col width="9.5" customWidth="1" min="20" max="20"/>
+    <col width="9.5" customWidth="1" min="21" max="21"/>
+    <col width="9.5" customWidth="1" min="22" max="22"/>
+    <col width="9.5" customWidth="1" min="23" max="23"/>
+    <col width="9.5" customWidth="1" min="24" max="24"/>
+    <col width="9.5" customWidth="1" min="25" max="25"/>
+    <col width="9.5" customWidth="1" min="26" max="26"/>
+    <col width="9.5" customWidth="1" min="27" max="27"/>
+    <col width="9.5" customWidth="1" min="28" max="28"/>
+    <col width="9.5" customWidth="1" min="29" max="29"/>
+    <col width="9.5" customWidth="1" min="30" max="30"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Airbnb — ADR engine (line 2). reported ADR y/y = ex-FX mechanism + FX translation identity (ex ante, spot held). Blue = input with source; black = formula; green = link.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="Y1" s="1" t="n"/>
+      <c r="Z1" s="1" t="n"/>
+      <c r="AA1" s="1" t="n"/>
+      <c r="AB1" s="1" t="n"/>
+      <c r="AC1" s="1" t="n"/>
+      <c r="AD1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Engine: analysis/src/pitch_model_v2/adr_engine (python3 -m pitch_model_v2.adr_engine.run); pre-registration docs/pitch-model-v2/lines/adr_fx_prereg.md; design adr_v1_design.md; rationale final_adr.md. FX through FRED 2026-09-18; forward quarters hold the last print (spot held).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>A = printed, E = engine</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>1Q21A</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>2Q21A</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>3Q21A</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>4Q21A</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>1Q22A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>2Q22A</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>3Q22A</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>4Q22A</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>1Q23A</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>2Q23A</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>3Q23A</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>4Q23A</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>1Q24A</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>2Q24A</t>
+        </is>
+      </c>
+      <c r="Q4" s="7" t="inlineStr">
+        <is>
+          <t>3Q24A</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
+        <is>
+          <t>4Q24A</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>1Q25A</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
+        <is>
+          <t>2Q25A</t>
+        </is>
+      </c>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>3Q25A</t>
+        </is>
+      </c>
+      <c r="V4" s="7" t="inlineStr">
+        <is>
+          <t>4Q25A</t>
+        </is>
+      </c>
+      <c r="W4" s="7" t="inlineStr">
+        <is>
+          <t>1Q26A</t>
+        </is>
+      </c>
+      <c r="X4" s="7" t="inlineStr">
+        <is>
+          <t>2Q26A</t>
+        </is>
+      </c>
+      <c r="Y4" s="7" t="inlineStr">
+        <is>
+          <t>3Q26E</t>
+        </is>
+      </c>
+      <c r="Z4" s="7" t="inlineStr">
+        <is>
+          <t>4Q26E</t>
+        </is>
+      </c>
+      <c r="AA4" s="7" t="inlineStr">
+        <is>
+          <t>1Q27E</t>
+        </is>
+      </c>
+      <c r="AB4" s="7" t="inlineStr">
+        <is>
+          <t>2Q27E</t>
+        </is>
+      </c>
+      <c r="AC4" s="7" t="inlineStr">
+        <is>
+          <t>3Q27E</t>
+        </is>
+      </c>
+      <c r="AD4" s="7" t="inlineStr">
+        <is>
+          <t>4Q27E</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A. Printed ADR and the disclosed identity: reported y/y − ex-FX y/y = FX effect (closes to ≤0.04pp)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+      <c r="Y6" s="5" t="n"/>
+      <c r="Z6" s="5" t="n"/>
+      <c r="AA6" s="5" t="n"/>
+      <c r="AB6" s="5" t="n"/>
+      <c r="AC6" s="5" t="n"/>
+      <c r="AD6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>ADR ($, GBV ÷ nights, printed; forward = engine path)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>data/processed/overnight/02_kpi_panel_quarterly.csv adr_usd (letters / 10-Q)</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>159.82</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>161.45</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>149.15</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>153.61</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>168.07</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>163.74</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>156.44</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>152.81</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>168.43</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>166.01</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>161.38</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>156.73</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>172.88</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>169.53</v>
+      </c>
+      <c r="Q7" s="11" t="n">
+        <v>163.64</v>
+      </c>
+      <c r="R7" s="11" t="n">
+        <v>158.13</v>
+      </c>
+      <c r="S7" s="11" t="n">
+        <v>171.34</v>
+      </c>
+      <c r="T7" s="11" t="n">
+        <v>174.48</v>
+      </c>
+      <c r="U7" s="11" t="n">
+        <v>171.29</v>
+      </c>
+      <c r="V7" s="11" t="n">
+        <v>167.51</v>
+      </c>
+      <c r="W7" s="11" t="n">
+        <v>186.82</v>
+      </c>
+      <c r="X7" s="11" t="n">
+        <v>183.73</v>
+      </c>
+      <c r="Y7" s="20">
+        <f>Y96</f>
+        <v/>
+      </c>
+      <c r="Z7" s="20">
+        <f>Z96</f>
+        <v/>
+      </c>
+      <c r="AA7" s="20">
+        <f>AA96</f>
+        <v/>
+      </c>
+      <c r="AB7" s="20">
+        <f>AB96</f>
+        <v/>
+      </c>
+      <c r="AC7" s="20">
+        <f>AC96</f>
+        <v/>
+      </c>
+      <c r="AD7" s="20">
+        <f>AD96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reported y/y</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>→ ADR / ADR four quarters earlier − 1</t>
+        </is>
+      </c>
+      <c r="G8" s="10">
+        <f>G7/C7-1</f>
+        <v/>
+      </c>
+      <c r="H8" s="10">
+        <f>H7/D7-1</f>
+        <v/>
+      </c>
+      <c r="I8" s="10">
+        <f>I7/E7-1</f>
+        <v/>
+      </c>
+      <c r="J8" s="10">
+        <f>J7/F7-1</f>
+        <v/>
+      </c>
+      <c r="K8" s="10">
+        <f>K7/G7-1</f>
+        <v/>
+      </c>
+      <c r="L8" s="10">
+        <f>L7/H7-1</f>
+        <v/>
+      </c>
+      <c r="M8" s="10">
+        <f>M7/I7-1</f>
+        <v/>
+      </c>
+      <c r="N8" s="10">
+        <f>N7/J7-1</f>
+        <v/>
+      </c>
+      <c r="O8" s="10">
+        <f>O7/K7-1</f>
+        <v/>
+      </c>
+      <c r="P8" s="10">
+        <f>P7/L7-1</f>
+        <v/>
+      </c>
+      <c r="Q8" s="10">
+        <f>Q7/M7-1</f>
+        <v/>
+      </c>
+      <c r="R8" s="10">
+        <f>R7/N7-1</f>
+        <v/>
+      </c>
+      <c r="S8" s="10">
+        <f>S7/O7-1</f>
+        <v/>
+      </c>
+      <c r="T8" s="10">
+        <f>T7/P7-1</f>
+        <v/>
+      </c>
+      <c r="U8" s="10">
+        <f>U7/Q7-1</f>
+        <v/>
+      </c>
+      <c r="V8" s="10">
+        <f>V7/R7-1</f>
+        <v/>
+      </c>
+      <c r="W8" s="10">
+        <f>W7/S7-1</f>
+        <v/>
+      </c>
+      <c r="X8" s="10">
+        <f>X7/T7-1</f>
+        <v/>
+      </c>
+      <c r="Y8" s="10">
+        <f>Y7/U7-1</f>
+        <v/>
+      </c>
+      <c r="Z8" s="10">
+        <f>Z7/V7-1</f>
+        <v/>
+      </c>
+      <c r="AA8" s="10">
+        <f>AA7/W7-1</f>
+        <v/>
+      </c>
+      <c r="AB8" s="10">
+        <f>AB7/X7-1</f>
+        <v/>
+      </c>
+      <c r="AC8" s="10">
+        <f>AC7/Y7-1</f>
+        <v/>
+      </c>
+      <c r="AD8" s="10">
+        <f>AD7/Z7-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ex-FX y/y, as stated in the letter (whole points; 3Q23/4Q23 'less than 1%' → 0.5)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>02_kpi_panel_quarterly.csv adr_yoy_exfx_pct; 2Q22 onward</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="W9" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="X9" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FX effect on ADR (pp) — the disclosed target</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>→ reported y/y × 100 − ex-FX y/y</t>
+        </is>
+      </c>
+      <c r="H10" s="15">
+        <f>H8*100-H9</f>
+        <v/>
+      </c>
+      <c r="I10" s="15">
+        <f>I8*100-I9</f>
+        <v/>
+      </c>
+      <c r="J10" s="15">
+        <f>J8*100-J9</f>
+        <v/>
+      </c>
+      <c r="K10" s="15">
+        <f>K8*100-K9</f>
+        <v/>
+      </c>
+      <c r="L10" s="15">
+        <f>L8*100-L9</f>
+        <v/>
+      </c>
+      <c r="M10" s="15">
+        <f>M8*100-M9</f>
+        <v/>
+      </c>
+      <c r="N10" s="15">
+        <f>N8*100-N9</f>
+        <v/>
+      </c>
+      <c r="O10" s="15">
+        <f>O8*100-O9</f>
+        <v/>
+      </c>
+      <c r="P10" s="15">
+        <f>P8*100-P9</f>
+        <v/>
+      </c>
+      <c r="Q10" s="15">
+        <f>Q8*100-Q9</f>
+        <v/>
+      </c>
+      <c r="R10" s="15">
+        <f>R8*100-R9</f>
+        <v/>
+      </c>
+      <c r="S10" s="15">
+        <f>S8*100-S9</f>
+        <v/>
+      </c>
+      <c r="T10" s="15">
+        <f>T8*100-T9</f>
+        <v/>
+      </c>
+      <c r="U10" s="15">
+        <f>U8*100-U9</f>
+        <v/>
+      </c>
+      <c r="V10" s="15">
+        <f>V8*100-V9</f>
+        <v/>
+      </c>
+      <c r="W10" s="15">
+        <f>W8*100-W9</f>
+        <v/>
+      </c>
+      <c r="X10" s="15">
+        <f>X8*100-X9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>B. FX translation identity (ex ante): FX pp = Σ_region GBV share × Σ_currency κ × (avg rate / avg rate a year earlier − 1) — zero fitted parameters</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="5" t="n"/>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="5" t="n"/>
+      <c r="Y12" s="5" t="n"/>
+      <c r="Z12" s="5" t="n"/>
+      <c r="AA12" s="5" t="n"/>
+      <c r="AB12" s="5" t="n"/>
+      <c r="AC12" s="5" t="n"/>
+      <c r="AD12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly average USD per EUR (business days; forward = spot held from 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>FRED DEXUSEU → adr_engine/fx_daily_2026-09-21.csv (fetch_fx.py)</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>1.2051578125</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>1.205263076923077</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>1.178662121212121</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>1.143265151515152</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>1.122084375</v>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>1.064409230769231</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>1.007031818181819</v>
+      </c>
+      <c r="J13" s="25" t="n">
+        <v>1.021918461538462</v>
+      </c>
+      <c r="K13" s="25" t="n">
+        <v>1.072967692307692</v>
+      </c>
+      <c r="L13" s="25" t="n">
+        <v>1.088615384615385</v>
+      </c>
+      <c r="M13" s="25" t="n">
+        <v>1.088321538461538</v>
+      </c>
+      <c r="N13" s="25" t="n">
+        <v>1.076330769230769</v>
+      </c>
+      <c r="O13" s="25" t="n">
+        <v>1.085847692307692</v>
+      </c>
+      <c r="P13" s="25" t="n">
+        <v>1.07668</v>
+      </c>
+      <c r="Q13" s="25" t="n">
+        <v>1.098504545454545</v>
+      </c>
+      <c r="R13" s="25" t="n">
+        <v>1.066693939393939</v>
+      </c>
+      <c r="S13" s="25" t="n">
+        <v>1.0523953125</v>
+      </c>
+      <c r="T13" s="25" t="n">
+        <v>1.134446153846154</v>
+      </c>
+      <c r="U13" s="25" t="n">
+        <v>1.168668181818182</v>
+      </c>
+      <c r="V13" s="25" t="n">
+        <v>1.164089393939394</v>
+      </c>
+      <c r="W13" s="25" t="n">
+        <v>1.17030625</v>
+      </c>
+      <c r="X13" s="25" t="n">
+        <v>1.162887692307692</v>
+      </c>
+      <c r="Y13" s="25" t="n">
+        <v>1.151559090909091</v>
+      </c>
+      <c r="Z13" s="25" t="n">
+        <v>1.1464</v>
+      </c>
+      <c r="AA13" s="25" t="n">
+        <v>1.1464</v>
+      </c>
+      <c r="AB13" s="25" t="n">
+        <v>1.1464</v>
+      </c>
+      <c r="AC13" s="25" t="n">
+        <v>1.1464</v>
+      </c>
+      <c r="AD13" s="25" t="n">
+        <v>1.1464</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly average USD per GBP (business days; forward = spot held from 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>FRED DEXUSUK → adr_engine/fx_daily_2026-09-21.csv (fetch_fx.py)</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>1.3790890625</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>1.398447692307692</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>1.378066666666666</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>1.348445454545454</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>1.3413921875</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>1.255924615384615</v>
+      </c>
+      <c r="I14" s="25" t="n">
+        <v>1.17679696969697</v>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>1.175173846153846</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>1.215069230769231</v>
+      </c>
+      <c r="L14" s="25" t="n">
+        <v>1.252130769230769</v>
+      </c>
+      <c r="M14" s="25" t="n">
+        <v>1.2662</v>
+      </c>
+      <c r="N14" s="25" t="n">
+        <v>1.241984615384616</v>
+      </c>
+      <c r="O14" s="25" t="n">
+        <v>1.268255384615384</v>
+      </c>
+      <c r="P14" s="25" t="n">
+        <v>1.262155384615385</v>
+      </c>
+      <c r="Q14" s="25" t="n">
+        <v>1.300309090909091</v>
+      </c>
+      <c r="R14" s="25" t="n">
+        <v>1.281445454545455</v>
+      </c>
+      <c r="S14" s="25" t="n">
+        <v>1.2597046875</v>
+      </c>
+      <c r="T14" s="25" t="n">
+        <v>1.335726153846154</v>
+      </c>
+      <c r="U14" s="25" t="n">
+        <v>1.348674242424242</v>
+      </c>
+      <c r="V14" s="25" t="n">
+        <v>1.33045909090909</v>
+      </c>
+      <c r="W14" s="25" t="n">
+        <v>1.34788125</v>
+      </c>
+      <c r="X14" s="25" t="n">
+        <v>1.34264</v>
+      </c>
+      <c r="Y14" s="25" t="n">
+        <v>1.345693939393939</v>
+      </c>
+      <c r="Z14" s="25" t="n">
+        <v>1.3372</v>
+      </c>
+      <c r="AA14" s="25" t="n">
+        <v>1.3372</v>
+      </c>
+      <c r="AB14" s="25" t="n">
+        <v>1.3372</v>
+      </c>
+      <c r="AC14" s="25" t="n">
+        <v>1.3372</v>
+      </c>
+      <c r="AD14" s="25" t="n">
+        <v>1.3372</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly average USD per BRL (business days; forward = spot held from 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>FRED DEXBZUS → adr_engine/fx_daily_2026-09-21.csv (fetch_fx.py)</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>0.1828723008270418</v>
+      </c>
+      <c r="D15" s="25" t="n">
+        <v>0.1892937986848461</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>0.1914042175840341</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>0.179017888235438</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>0.191803311632118</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>0.2034853228954897</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>0.1907429645142075</v>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>0.1903125873972193</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>0.1925591939673749</v>
+      </c>
+      <c r="L15" s="25" t="n">
+        <v>0.2020691317800913</v>
+      </c>
+      <c r="M15" s="25" t="n">
+        <v>0.2049451450606586</v>
+      </c>
+      <c r="N15" s="25" t="n">
+        <v>0.201970528062551</v>
+      </c>
+      <c r="O15" s="25" t="n">
+        <v>0.2020322155687002</v>
+      </c>
+      <c r="P15" s="25" t="n">
+        <v>0.1920076732120785</v>
+      </c>
+      <c r="Q15" s="25" t="n">
+        <v>0.1803480448147409</v>
+      </c>
+      <c r="R15" s="25" t="n">
+        <v>0.1714218169833799</v>
+      </c>
+      <c r="S15" s="25" t="n">
+        <v>0.1709567952814824</v>
+      </c>
+      <c r="T15" s="25" t="n">
+        <v>0.1764898545864937</v>
+      </c>
+      <c r="U15" s="25" t="n">
+        <v>0.1836054570282772</v>
+      </c>
+      <c r="V15" s="25" t="n">
+        <v>0.1852856369145278</v>
+      </c>
+      <c r="W15" s="25" t="n">
+        <v>0.1902132769878812</v>
+      </c>
+      <c r="X15" s="25" t="n">
+        <v>0.198124158679975</v>
+      </c>
+      <c r="Y15" s="25" t="n">
+        <v>0.1947710746997425</v>
+      </c>
+      <c r="Z15" s="25" t="n">
+        <v>0.1938134739127064</v>
+      </c>
+      <c r="AA15" s="25" t="n">
+        <v>0.1938134739127064</v>
+      </c>
+      <c r="AB15" s="25" t="n">
+        <v>0.1938134739127064</v>
+      </c>
+      <c r="AC15" s="25" t="n">
+        <v>0.1938134739127064</v>
+      </c>
+      <c r="AD15" s="25" t="n">
+        <v>0.1938134739127064</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly average USD per MXN (business days; forward = spot held from 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>FRED DEXMXUS → adr_engine/fx_daily_2026-09-21.csv (fetch_fx.py)</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>0.04918832670718521</v>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>0.0499773784755694</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>0.0499411766982432</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>0.04821163312584239</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>0.04879082613628123</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>0.04988255105181749</v>
+      </c>
+      <c r="I16" s="25" t="n">
+        <v>0.04943885391995816</v>
+      </c>
+      <c r="J16" s="25" t="n">
+        <v>0.05084030729701012</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0.05360100537952309</v>
+      </c>
+      <c r="L16" s="25" t="n">
+        <v>0.05658791078503513</v>
+      </c>
+      <c r="M16" s="25" t="n">
+        <v>0.05864068251264604</v>
+      </c>
+      <c r="N16" s="25" t="n">
+        <v>0.05704565331136915</v>
+      </c>
+      <c r="O16" s="25" t="n">
+        <v>0.05889471705027263</v>
+      </c>
+      <c r="P16" s="25" t="n">
+        <v>0.05812609026921273</v>
+      </c>
+      <c r="Q16" s="25" t="n">
+        <v>0.05291877628782751</v>
+      </c>
+      <c r="R16" s="25" t="n">
+        <v>0.04978366379307615</v>
+      </c>
+      <c r="S16" s="25" t="n">
+        <v>0.04897989819692692</v>
+      </c>
+      <c r="T16" s="25" t="n">
+        <v>0.05128912381740783</v>
+      </c>
+      <c r="U16" s="25" t="n">
+        <v>0.05369154947405428</v>
+      </c>
+      <c r="V16" s="25" t="n">
+        <v>0.05465944166609391</v>
+      </c>
+      <c r="W16" s="25" t="n">
+        <v>0.05695579703830193</v>
+      </c>
+      <c r="X16" s="25" t="n">
+        <v>0.05753358459784357</v>
+      </c>
+      <c r="Y16" s="25" t="n">
+        <v>0.05811213303178497</v>
+      </c>
+      <c r="Z16" s="25" t="n">
+        <v>0.05798647755343456</v>
+      </c>
+      <c r="AA16" s="25" t="n">
+        <v>0.05798647755343456</v>
+      </c>
+      <c r="AB16" s="25" t="n">
+        <v>0.05798647755343456</v>
+      </c>
+      <c r="AC16" s="25" t="n">
+        <v>0.05798647755343456</v>
+      </c>
+      <c r="AD16" s="25" t="n">
+        <v>0.05798647755343456</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly average USD per JPY (business days; forward = spot held from 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>FRED DEXJPUS → adr_engine/fx_daily_2026-09-21.csv (fetch_fx.py)</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>0.009434905091065392</v>
+      </c>
+      <c r="D17" s="25" t="n">
+        <v>0.009138125350288963</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>0.009084201253293359</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>0.008796893481521673</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>0.008602321487547578</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>0.007712151988556444</v>
+      </c>
+      <c r="I17" s="25" t="n">
+        <v>0.007234613902285213</v>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>0.007089682009248813</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>0.00755632884427469</v>
+      </c>
+      <c r="L17" s="25" t="n">
+        <v>0.007279496228318787</v>
+      </c>
+      <c r="M17" s="25" t="n">
+        <v>0.006920795766246872</v>
+      </c>
+      <c r="N17" s="25" t="n">
+        <v>0.006768800148017067</v>
+      </c>
+      <c r="O17" s="25" t="n">
+        <v>0.006739872084298605</v>
+      </c>
+      <c r="P17" s="25" t="n">
+        <v>0.006418765857552636</v>
+      </c>
+      <c r="Q17" s="25" t="n">
+        <v>0.006713874936983914</v>
+      </c>
+      <c r="R17" s="25" t="n">
+        <v>0.006564705003169738</v>
+      </c>
+      <c r="S17" s="25" t="n">
+        <v>0.006559285210100668</v>
+      </c>
+      <c r="T17" s="25" t="n">
+        <v>0.006923223900108332</v>
+      </c>
+      <c r="U17" s="25" t="n">
+        <v>0.006781857666450467</v>
+      </c>
+      <c r="V17" s="25" t="n">
+        <v>0.006490955794272727</v>
+      </c>
+      <c r="W17" s="25" t="n">
+        <v>0.006376553573657654</v>
+      </c>
+      <c r="X17" s="25" t="n">
+        <v>0.006274375676076636</v>
+      </c>
+      <c r="Y17" s="25" t="n">
+        <v>0.006286411311271813</v>
+      </c>
+      <c r="Z17" s="25" t="n">
+        <v>0.006374705169885805</v>
+      </c>
+      <c r="AA17" s="25" t="n">
+        <v>0.006374705169885805</v>
+      </c>
+      <c r="AB17" s="25" t="n">
+        <v>0.006374705169885805</v>
+      </c>
+      <c r="AC17" s="25" t="n">
+        <v>0.006374705169885805</v>
+      </c>
+      <c r="AD17" s="25" t="n">
+        <v>0.006374705169885805</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly average USD per AUD (business days; forward = spot held from 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FRED DEXUSAL → adr_engine/fx_daily_2026-09-21.csv (fetch_fx.py)</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>0.7728421874999999</v>
+      </c>
+      <c r="D18" s="25" t="n">
+        <v>0.7700661538461536</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>0.7347666666666668</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>0.7287893939393935</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>0.7247046875000001</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>0.7140476923076925</v>
+      </c>
+      <c r="I18" s="25" t="n">
+        <v>0.6832560606060607</v>
+      </c>
+      <c r="J18" s="25" t="n">
+        <v>0.6575876923076923</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0.6834553846153846</v>
+      </c>
+      <c r="L18" s="25" t="n">
+        <v>0.6681000000000001</v>
+      </c>
+      <c r="M18" s="25" t="n">
+        <v>0.6548123076923076</v>
+      </c>
+      <c r="N18" s="25" t="n">
+        <v>0.6514723076923078</v>
+      </c>
+      <c r="O18" s="25" t="n">
+        <v>0.6578046153846154</v>
+      </c>
+      <c r="P18" s="25" t="n">
+        <v>0.6590723076923076</v>
+      </c>
+      <c r="Q18" s="25" t="n">
+        <v>0.6699348484848485</v>
+      </c>
+      <c r="R18" s="25" t="n">
+        <v>0.6522651515151514</v>
+      </c>
+      <c r="S18" s="25" t="n">
+        <v>0.6275421875</v>
+      </c>
+      <c r="T18" s="25" t="n">
+        <v>0.6410723076923076</v>
+      </c>
+      <c r="U18" s="25" t="n">
+        <v>0.6543196969696971</v>
+      </c>
+      <c r="V18" s="25" t="n">
+        <v>0.6567257575757575</v>
+      </c>
+      <c r="W18" s="25" t="n">
+        <v>0.6949359375000002</v>
+      </c>
+      <c r="X18" s="25" t="n">
+        <v>0.7099738461538465</v>
+      </c>
+      <c r="Y18" s="25" t="n">
+        <v>0.7071303030303033</v>
+      </c>
+      <c r="Z18" s="25" t="n">
+        <v>0.7111000000000001</v>
+      </c>
+      <c r="AA18" s="25" t="n">
+        <v>0.7111</v>
+      </c>
+      <c r="AB18" s="25" t="n">
+        <v>0.7111</v>
+      </c>
+      <c r="AC18" s="25" t="n">
+        <v>0.7111000000000001</v>
+      </c>
+      <c r="AD18" s="25" t="n">
+        <v>0.7111000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly average USD per KRW (business days; forward = spot held from 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>FRED DEXKOUS → adr_engine/fx_daily_2026-09-21.csv (fetch_fx.py)</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>0.0008980574082007703</v>
+      </c>
+      <c r="D19" s="25" t="n">
+        <v>0.0008919450061835182</v>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>0.0008625012419089757</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>0.0008448975458408619</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>0.0008294930814214625</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>0.0007935042363192045</v>
+      </c>
+      <c r="I19" s="25" t="n">
+        <v>0.0007465734439631378</v>
+      </c>
+      <c r="J19" s="25" t="n">
+        <v>0.0007371386506815184</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>0.0007842569249517721</v>
+      </c>
+      <c r="L19" s="25" t="n">
+        <v>0.0007605086499953661</v>
+      </c>
+      <c r="M19" s="25" t="n">
+        <v>0.0007617837450221322</v>
+      </c>
+      <c r="N19" s="25" t="n">
+        <v>0.0007569954473562218</v>
+      </c>
+      <c r="O19" s="25" t="n">
+        <v>0.0007525865917639829</v>
+      </c>
+      <c r="P19" s="25" t="n">
+        <v>0.0007298318452153125</v>
+      </c>
+      <c r="Q19" s="25" t="n">
+        <v>0.000737899662253835</v>
+      </c>
+      <c r="R19" s="25" t="n">
+        <v>0.0007154503756419076</v>
+      </c>
+      <c r="S19" s="25" t="n">
+        <v>0.0006886114113059277</v>
+      </c>
+      <c r="T19" s="25" t="n">
+        <v>0.0007153119891327108</v>
+      </c>
+      <c r="U19" s="25" t="n">
+        <v>0.0007212043142890151</v>
+      </c>
+      <c r="V19" s="25" t="n">
+        <v>0.0006903961148526531</v>
+      </c>
+      <c r="W19" s="25" t="n">
+        <v>0.000682762487362517</v>
+      </c>
+      <c r="X19" s="25" t="n">
+        <v>0.0006662624103036613</v>
+      </c>
+      <c r="Y19" s="25" t="n">
+        <v>0.0007047699372736059</v>
+      </c>
+      <c r="Z19" s="25" t="n">
+        <v>0.0007204766673631</v>
+      </c>
+      <c r="AA19" s="25" t="n">
+        <v>0.0007204766673631</v>
+      </c>
+      <c r="AB19" s="25" t="n">
+        <v>0.0007204766673631</v>
+      </c>
+      <c r="AC19" s="25" t="n">
+        <v>0.0007204766673631</v>
+      </c>
+      <c r="AD19" s="25" t="n">
+        <v>0.0007204766673631</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly average USD per CAD (business days; forward = spot held from 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>FRED DEXCAUS → adr_engine/fx_daily_2026-09-21.csv (fetch_fx.py)</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>0.7899369597419825</v>
+      </c>
+      <c r="D20" s="25" t="n">
+        <v>0.8144081005015442</v>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>0.7940114841853838</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>0.7934498816011684</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>0.7897413249233408</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>0.7833372703335949</v>
+      </c>
+      <c r="I20" s="25" t="n">
+        <v>0.7659868168487041</v>
+      </c>
+      <c r="J20" s="25" t="n">
+        <v>0.7367998779480021</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0.739380892237658</v>
+      </c>
+      <c r="L20" s="25" t="n">
+        <v>0.7447272926565711</v>
+      </c>
+      <c r="M20" s="25" t="n">
+        <v>0.7457969007176178</v>
+      </c>
+      <c r="N20" s="25" t="n">
+        <v>0.7347331249324642</v>
+      </c>
+      <c r="O20" s="25" t="n">
+        <v>0.7418575119102154</v>
+      </c>
+      <c r="P20" s="25" t="n">
+        <v>0.7309494172204517</v>
+      </c>
+      <c r="Q20" s="25" t="n">
+        <v>0.7332502871348516</v>
+      </c>
+      <c r="R20" s="25" t="n">
+        <v>0.7149381444652281</v>
+      </c>
+      <c r="S20" s="25" t="n">
+        <v>0.696965857642778</v>
+      </c>
+      <c r="T20" s="25" t="n">
+        <v>0.7226533581528588</v>
+      </c>
+      <c r="U20" s="25" t="n">
+        <v>0.7263006684597706</v>
+      </c>
+      <c r="V20" s="25" t="n">
+        <v>0.7174737354887584</v>
+      </c>
+      <c r="W20" s="25" t="n">
+        <v>0.7291271271354296</v>
+      </c>
+      <c r="X20" s="25" t="n">
+        <v>0.7226625121141692</v>
+      </c>
+      <c r="Y20" s="25" t="n">
+        <v>0.715337319564357</v>
+      </c>
+      <c r="Z20" s="25" t="n">
+        <v>0.7138777841233571</v>
+      </c>
+      <c r="AA20" s="25" t="n">
+        <v>0.7138777841233572</v>
+      </c>
+      <c r="AB20" s="25" t="n">
+        <v>0.7138777841233572</v>
+      </c>
+      <c r="AC20" s="25" t="n">
+        <v>0.7138777841233571</v>
+      </c>
+      <c r="AD20" s="25" t="n">
+        <v>0.7138777841233571</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly average USD per INR (business days; forward = spot held from 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>FRED DEXINUS → adr_engine/fx_daily_2026-09-21.csv (fetch_fx.py)</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>0.01371640452690674</v>
+      </c>
+      <c r="D21" s="25" t="n">
+        <v>0.01355829368439952</v>
+      </c>
+      <c r="E21" s="25" t="n">
+        <v>0.01349835916932289</v>
+      </c>
+      <c r="F21" s="25" t="n">
+        <v>0.01334879644596242</v>
+      </c>
+      <c r="G21" s="25" t="n">
+        <v>0.0132972184186094</v>
+      </c>
+      <c r="H21" s="25" t="n">
+        <v>0.01295445844676586</v>
+      </c>
+      <c r="I21" s="25" t="n">
+        <v>0.01253786180770151</v>
+      </c>
+      <c r="J21" s="25" t="n">
+        <v>0.01217521170123298</v>
+      </c>
+      <c r="K21" s="25" t="n">
+        <v>0.01216573172989259</v>
+      </c>
+      <c r="L21" s="25" t="n">
+        <v>0.01216991360465129</v>
+      </c>
+      <c r="M21" s="25" t="n">
+        <v>0.01209591888833167</v>
+      </c>
+      <c r="N21" s="25" t="n">
+        <v>0.01201291290368868</v>
+      </c>
+      <c r="O21" s="25" t="n">
+        <v>0.01204400393306578</v>
+      </c>
+      <c r="P21" s="25" t="n">
+        <v>0.01198932693191114</v>
+      </c>
+      <c r="Q21" s="25" t="n">
+        <v>0.01194017385618696</v>
+      </c>
+      <c r="R21" s="25" t="n">
+        <v>0.01184368962439188</v>
+      </c>
+      <c r="S21" s="25" t="n">
+        <v>0.01154940548819701</v>
+      </c>
+      <c r="T21" s="25" t="n">
+        <v>0.01168677454510077</v>
+      </c>
+      <c r="U21" s="25" t="n">
+        <v>0.0114539660026601</v>
+      </c>
+      <c r="V21" s="25" t="n">
+        <v>0.01122423972080312</v>
+      </c>
+      <c r="W21" s="25" t="n">
+        <v>0.01093172766317048</v>
+      </c>
+      <c r="X21" s="25" t="n">
+        <v>0.01056799659097119</v>
+      </c>
+      <c r="Y21" s="25" t="n">
+        <v>0.010461346931782</v>
+      </c>
+      <c r="Z21" s="25" t="n">
+        <v>0.01043079169708981</v>
+      </c>
+      <c r="AA21" s="25" t="n">
+        <v>0.01043079169708981</v>
+      </c>
+      <c r="AB21" s="25" t="n">
+        <v>0.01043079169708981</v>
+      </c>
+      <c r="AC21" s="25" t="n">
+        <v>0.01043079169708981</v>
+      </c>
+      <c r="AD21" s="25" t="n">
+        <v>0.01043079169708981</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    share of the quarter's business days printed at 18 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>engine fx_forecast_asof.csv obs_frac_at_asof</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="12" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="Z22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EUR y/y of the quarterly average (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>→ (avg / avg four quarters earlier − 1) × 100</t>
+        </is>
+      </c>
+      <c r="G24" s="16">
+        <f>(G13/C13-1)*100</f>
+        <v/>
+      </c>
+      <c r="H24" s="16">
+        <f>(H13/D13-1)*100</f>
+        <v/>
+      </c>
+      <c r="I24" s="16">
+        <f>(I13/E13-1)*100</f>
+        <v/>
+      </c>
+      <c r="J24" s="16">
+        <f>(J13/F13-1)*100</f>
+        <v/>
+      </c>
+      <c r="K24" s="16">
+        <f>(K13/G13-1)*100</f>
+        <v/>
+      </c>
+      <c r="L24" s="16">
+        <f>(L13/H13-1)*100</f>
+        <v/>
+      </c>
+      <c r="M24" s="16">
+        <f>(M13/I13-1)*100</f>
+        <v/>
+      </c>
+      <c r="N24" s="16">
+        <f>(N13/J13-1)*100</f>
+        <v/>
+      </c>
+      <c r="O24" s="16">
+        <f>(O13/K13-1)*100</f>
+        <v/>
+      </c>
+      <c r="P24" s="16">
+        <f>(P13/L13-1)*100</f>
+        <v/>
+      </c>
+      <c r="Q24" s="16">
+        <f>(Q13/M13-1)*100</f>
+        <v/>
+      </c>
+      <c r="R24" s="16">
+        <f>(R13/N13-1)*100</f>
+        <v/>
+      </c>
+      <c r="S24" s="16">
+        <f>(S13/O13-1)*100</f>
+        <v/>
+      </c>
+      <c r="T24" s="16">
+        <f>(T13/P13-1)*100</f>
+        <v/>
+      </c>
+      <c r="U24" s="16">
+        <f>(U13/Q13-1)*100</f>
+        <v/>
+      </c>
+      <c r="V24" s="16">
+        <f>(V13/R13-1)*100</f>
+        <v/>
+      </c>
+      <c r="W24" s="16">
+        <f>(W13/S13-1)*100</f>
+        <v/>
+      </c>
+      <c r="X24" s="16">
+        <f>(X13/T13-1)*100</f>
+        <v/>
+      </c>
+      <c r="Y24" s="16">
+        <f>(Y13/U13-1)*100</f>
+        <v/>
+      </c>
+      <c r="Z24" s="16">
+        <f>(Z13/V13-1)*100</f>
+        <v/>
+      </c>
+      <c r="AA24" s="16">
+        <f>(AA13/W13-1)*100</f>
+        <v/>
+      </c>
+      <c r="AB24" s="16">
+        <f>(AB13/X13-1)*100</f>
+        <v/>
+      </c>
+      <c r="AC24" s="16">
+        <f>(AC13/Y13-1)*100</f>
+        <v/>
+      </c>
+      <c r="AD24" s="16">
+        <f>(AD13/Z13-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GBP y/y of the quarterly average (%)</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>→ (avg / avg four quarters earlier − 1) × 100</t>
+        </is>
+      </c>
+      <c r="G25" s="16">
+        <f>(G14/C14-1)*100</f>
+        <v/>
+      </c>
+      <c r="H25" s="16">
+        <f>(H14/D14-1)*100</f>
+        <v/>
+      </c>
+      <c r="I25" s="16">
+        <f>(I14/E14-1)*100</f>
+        <v/>
+      </c>
+      <c r="J25" s="16">
+        <f>(J14/F14-1)*100</f>
+        <v/>
+      </c>
+      <c r="K25" s="16">
+        <f>(K14/G14-1)*100</f>
+        <v/>
+      </c>
+      <c r="L25" s="16">
+        <f>(L14/H14-1)*100</f>
+        <v/>
+      </c>
+      <c r="M25" s="16">
+        <f>(M14/I14-1)*100</f>
+        <v/>
+      </c>
+      <c r="N25" s="16">
+        <f>(N14/J14-1)*100</f>
+        <v/>
+      </c>
+      <c r="O25" s="16">
+        <f>(O14/K14-1)*100</f>
+        <v/>
+      </c>
+      <c r="P25" s="16">
+        <f>(P14/L14-1)*100</f>
+        <v/>
+      </c>
+      <c r="Q25" s="16">
+        <f>(Q14/M14-1)*100</f>
+        <v/>
+      </c>
+      <c r="R25" s="16">
+        <f>(R14/N14-1)*100</f>
+        <v/>
+      </c>
+      <c r="S25" s="16">
+        <f>(S14/O14-1)*100</f>
+        <v/>
+      </c>
+      <c r="T25" s="16">
+        <f>(T14/P14-1)*100</f>
+        <v/>
+      </c>
+      <c r="U25" s="16">
+        <f>(U14/Q14-1)*100</f>
+        <v/>
+      </c>
+      <c r="V25" s="16">
+        <f>(V14/R14-1)*100</f>
+        <v/>
+      </c>
+      <c r="W25" s="16">
+        <f>(W14/S14-1)*100</f>
+        <v/>
+      </c>
+      <c r="X25" s="16">
+        <f>(X14/T14-1)*100</f>
+        <v/>
+      </c>
+      <c r="Y25" s="16">
+        <f>(Y14/U14-1)*100</f>
+        <v/>
+      </c>
+      <c r="Z25" s="16">
+        <f>(Z14/V14-1)*100</f>
+        <v/>
+      </c>
+      <c r="AA25" s="16">
+        <f>(AA14/W14-1)*100</f>
+        <v/>
+      </c>
+      <c r="AB25" s="16">
+        <f>(AB14/X14-1)*100</f>
+        <v/>
+      </c>
+      <c r="AC25" s="16">
+        <f>(AC14/Y14-1)*100</f>
+        <v/>
+      </c>
+      <c r="AD25" s="16">
+        <f>(AD14/Z14-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    BRL y/y of the quarterly average (%)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>→ (avg / avg four quarters earlier − 1) × 100</t>
+        </is>
+      </c>
+      <c r="G26" s="16">
+        <f>(G15/C15-1)*100</f>
+        <v/>
+      </c>
+      <c r="H26" s="16">
+        <f>(H15/D15-1)*100</f>
+        <v/>
+      </c>
+      <c r="I26" s="16">
+        <f>(I15/E15-1)*100</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>(J15/F15-1)*100</f>
+        <v/>
+      </c>
+      <c r="K26" s="16">
+        <f>(K15/G15-1)*100</f>
+        <v/>
+      </c>
+      <c r="L26" s="16">
+        <f>(L15/H15-1)*100</f>
+        <v/>
+      </c>
+      <c r="M26" s="16">
+        <f>(M15/I15-1)*100</f>
+        <v/>
+      </c>
+      <c r="N26" s="16">
+        <f>(N15/J15-1)*100</f>
+        <v/>
+      </c>
+      <c r="O26" s="16">
+        <f>(O15/K15-1)*100</f>
+        <v/>
+      </c>
+      <c r="P26" s="16">
+        <f>(P15/L15-1)*100</f>
+        <v/>
+      </c>
+      <c r="Q26" s="16">
+        <f>(Q15/M15-1)*100</f>
+        <v/>
+      </c>
+      <c r="R26" s="16">
+        <f>(R15/N15-1)*100</f>
+        <v/>
+      </c>
+      <c r="S26" s="16">
+        <f>(S15/O15-1)*100</f>
+        <v/>
+      </c>
+      <c r="T26" s="16">
+        <f>(T15/P15-1)*100</f>
+        <v/>
+      </c>
+      <c r="U26" s="16">
+        <f>(U15/Q15-1)*100</f>
+        <v/>
+      </c>
+      <c r="V26" s="16">
+        <f>(V15/R15-1)*100</f>
+        <v/>
+      </c>
+      <c r="W26" s="16">
+        <f>(W15/S15-1)*100</f>
+        <v/>
+      </c>
+      <c r="X26" s="16">
+        <f>(X15/T15-1)*100</f>
+        <v/>
+      </c>
+      <c r="Y26" s="16">
+        <f>(Y15/U15-1)*100</f>
+        <v/>
+      </c>
+      <c r="Z26" s="16">
+        <f>(Z15/V15-1)*100</f>
+        <v/>
+      </c>
+      <c r="AA26" s="16">
+        <f>(AA15/W15-1)*100</f>
+        <v/>
+      </c>
+      <c r="AB26" s="16">
+        <f>(AB15/X15-1)*100</f>
+        <v/>
+      </c>
+      <c r="AC26" s="16">
+        <f>(AC15/Y15-1)*100</f>
+        <v/>
+      </c>
+      <c r="AD26" s="16">
+        <f>(AD15/Z15-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    MXN y/y of the quarterly average (%)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>→ (avg / avg four quarters earlier − 1) × 100</t>
+        </is>
+      </c>
+      <c r="G27" s="16">
+        <f>(G16/C16-1)*100</f>
+        <v/>
+      </c>
+      <c r="H27" s="16">
+        <f>(H16/D16-1)*100</f>
+        <v/>
+      </c>
+      <c r="I27" s="16">
+        <f>(I16/E16-1)*100</f>
+        <v/>
+      </c>
+      <c r="J27" s="16">
+        <f>(J16/F16-1)*100</f>
+        <v/>
+      </c>
+      <c r="K27" s="16">
+        <f>(K16/G16-1)*100</f>
+        <v/>
+      </c>
+      <c r="L27" s="16">
+        <f>(L16/H16-1)*100</f>
+        <v/>
+      </c>
+      <c r="M27" s="16">
+        <f>(M16/I16-1)*100</f>
+        <v/>
+      </c>
+      <c r="N27" s="16">
+        <f>(N16/J16-1)*100</f>
+        <v/>
+      </c>
+      <c r="O27" s="16">
+        <f>(O16/K16-1)*100</f>
+        <v/>
+      </c>
+      <c r="P27" s="16">
+        <f>(P16/L16-1)*100</f>
+        <v/>
+      </c>
+      <c r="Q27" s="16">
+        <f>(Q16/M16-1)*100</f>
+        <v/>
+      </c>
+      <c r="R27" s="16">
+        <f>(R16/N16-1)*100</f>
+        <v/>
+      </c>
+      <c r="S27" s="16">
+        <f>(S16/O16-1)*100</f>
+        <v/>
+      </c>
+      <c r="T27" s="16">
+        <f>(T16/P16-1)*100</f>
+        <v/>
+      </c>
+      <c r="U27" s="16">
+        <f>(U16/Q16-1)*100</f>
+        <v/>
+      </c>
+      <c r="V27" s="16">
+        <f>(V16/R16-1)*100</f>
+        <v/>
+      </c>
+      <c r="W27" s="16">
+        <f>(W16/S16-1)*100</f>
+        <v/>
+      </c>
+      <c r="X27" s="16">
+        <f>(X16/T16-1)*100</f>
+        <v/>
+      </c>
+      <c r="Y27" s="16">
+        <f>(Y16/U16-1)*100</f>
+        <v/>
+      </c>
+      <c r="Z27" s="16">
+        <f>(Z16/V16-1)*100</f>
+        <v/>
+      </c>
+      <c r="AA27" s="16">
+        <f>(AA16/W16-1)*100</f>
+        <v/>
+      </c>
+      <c r="AB27" s="16">
+        <f>(AB16/X16-1)*100</f>
+        <v/>
+      </c>
+      <c r="AC27" s="16">
+        <f>(AC16/Y16-1)*100</f>
+        <v/>
+      </c>
+      <c r="AD27" s="16">
+        <f>(AD16/Z16-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JPY y/y of the quarterly average (%)</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>→ (avg / avg four quarters earlier − 1) × 100</t>
+        </is>
+      </c>
+      <c r="G28" s="16">
+        <f>(G17/C17-1)*100</f>
+        <v/>
+      </c>
+      <c r="H28" s="16">
+        <f>(H17/D17-1)*100</f>
+        <v/>
+      </c>
+      <c r="I28" s="16">
+        <f>(I17/E17-1)*100</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>(J17/F17-1)*100</f>
+        <v/>
+      </c>
+      <c r="K28" s="16">
+        <f>(K17/G17-1)*100</f>
+        <v/>
+      </c>
+      <c r="L28" s="16">
+        <f>(L17/H17-1)*100</f>
+        <v/>
+      </c>
+      <c r="M28" s="16">
+        <f>(M17/I17-1)*100</f>
+        <v/>
+      </c>
+      <c r="N28" s="16">
+        <f>(N17/J17-1)*100</f>
+        <v/>
+      </c>
+      <c r="O28" s="16">
+        <f>(O17/K17-1)*100</f>
+        <v/>
+      </c>
+      <c r="P28" s="16">
+        <f>(P17/L17-1)*100</f>
+        <v/>
+      </c>
+      <c r="Q28" s="16">
+        <f>(Q17/M17-1)*100</f>
+        <v/>
+      </c>
+      <c r="R28" s="16">
+        <f>(R17/N17-1)*100</f>
+        <v/>
+      </c>
+      <c r="S28" s="16">
+        <f>(S17/O17-1)*100</f>
+        <v/>
+      </c>
+      <c r="T28" s="16">
+        <f>(T17/P17-1)*100</f>
+        <v/>
+      </c>
+      <c r="U28" s="16">
+        <f>(U17/Q17-1)*100</f>
+        <v/>
+      </c>
+      <c r="V28" s="16">
+        <f>(V17/R17-1)*100</f>
+        <v/>
+      </c>
+      <c r="W28" s="16">
+        <f>(W17/S17-1)*100</f>
+        <v/>
+      </c>
+      <c r="X28" s="16">
+        <f>(X17/T17-1)*100</f>
+        <v/>
+      </c>
+      <c r="Y28" s="16">
+        <f>(Y17/U17-1)*100</f>
+        <v/>
+      </c>
+      <c r="Z28" s="16">
+        <f>(Z17/V17-1)*100</f>
+        <v/>
+      </c>
+      <c r="AA28" s="16">
+        <f>(AA17/W17-1)*100</f>
+        <v/>
+      </c>
+      <c r="AB28" s="16">
+        <f>(AB17/X17-1)*100</f>
+        <v/>
+      </c>
+      <c r="AC28" s="16">
+        <f>(AC17/Y17-1)*100</f>
+        <v/>
+      </c>
+      <c r="AD28" s="16">
+        <f>(AD17/Z17-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    AUD y/y of the quarterly average (%)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>→ (avg / avg four quarters earlier − 1) × 100</t>
+        </is>
+      </c>
+      <c r="G29" s="16">
+        <f>(G18/C18-1)*100</f>
+        <v/>
+      </c>
+      <c r="H29" s="16">
+        <f>(H18/D18-1)*100</f>
+        <v/>
+      </c>
+      <c r="I29" s="16">
+        <f>(I18/E18-1)*100</f>
+        <v/>
+      </c>
+      <c r="J29" s="16">
+        <f>(J18/F18-1)*100</f>
+        <v/>
+      </c>
+      <c r="K29" s="16">
+        <f>(K18/G18-1)*100</f>
+        <v/>
+      </c>
+      <c r="L29" s="16">
+        <f>(L18/H18-1)*100</f>
+        <v/>
+      </c>
+      <c r="M29" s="16">
+        <f>(M18/I18-1)*100</f>
+        <v/>
+      </c>
+      <c r="N29" s="16">
+        <f>(N18/J18-1)*100</f>
+        <v/>
+      </c>
+      <c r="O29" s="16">
+        <f>(O18/K18-1)*100</f>
+        <v/>
+      </c>
+      <c r="P29" s="16">
+        <f>(P18/L18-1)*100</f>
+        <v/>
+      </c>
+      <c r="Q29" s="16">
+        <f>(Q18/M18-1)*100</f>
+        <v/>
+      </c>
+      <c r="R29" s="16">
+        <f>(R18/N18-1)*100</f>
+        <v/>
+      </c>
+      <c r="S29" s="16">
+        <f>(S18/O18-1)*100</f>
+        <v/>
+      </c>
+      <c r="T29" s="16">
+        <f>(T18/P18-1)*100</f>
+        <v/>
+      </c>
+      <c r="U29" s="16">
+        <f>(U18/Q18-1)*100</f>
+        <v/>
+      </c>
+      <c r="V29" s="16">
+        <f>(V18/R18-1)*100</f>
+        <v/>
+      </c>
+      <c r="W29" s="16">
+        <f>(W18/S18-1)*100</f>
+        <v/>
+      </c>
+      <c r="X29" s="16">
+        <f>(X18/T18-1)*100</f>
+        <v/>
+      </c>
+      <c r="Y29" s="16">
+        <f>(Y18/U18-1)*100</f>
+        <v/>
+      </c>
+      <c r="Z29" s="16">
+        <f>(Z18/V18-1)*100</f>
+        <v/>
+      </c>
+      <c r="AA29" s="16">
+        <f>(AA18/W18-1)*100</f>
+        <v/>
+      </c>
+      <c r="AB29" s="16">
+        <f>(AB18/X18-1)*100</f>
+        <v/>
+      </c>
+      <c r="AC29" s="16">
+        <f>(AC18/Y18-1)*100</f>
+        <v/>
+      </c>
+      <c r="AD29" s="16">
+        <f>(AD18/Z18-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    KRW y/y of the quarterly average (%)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>→ (avg / avg four quarters earlier − 1) × 100</t>
+        </is>
+      </c>
+      <c r="G30" s="16">
+        <f>(G19/C19-1)*100</f>
+        <v/>
+      </c>
+      <c r="H30" s="16">
+        <f>(H19/D19-1)*100</f>
+        <v/>
+      </c>
+      <c r="I30" s="16">
+        <f>(I19/E19-1)*100</f>
+        <v/>
+      </c>
+      <c r="J30" s="16">
+        <f>(J19/F19-1)*100</f>
+        <v/>
+      </c>
+      <c r="K30" s="16">
+        <f>(K19/G19-1)*100</f>
+        <v/>
+      </c>
+      <c r="L30" s="16">
+        <f>(L19/H19-1)*100</f>
+        <v/>
+      </c>
+      <c r="M30" s="16">
+        <f>(M19/I19-1)*100</f>
+        <v/>
+      </c>
+      <c r="N30" s="16">
+        <f>(N19/J19-1)*100</f>
+        <v/>
+      </c>
+      <c r="O30" s="16">
+        <f>(O19/K19-1)*100</f>
+        <v/>
+      </c>
+      <c r="P30" s="16">
+        <f>(P19/L19-1)*100</f>
+        <v/>
+      </c>
+      <c r="Q30" s="16">
+        <f>(Q19/M19-1)*100</f>
+        <v/>
+      </c>
+      <c r="R30" s="16">
+        <f>(R19/N19-1)*100</f>
+        <v/>
+      </c>
+      <c r="S30" s="16">
+        <f>(S19/O19-1)*100</f>
+        <v/>
+      </c>
+      <c r="T30" s="16">
+        <f>(T19/P19-1)*100</f>
+        <v/>
+      </c>
+      <c r="U30" s="16">
+        <f>(U19/Q19-1)*100</f>
+        <v/>
+      </c>
+      <c r="V30" s="16">
+        <f>(V19/R19-1)*100</f>
+        <v/>
+      </c>
+      <c r="W30" s="16">
+        <f>(W19/S19-1)*100</f>
+        <v/>
+      </c>
+      <c r="X30" s="16">
+        <f>(X19/T19-1)*100</f>
+        <v/>
+      </c>
+      <c r="Y30" s="16">
+        <f>(Y19/U19-1)*100</f>
+        <v/>
+      </c>
+      <c r="Z30" s="16">
+        <f>(Z19/V19-1)*100</f>
+        <v/>
+      </c>
+      <c r="AA30" s="16">
+        <f>(AA19/W19-1)*100</f>
+        <v/>
+      </c>
+      <c r="AB30" s="16">
+        <f>(AB19/X19-1)*100</f>
+        <v/>
+      </c>
+      <c r="AC30" s="16">
+        <f>(AC19/Y19-1)*100</f>
+        <v/>
+      </c>
+      <c r="AD30" s="16">
+        <f>(AD19/Z19-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CAD y/y of the quarterly average (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>→ (avg / avg four quarters earlier − 1) × 100</t>
+        </is>
+      </c>
+      <c r="G31" s="16">
+        <f>(G20/C20-1)*100</f>
+        <v/>
+      </c>
+      <c r="H31" s="16">
+        <f>(H20/D20-1)*100</f>
+        <v/>
+      </c>
+      <c r="I31" s="16">
+        <f>(I20/E20-1)*100</f>
+        <v/>
+      </c>
+      <c r="J31" s="16">
+        <f>(J20/F20-1)*100</f>
+        <v/>
+      </c>
+      <c r="K31" s="16">
+        <f>(K20/G20-1)*100</f>
+        <v/>
+      </c>
+      <c r="L31" s="16">
+        <f>(L20/H20-1)*100</f>
+        <v/>
+      </c>
+      <c r="M31" s="16">
+        <f>(M20/I20-1)*100</f>
+        <v/>
+      </c>
+      <c r="N31" s="16">
+        <f>(N20/J20-1)*100</f>
+        <v/>
+      </c>
+      <c r="O31" s="16">
+        <f>(O20/K20-1)*100</f>
+        <v/>
+      </c>
+      <c r="P31" s="16">
+        <f>(P20/L20-1)*100</f>
+        <v/>
+      </c>
+      <c r="Q31" s="16">
+        <f>(Q20/M20-1)*100</f>
+        <v/>
+      </c>
+      <c r="R31" s="16">
+        <f>(R20/N20-1)*100</f>
+        <v/>
+      </c>
+      <c r="S31" s="16">
+        <f>(S20/O20-1)*100</f>
+        <v/>
+      </c>
+      <c r="T31" s="16">
+        <f>(T20/P20-1)*100</f>
+        <v/>
+      </c>
+      <c r="U31" s="16">
+        <f>(U20/Q20-1)*100</f>
+        <v/>
+      </c>
+      <c r="V31" s="16">
+        <f>(V20/R20-1)*100</f>
+        <v/>
+      </c>
+      <c r="W31" s="16">
+        <f>(W20/S20-1)*100</f>
+        <v/>
+      </c>
+      <c r="X31" s="16">
+        <f>(X20/T20-1)*100</f>
+        <v/>
+      </c>
+      <c r="Y31" s="16">
+        <f>(Y20/U20-1)*100</f>
+        <v/>
+      </c>
+      <c r="Z31" s="16">
+        <f>(Z20/V20-1)*100</f>
+        <v/>
+      </c>
+      <c r="AA31" s="16">
+        <f>(AA20/W20-1)*100</f>
+        <v/>
+      </c>
+      <c r="AB31" s="16">
+        <f>(AB20/X20-1)*100</f>
+        <v/>
+      </c>
+      <c r="AC31" s="16">
+        <f>(AC20/Y20-1)*100</f>
+        <v/>
+      </c>
+      <c r="AD31" s="16">
+        <f>(AD20/Z20-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INR y/y of the quarterly average (%)</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>→ (avg / avg four quarters earlier − 1) × 100</t>
+        </is>
+      </c>
+      <c r="G32" s="16">
+        <f>(G21/C21-1)*100</f>
+        <v/>
+      </c>
+      <c r="H32" s="16">
+        <f>(H21/D21-1)*100</f>
+        <v/>
+      </c>
+      <c r="I32" s="16">
+        <f>(I21/E21-1)*100</f>
+        <v/>
+      </c>
+      <c r="J32" s="16">
+        <f>(J21/F21-1)*100</f>
+        <v/>
+      </c>
+      <c r="K32" s="16">
+        <f>(K21/G21-1)*100</f>
+        <v/>
+      </c>
+      <c r="L32" s="16">
+        <f>(L21/H21-1)*100</f>
+        <v/>
+      </c>
+      <c r="M32" s="16">
+        <f>(M21/I21-1)*100</f>
+        <v/>
+      </c>
+      <c r="N32" s="16">
+        <f>(N21/J21-1)*100</f>
+        <v/>
+      </c>
+      <c r="O32" s="16">
+        <f>(O21/K21-1)*100</f>
+        <v/>
+      </c>
+      <c r="P32" s="16">
+        <f>(P21/L21-1)*100</f>
+        <v/>
+      </c>
+      <c r="Q32" s="16">
+        <f>(Q21/M21-1)*100</f>
+        <v/>
+      </c>
+      <c r="R32" s="16">
+        <f>(R21/N21-1)*100</f>
+        <v/>
+      </c>
+      <c r="S32" s="16">
+        <f>(S21/O21-1)*100</f>
+        <v/>
+      </c>
+      <c r="T32" s="16">
+        <f>(T21/P21-1)*100</f>
+        <v/>
+      </c>
+      <c r="U32" s="16">
+        <f>(U21/Q21-1)*100</f>
+        <v/>
+      </c>
+      <c r="V32" s="16">
+        <f>(V21/R21-1)*100</f>
+        <v/>
+      </c>
+      <c r="W32" s="16">
+        <f>(W21/S21-1)*100</f>
+        <v/>
+      </c>
+      <c r="X32" s="16">
+        <f>(X21/T21-1)*100</f>
+        <v/>
+      </c>
+      <c r="Y32" s="16">
+        <f>(Y21/U21-1)*100</f>
+        <v/>
+      </c>
+      <c r="Z32" s="16">
+        <f>(Z21/V21-1)*100</f>
+        <v/>
+      </c>
+      <c r="AA32" s="16">
+        <f>(AA21/W21-1)*100</f>
+        <v/>
+      </c>
+      <c r="AB32" s="16">
+        <f>(AB21/X21-1)*100</f>
+        <v/>
+      </c>
+      <c r="AC32" s="16">
+        <f>(AC21/Y21-1)*100</f>
+        <v/>
+      </c>
+      <c r="AD32" s="16">
+        <f>(AD21/Z21-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Destination-currency basket weights κ (frozen judgement, 01b_basket_weights_used.csv; USD legs carry 0)</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>rows = region; columns C..K = EUR GBP BRL MXN JPY AUD KRW CAD INR; L = USD</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    κ na</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    κ emea</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    κ latam</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    κ apac</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    basket y/y, na (%)</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>→ Σ_currency κ × currency y/y</t>
+        </is>
+      </c>
+      <c r="G40" s="16">
+        <f>$F$35*G27+$J$35*G31</f>
+        <v/>
+      </c>
+      <c r="H40" s="16">
+        <f>$F$35*H27+$J$35*H31</f>
+        <v/>
+      </c>
+      <c r="I40" s="16">
+        <f>$F$35*I27+$J$35*I31</f>
+        <v/>
+      </c>
+      <c r="J40" s="16">
+        <f>$F$35*J27+$J$35*J31</f>
+        <v/>
+      </c>
+      <c r="K40" s="16">
+        <f>$F$35*K27+$J$35*K31</f>
+        <v/>
+      </c>
+      <c r="L40" s="16">
+        <f>$F$35*L27+$J$35*L31</f>
+        <v/>
+      </c>
+      <c r="M40" s="16">
+        <f>$F$35*M27+$J$35*M31</f>
+        <v/>
+      </c>
+      <c r="N40" s="16">
+        <f>$F$35*N27+$J$35*N31</f>
+        <v/>
+      </c>
+      <c r="O40" s="16">
+        <f>$F$35*O27+$J$35*O31</f>
+        <v/>
+      </c>
+      <c r="P40" s="16">
+        <f>$F$35*P27+$J$35*P31</f>
+        <v/>
+      </c>
+      <c r="Q40" s="16">
+        <f>$F$35*Q27+$J$35*Q31</f>
+        <v/>
+      </c>
+      <c r="R40" s="16">
+        <f>$F$35*R27+$J$35*R31</f>
+        <v/>
+      </c>
+      <c r="S40" s="16">
+        <f>$F$35*S27+$J$35*S31</f>
+        <v/>
+      </c>
+      <c r="T40" s="16">
+        <f>$F$35*T27+$J$35*T31</f>
+        <v/>
+      </c>
+      <c r="U40" s="16">
+        <f>$F$35*U27+$J$35*U31</f>
+        <v/>
+      </c>
+      <c r="V40" s="16">
+        <f>$F$35*V27+$J$35*V31</f>
+        <v/>
+      </c>
+      <c r="W40" s="16">
+        <f>$F$35*W27+$J$35*W31</f>
+        <v/>
+      </c>
+      <c r="X40" s="16">
+        <f>$F$35*X27+$J$35*X31</f>
+        <v/>
+      </c>
+      <c r="Y40" s="16">
+        <f>$F$35*Y27+$J$35*Y31</f>
+        <v/>
+      </c>
+      <c r="Z40" s="16">
+        <f>$F$35*Z27+$J$35*Z31</f>
+        <v/>
+      </c>
+      <c r="AA40" s="16">
+        <f>$F$35*AA27+$J$35*AA31</f>
+        <v/>
+      </c>
+      <c r="AB40" s="16">
+        <f>$F$35*AB27+$J$35*AB31</f>
+        <v/>
+      </c>
+      <c r="AC40" s="16">
+        <f>$F$35*AC27+$J$35*AC31</f>
+        <v/>
+      </c>
+      <c r="AD40" s="16">
+        <f>$F$35*AD27+$J$35*AD31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    basket y/y, emea (%)</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>→ Σ_currency κ × currency y/y</t>
+        </is>
+      </c>
+      <c r="G41" s="16">
+        <f>$C$36*G24+$D$36*G25</f>
+        <v/>
+      </c>
+      <c r="H41" s="16">
+        <f>$C$36*H24+$D$36*H25</f>
+        <v/>
+      </c>
+      <c r="I41" s="16">
+        <f>$C$36*I24+$D$36*I25</f>
+        <v/>
+      </c>
+      <c r="J41" s="16">
+        <f>$C$36*J24+$D$36*J25</f>
+        <v/>
+      </c>
+      <c r="K41" s="16">
+        <f>$C$36*K24+$D$36*K25</f>
+        <v/>
+      </c>
+      <c r="L41" s="16">
+        <f>$C$36*L24+$D$36*L25</f>
+        <v/>
+      </c>
+      <c r="M41" s="16">
+        <f>$C$36*M24+$D$36*M25</f>
+        <v/>
+      </c>
+      <c r="N41" s="16">
+        <f>$C$36*N24+$D$36*N25</f>
+        <v/>
+      </c>
+      <c r="O41" s="16">
+        <f>$C$36*O24+$D$36*O25</f>
+        <v/>
+      </c>
+      <c r="P41" s="16">
+        <f>$C$36*P24+$D$36*P25</f>
+        <v/>
+      </c>
+      <c r="Q41" s="16">
+        <f>$C$36*Q24+$D$36*Q25</f>
+        <v/>
+      </c>
+      <c r="R41" s="16">
+        <f>$C$36*R24+$D$36*R25</f>
+        <v/>
+      </c>
+      <c r="S41" s="16">
+        <f>$C$36*S24+$D$36*S25</f>
+        <v/>
+      </c>
+      <c r="T41" s="16">
+        <f>$C$36*T24+$D$36*T25</f>
+        <v/>
+      </c>
+      <c r="U41" s="16">
+        <f>$C$36*U24+$D$36*U25</f>
+        <v/>
+      </c>
+      <c r="V41" s="16">
+        <f>$C$36*V24+$D$36*V25</f>
+        <v/>
+      </c>
+      <c r="W41" s="16">
+        <f>$C$36*W24+$D$36*W25</f>
+        <v/>
+      </c>
+      <c r="X41" s="16">
+        <f>$C$36*X24+$D$36*X25</f>
+        <v/>
+      </c>
+      <c r="Y41" s="16">
+        <f>$C$36*Y24+$D$36*Y25</f>
+        <v/>
+      </c>
+      <c r="Z41" s="16">
+        <f>$C$36*Z24+$D$36*Z25</f>
+        <v/>
+      </c>
+      <c r="AA41" s="16">
+        <f>$C$36*AA24+$D$36*AA25</f>
+        <v/>
+      </c>
+      <c r="AB41" s="16">
+        <f>$C$36*AB24+$D$36*AB25</f>
+        <v/>
+      </c>
+      <c r="AC41" s="16">
+        <f>$C$36*AC24+$D$36*AC25</f>
+        <v/>
+      </c>
+      <c r="AD41" s="16">
+        <f>$C$36*AD24+$D$36*AD25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    basket y/y, latam (%)</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>→ Σ_currency κ × currency y/y</t>
+        </is>
+      </c>
+      <c r="G42" s="16">
+        <f>$E$37*G26+$F$37*G27</f>
+        <v/>
+      </c>
+      <c r="H42" s="16">
+        <f>$E$37*H26+$F$37*H27</f>
+        <v/>
+      </c>
+      <c r="I42" s="16">
+        <f>$E$37*I26+$F$37*I27</f>
+        <v/>
+      </c>
+      <c r="J42" s="16">
+        <f>$E$37*J26+$F$37*J27</f>
+        <v/>
+      </c>
+      <c r="K42" s="16">
+        <f>$E$37*K26+$F$37*K27</f>
+        <v/>
+      </c>
+      <c r="L42" s="16">
+        <f>$E$37*L26+$F$37*L27</f>
+        <v/>
+      </c>
+      <c r="M42" s="16">
+        <f>$E$37*M26+$F$37*M27</f>
+        <v/>
+      </c>
+      <c r="N42" s="16">
+        <f>$E$37*N26+$F$37*N27</f>
+        <v/>
+      </c>
+      <c r="O42" s="16">
+        <f>$E$37*O26+$F$37*O27</f>
+        <v/>
+      </c>
+      <c r="P42" s="16">
+        <f>$E$37*P26+$F$37*P27</f>
+        <v/>
+      </c>
+      <c r="Q42" s="16">
+        <f>$E$37*Q26+$F$37*Q27</f>
+        <v/>
+      </c>
+      <c r="R42" s="16">
+        <f>$E$37*R26+$F$37*R27</f>
+        <v/>
+      </c>
+      <c r="S42" s="16">
+        <f>$E$37*S26+$F$37*S27</f>
+        <v/>
+      </c>
+      <c r="T42" s="16">
+        <f>$E$37*T26+$F$37*T27</f>
+        <v/>
+      </c>
+      <c r="U42" s="16">
+        <f>$E$37*U26+$F$37*U27</f>
+        <v/>
+      </c>
+      <c r="V42" s="16">
+        <f>$E$37*V26+$F$37*V27</f>
+        <v/>
+      </c>
+      <c r="W42" s="16">
+        <f>$E$37*W26+$F$37*W27</f>
+        <v/>
+      </c>
+      <c r="X42" s="16">
+        <f>$E$37*X26+$F$37*X27</f>
+        <v/>
+      </c>
+      <c r="Y42" s="16">
+        <f>$E$37*Y26+$F$37*Y27</f>
+        <v/>
+      </c>
+      <c r="Z42" s="16">
+        <f>$E$37*Z26+$F$37*Z27</f>
+        <v/>
+      </c>
+      <c r="AA42" s="16">
+        <f>$E$37*AA26+$F$37*AA27</f>
+        <v/>
+      </c>
+      <c r="AB42" s="16">
+        <f>$E$37*AB26+$F$37*AB27</f>
+        <v/>
+      </c>
+      <c r="AC42" s="16">
+        <f>$E$37*AC26+$F$37*AC27</f>
+        <v/>
+      </c>
+      <c r="AD42" s="16">
+        <f>$E$37*AD26+$F$37*AD27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    basket y/y, apac (%)</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>→ Σ_currency κ × currency y/y</t>
+        </is>
+      </c>
+      <c r="G43" s="16">
+        <f>$G$38*G28+$H$38*G29+$I$38*G30+$K$38*G32</f>
+        <v/>
+      </c>
+      <c r="H43" s="16">
+        <f>$G$38*H28+$H$38*H29+$I$38*H30+$K$38*H32</f>
+        <v/>
+      </c>
+      <c r="I43" s="16">
+        <f>$G$38*I28+$H$38*I29+$I$38*I30+$K$38*I32</f>
+        <v/>
+      </c>
+      <c r="J43" s="16">
+        <f>$G$38*J28+$H$38*J29+$I$38*J30+$K$38*J32</f>
+        <v/>
+      </c>
+      <c r="K43" s="16">
+        <f>$G$38*K28+$H$38*K29+$I$38*K30+$K$38*K32</f>
+        <v/>
+      </c>
+      <c r="L43" s="16">
+        <f>$G$38*L28+$H$38*L29+$I$38*L30+$K$38*L32</f>
+        <v/>
+      </c>
+      <c r="M43" s="16">
+        <f>$G$38*M28+$H$38*M29+$I$38*M30+$K$38*M32</f>
+        <v/>
+      </c>
+      <c r="N43" s="16">
+        <f>$G$38*N28+$H$38*N29+$I$38*N30+$K$38*N32</f>
+        <v/>
+      </c>
+      <c r="O43" s="16">
+        <f>$G$38*O28+$H$38*O29+$I$38*O30+$K$38*O32</f>
+        <v/>
+      </c>
+      <c r="P43" s="16">
+        <f>$G$38*P28+$H$38*P29+$I$38*P30+$K$38*P32</f>
+        <v/>
+      </c>
+      <c r="Q43" s="16">
+        <f>$G$38*Q28+$H$38*Q29+$I$38*Q30+$K$38*Q32</f>
+        <v/>
+      </c>
+      <c r="R43" s="16">
+        <f>$G$38*R28+$H$38*R29+$I$38*R30+$K$38*R32</f>
+        <v/>
+      </c>
+      <c r="S43" s="16">
+        <f>$G$38*S28+$H$38*S29+$I$38*S30+$K$38*S32</f>
+        <v/>
+      </c>
+      <c r="T43" s="16">
+        <f>$G$38*T28+$H$38*T29+$I$38*T30+$K$38*T32</f>
+        <v/>
+      </c>
+      <c r="U43" s="16">
+        <f>$G$38*U28+$H$38*U29+$I$38*U30+$K$38*U32</f>
+        <v/>
+      </c>
+      <c r="V43" s="16">
+        <f>$G$38*V28+$H$38*V29+$I$38*V30+$K$38*V32</f>
+        <v/>
+      </c>
+      <c r="W43" s="16">
+        <f>$G$38*W28+$H$38*W29+$I$38*W30+$K$38*W32</f>
+        <v/>
+      </c>
+      <c r="X43" s="16">
+        <f>$G$38*X28+$H$38*X29+$I$38*X30+$K$38*X32</f>
+        <v/>
+      </c>
+      <c r="Y43" s="16">
+        <f>$G$38*Y28+$H$38*Y29+$I$38*Y30+$K$38*Y32</f>
+        <v/>
+      </c>
+      <c r="Z43" s="16">
+        <f>$G$38*Z28+$H$38*Z29+$I$38*Z30+$K$38*Z32</f>
+        <v/>
+      </c>
+      <c r="AA43" s="16">
+        <f>$G$38*AA28+$H$38*AA29+$I$38*AA30+$K$38*AA32</f>
+        <v/>
+      </c>
+      <c r="AB43" s="16">
+        <f>$G$38*AB28+$H$38*AB29+$I$38*AB30+$K$38*AB32</f>
+        <v/>
+      </c>
+      <c r="AC43" s="16">
+        <f>$G$38*AC28+$H$38*AC29+$I$38*AC30+$K$38*AC32</f>
+        <v/>
+      </c>
+      <c r="AD43" s="16">
+        <f>$G$38*AD28+$H$38*AD29+$I$38*AD30+$K$38*AD32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Regional GBV shares (10-K Geographic Mix, latest fiscal year filed before the quarter's print; FY2025 forward)</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>data/processed/adr/01_regional_annual.csv gbv_share_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GBV share, na</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="n">
+        <v>0.5511133243224016</v>
+      </c>
+      <c r="D45" s="26" t="n">
+        <v>0.5511133243224016</v>
+      </c>
+      <c r="E45" s="26" t="n">
+        <v>0.5511133243224016</v>
+      </c>
+      <c r="F45" s="26" t="n">
+        <v>0.5511133243224016</v>
+      </c>
+      <c r="G45" s="26" t="n">
+        <v>0.5398276340209485</v>
+      </c>
+      <c r="H45" s="26" t="n">
+        <v>0.5398276340209485</v>
+      </c>
+      <c r="I45" s="26" t="n">
+        <v>0.5398276340209485</v>
+      </c>
+      <c r="J45" s="26" t="n">
+        <v>0.5398276340209485</v>
+      </c>
+      <c r="K45" s="26" t="n">
+        <v>0.5101246598747073</v>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>0.5101246598747073</v>
+      </c>
+      <c r="M45" s="26" t="n">
+        <v>0.5101246598747073</v>
+      </c>
+      <c r="N45" s="26" t="n">
+        <v>0.5101246598747073</v>
+      </c>
+      <c r="O45" s="26" t="n">
+        <v>0.4769972150931033</v>
+      </c>
+      <c r="P45" s="26" t="n">
+        <v>0.4769972150931033</v>
+      </c>
+      <c r="Q45" s="26" t="n">
+        <v>0.4769972150931033</v>
+      </c>
+      <c r="R45" s="26" t="n">
+        <v>0.4769972150931033</v>
+      </c>
+      <c r="S45" s="26" t="n">
+        <v>0.4623887312921843</v>
+      </c>
+      <c r="T45" s="26" t="n">
+        <v>0.4623887312921843</v>
+      </c>
+      <c r="U45" s="26" t="n">
+        <v>0.4623887312921843</v>
+      </c>
+      <c r="V45" s="26" t="n">
+        <v>0.4623887312921843</v>
+      </c>
+      <c r="W45" s="26" t="n">
+        <v>0.4414777645086718</v>
+      </c>
+      <c r="X45" s="26" t="n">
+        <v>0.4414777645086718</v>
+      </c>
+      <c r="Y45" s="26" t="n">
+        <v>0.4414777645086718</v>
+      </c>
+      <c r="Z45" s="26" t="n">
+        <v>0.4414777645086718</v>
+      </c>
+      <c r="AA45" s="26" t="n">
+        <v>0.4414777645086718</v>
+      </c>
+      <c r="AB45" s="26" t="n">
+        <v>0.4414777645086718</v>
+      </c>
+      <c r="AC45" s="26" t="n">
+        <v>0.4414777645086718</v>
+      </c>
+      <c r="AD45" s="26" t="n">
+        <v>0.4414777645086718</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GBV share, emea</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>0.2787014215232938</v>
+      </c>
+      <c r="D46" s="26" t="n">
+        <v>0.2787014215232938</v>
+      </c>
+      <c r="E46" s="26" t="n">
+        <v>0.2787014215232938</v>
+      </c>
+      <c r="F46" s="26" t="n">
+        <v>0.2787014215232938</v>
+      </c>
+      <c r="G46" s="26" t="n">
+        <v>0.3116005717089404</v>
+      </c>
+      <c r="H46" s="26" t="n">
+        <v>0.3116005717089404</v>
+      </c>
+      <c r="I46" s="26" t="n">
+        <v>0.3116005717089404</v>
+      </c>
+      <c r="J46" s="26" t="n">
+        <v>0.3116005717089404</v>
+      </c>
+      <c r="K46" s="26" t="n">
+        <v>0.3399038157311903</v>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>0.3399038157311903</v>
+      </c>
+      <c r="M46" s="26" t="n">
+        <v>0.3399038157311903</v>
+      </c>
+      <c r="N46" s="26" t="n">
+        <v>0.3399038157311903</v>
+      </c>
+      <c r="O46" s="26" t="n">
+        <v>0.3582291268497789</v>
+      </c>
+      <c r="P46" s="26" t="n">
+        <v>0.3582291268497789</v>
+      </c>
+      <c r="Q46" s="26" t="n">
+        <v>0.3582291268497789</v>
+      </c>
+      <c r="R46" s="26" t="n">
+        <v>0.3582291268497789</v>
+      </c>
+      <c r="S46" s="26" t="n">
+        <v>0.3637630832436662</v>
+      </c>
+      <c r="T46" s="26" t="n">
+        <v>0.3637630832436662</v>
+      </c>
+      <c r="U46" s="26" t="n">
+        <v>0.3637630832436662</v>
+      </c>
+      <c r="V46" s="26" t="n">
+        <v>0.3637630832436662</v>
+      </c>
+      <c r="W46" s="26" t="n">
+        <v>0.3742837421800533</v>
+      </c>
+      <c r="X46" s="26" t="n">
+        <v>0.3742837421800533</v>
+      </c>
+      <c r="Y46" s="26" t="n">
+        <v>0.3742837421800533</v>
+      </c>
+      <c r="Z46" s="26" t="n">
+        <v>0.3742837421800533</v>
+      </c>
+      <c r="AA46" s="26" t="n">
+        <v>0.3742837421800533</v>
+      </c>
+      <c r="AB46" s="26" t="n">
+        <v>0.3742837421800533</v>
+      </c>
+      <c r="AC46" s="26" t="n">
+        <v>0.3742837421800533</v>
+      </c>
+      <c r="AD46" s="26" t="n">
+        <v>0.3742837421800533</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GBV share, latam</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>0.07117241148433479</v>
+      </c>
+      <c r="D47" s="26" t="n">
+        <v>0.07117241148433479</v>
+      </c>
+      <c r="E47" s="26" t="n">
+        <v>0.07117241148433479</v>
+      </c>
+      <c r="F47" s="26" t="n">
+        <v>0.07117241148433479</v>
+      </c>
+      <c r="G47" s="26" t="n">
+        <v>0.0790579601936984</v>
+      </c>
+      <c r="H47" s="26" t="n">
+        <v>0.0790579601936984</v>
+      </c>
+      <c r="I47" s="26" t="n">
+        <v>0.0790579601936984</v>
+      </c>
+      <c r="J47" s="26" t="n">
+        <v>0.0790579601936984</v>
+      </c>
+      <c r="K47" s="26" t="n">
+        <v>0.07653610074036575</v>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>0.07653610074036575</v>
+      </c>
+      <c r="M47" s="26" t="n">
+        <v>0.07653610074036575</v>
+      </c>
+      <c r="N47" s="26" t="n">
+        <v>0.07653610074036575</v>
+      </c>
+      <c r="O47" s="26" t="n">
+        <v>0.08264620761207885</v>
+      </c>
+      <c r="P47" s="26" t="n">
+        <v>0.08264620761207885</v>
+      </c>
+      <c r="Q47" s="26" t="n">
+        <v>0.08264620761207885</v>
+      </c>
+      <c r="R47" s="26" t="n">
+        <v>0.08264620761207885</v>
+      </c>
+      <c r="S47" s="26" t="n">
+        <v>0.08671622811307834</v>
+      </c>
+      <c r="T47" s="26" t="n">
+        <v>0.08671622811307834</v>
+      </c>
+      <c r="U47" s="26" t="n">
+        <v>0.08671622811307834</v>
+      </c>
+      <c r="V47" s="26" t="n">
+        <v>0.08671622811307834</v>
+      </c>
+      <c r="W47" s="26" t="n">
+        <v>0.09358736975885533</v>
+      </c>
+      <c r="X47" s="26" t="n">
+        <v>0.09358736975885533</v>
+      </c>
+      <c r="Y47" s="26" t="n">
+        <v>0.09358736975885533</v>
+      </c>
+      <c r="Z47" s="26" t="n">
+        <v>0.09358736975885533</v>
+      </c>
+      <c r="AA47" s="26" t="n">
+        <v>0.09358736975885533</v>
+      </c>
+      <c r="AB47" s="26" t="n">
+        <v>0.09358736975885533</v>
+      </c>
+      <c r="AC47" s="26" t="n">
+        <v>0.09358736975885533</v>
+      </c>
+      <c r="AD47" s="26" t="n">
+        <v>0.09358736975885533</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GBV share, apac</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="n">
+        <v>0.09901284266996974</v>
+      </c>
+      <c r="D48" s="26" t="n">
+        <v>0.09901284266996974</v>
+      </c>
+      <c r="E48" s="26" t="n">
+        <v>0.09901284266996974</v>
+      </c>
+      <c r="F48" s="26" t="n">
+        <v>0.09901284266996974</v>
+      </c>
+      <c r="G48" s="26" t="n">
+        <v>0.06951383407641275</v>
+      </c>
+      <c r="H48" s="26" t="n">
+        <v>0.06951383407641275</v>
+      </c>
+      <c r="I48" s="26" t="n">
+        <v>0.06951383407641275</v>
+      </c>
+      <c r="J48" s="26" t="n">
+        <v>0.06951383407641275</v>
+      </c>
+      <c r="K48" s="26" t="n">
+        <v>0.07343542365373663</v>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>0.07343542365373663</v>
+      </c>
+      <c r="M48" s="26" t="n">
+        <v>0.07343542365373663</v>
+      </c>
+      <c r="N48" s="26" t="n">
+        <v>0.07343542365373663</v>
+      </c>
+      <c r="O48" s="26" t="n">
+        <v>0.08212745044503905</v>
+      </c>
+      <c r="P48" s="26" t="n">
+        <v>0.08212745044503905</v>
+      </c>
+      <c r="Q48" s="26" t="n">
+        <v>0.08212745044503905</v>
+      </c>
+      <c r="R48" s="26" t="n">
+        <v>0.08212745044503905</v>
+      </c>
+      <c r="S48" s="26" t="n">
+        <v>0.08713195735107111</v>
+      </c>
+      <c r="T48" s="26" t="n">
+        <v>0.08713195735107111</v>
+      </c>
+      <c r="U48" s="26" t="n">
+        <v>0.08713195735107111</v>
+      </c>
+      <c r="V48" s="26" t="n">
+        <v>0.08713195735107111</v>
+      </c>
+      <c r="W48" s="26" t="n">
+        <v>0.09065112355241968</v>
+      </c>
+      <c r="X48" s="26" t="n">
+        <v>0.09065112355241968</v>
+      </c>
+      <c r="Y48" s="26" t="n">
+        <v>0.09065112355241968</v>
+      </c>
+      <c r="Z48" s="26" t="n">
+        <v>0.09065112355241968</v>
+      </c>
+      <c r="AA48" s="26" t="n">
+        <v>0.09065112355241968</v>
+      </c>
+      <c r="AB48" s="26" t="n">
+        <v>0.09065112355241968</v>
+      </c>
+      <c r="AC48" s="26" t="n">
+        <v>0.09065112355241968</v>
+      </c>
+      <c r="AD48" s="26" t="n">
+        <v>0.09065112355241968</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    fiscal year of the shares used</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D49" s="23" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E49" s="23" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F49" s="23" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G49" s="23" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H49" s="23" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I49" s="23" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J49" s="23" t="n">
+        <v>2021</v>
+      </c>
+      <c r="K49" s="23" t="n">
+        <v>2022</v>
+      </c>
+      <c r="L49" s="23" t="n">
+        <v>2022</v>
+      </c>
+      <c r="M49" s="23" t="n">
+        <v>2022</v>
+      </c>
+      <c r="N49" s="23" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O49" s="23" t="n">
+        <v>2023</v>
+      </c>
+      <c r="P49" s="23" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q49" s="23" t="n">
+        <v>2023</v>
+      </c>
+      <c r="R49" s="23" t="n">
+        <v>2023</v>
+      </c>
+      <c r="S49" s="23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="T49" s="23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="U49" s="23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="V49" s="23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W49" s="23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="X49" s="23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Y49" s="23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z49" s="23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA49" s="23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AB49" s="23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AC49" s="23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AD49" s="23" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>FX effect on ADR — translation identity (pp)</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>→ SUMPRODUCT(GBV shares, regional basket y/y); the promoted leg (pre-registration §5, V0)</t>
+        </is>
+      </c>
+      <c r="G51" s="16">
+        <f>SUMPRODUCT(G45:G48,G40:G43)</f>
+        <v/>
+      </c>
+      <c r="H51" s="16">
+        <f>SUMPRODUCT(H45:H48,H40:H43)</f>
+        <v/>
+      </c>
+      <c r="I51" s="16">
+        <f>SUMPRODUCT(I45:I48,I40:I43)</f>
+        <v/>
+      </c>
+      <c r="J51" s="16">
+        <f>SUMPRODUCT(J45:J48,J40:J43)</f>
+        <v/>
+      </c>
+      <c r="K51" s="16">
+        <f>SUMPRODUCT(K45:K48,K40:K43)</f>
+        <v/>
+      </c>
+      <c r="L51" s="16">
+        <f>SUMPRODUCT(L45:L48,L40:L43)</f>
+        <v/>
+      </c>
+      <c r="M51" s="16">
+        <f>SUMPRODUCT(M45:M48,M40:M43)</f>
+        <v/>
+      </c>
+      <c r="N51" s="16">
+        <f>SUMPRODUCT(N45:N48,N40:N43)</f>
+        <v/>
+      </c>
+      <c r="O51" s="16">
+        <f>SUMPRODUCT(O45:O48,O40:O43)</f>
+        <v/>
+      </c>
+      <c r="P51" s="16">
+        <f>SUMPRODUCT(P45:P48,P40:P43)</f>
+        <v/>
+      </c>
+      <c r="Q51" s="16">
+        <f>SUMPRODUCT(Q45:Q48,Q40:Q43)</f>
+        <v/>
+      </c>
+      <c r="R51" s="16">
+        <f>SUMPRODUCT(R45:R48,R40:R43)</f>
+        <v/>
+      </c>
+      <c r="S51" s="16">
+        <f>SUMPRODUCT(S45:S48,S40:S43)</f>
+        <v/>
+      </c>
+      <c r="T51" s="16">
+        <f>SUMPRODUCT(T45:T48,T40:T43)</f>
+        <v/>
+      </c>
+      <c r="U51" s="16">
+        <f>SUMPRODUCT(U45:U48,U40:U43)</f>
+        <v/>
+      </c>
+      <c r="V51" s="16">
+        <f>SUMPRODUCT(V45:V48,V40:V43)</f>
+        <v/>
+      </c>
+      <c r="W51" s="16">
+        <f>SUMPRODUCT(W45:W48,W40:W43)</f>
+        <v/>
+      </c>
+      <c r="X51" s="16">
+        <f>SUMPRODUCT(X45:X48,X40:X43)</f>
+        <v/>
+      </c>
+      <c r="Y51" s="14">
+        <f>SUMPRODUCT(Y45:Y48,Y40:Y43)</f>
+        <v/>
+      </c>
+      <c r="Z51" s="14">
+        <f>SUMPRODUCT(Z45:Z48,Z40:Z43)</f>
+        <v/>
+      </c>
+      <c r="AA51" s="14">
+        <f>SUMPRODUCT(AA45:AA48,AA40:AA43)</f>
+        <v/>
+      </c>
+      <c r="AB51" s="14">
+        <f>SUMPRODUCT(AB45:AB48,AB40:AB43)</f>
+        <v/>
+      </c>
+      <c r="AC51" s="14">
+        <f>SUMPRODUCT(AC45:AC48,AC40:AC43)</f>
+        <v/>
+      </c>
+      <c r="AD51" s="14">
+        <f>SUMPRODUCT(AD45:AD48,AD40:AD43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    error: identity − disclosed (pp), completed quarters</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>→ identity − row 10</t>
+        </is>
+      </c>
+      <c r="I52" s="16">
+        <f>I51-I10</f>
+        <v/>
+      </c>
+      <c r="J52" s="16">
+        <f>J51-J10</f>
+        <v/>
+      </c>
+      <c r="K52" s="16">
+        <f>K51-K10</f>
+        <v/>
+      </c>
+      <c r="L52" s="16">
+        <f>L51-L10</f>
+        <v/>
+      </c>
+      <c r="M52" s="16">
+        <f>M51-M10</f>
+        <v/>
+      </c>
+      <c r="N52" s="16">
+        <f>N51-N10</f>
+        <v/>
+      </c>
+      <c r="O52" s="16">
+        <f>O51-O10</f>
+        <v/>
+      </c>
+      <c r="P52" s="16">
+        <f>P51-P10</f>
+        <v/>
+      </c>
+      <c r="Q52" s="16">
+        <f>Q51-Q10</f>
+        <v/>
+      </c>
+      <c r="R52" s="16">
+        <f>R51-R10</f>
+        <v/>
+      </c>
+      <c r="S52" s="16">
+        <f>S51-S10</f>
+        <v/>
+      </c>
+      <c r="T52" s="16">
+        <f>T51-T10</f>
+        <v/>
+      </c>
+      <c r="U52" s="16">
+        <f>U51-U10</f>
+        <v/>
+      </c>
+      <c r="V52" s="16">
+        <f>V51-V10</f>
+        <v/>
+      </c>
+      <c r="W52" s="16">
+        <f>W51-W10</f>
+        <v/>
+      </c>
+      <c r="X52" s="16">
+        <f>X51-X10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    naive error: last quarter's disclosed − disclosed (pp)</t>
+        </is>
+      </c>
+      <c r="I53" s="16">
+        <f>H10-I10</f>
+        <v/>
+      </c>
+      <c r="J53" s="16">
+        <f>I10-J10</f>
+        <v/>
+      </c>
+      <c r="K53" s="16">
+        <f>J10-K10</f>
+        <v/>
+      </c>
+      <c r="L53" s="16">
+        <f>K10-L10</f>
+        <v/>
+      </c>
+      <c r="M53" s="16">
+        <f>L10-M10</f>
+        <v/>
+      </c>
+      <c r="N53" s="16">
+        <f>M10-N10</f>
+        <v/>
+      </c>
+      <c r="O53" s="16">
+        <f>N10-O10</f>
+        <v/>
+      </c>
+      <c r="P53" s="16">
+        <f>O10-P10</f>
+        <v/>
+      </c>
+      <c r="Q53" s="16">
+        <f>P10-Q10</f>
+        <v/>
+      </c>
+      <c r="R53" s="16">
+        <f>Q10-R10</f>
+        <v/>
+      </c>
+      <c r="S53" s="16">
+        <f>R10-S10</f>
+        <v/>
+      </c>
+      <c r="T53" s="16">
+        <f>S10-T10</f>
+        <v/>
+      </c>
+      <c r="U53" s="16">
+        <f>T10-U10</f>
+        <v/>
+      </c>
+      <c r="V53" s="16">
+        <f>U10-V10</f>
+        <v/>
+      </c>
+      <c r="W53" s="16">
+        <f>V10-W10</f>
+        <v/>
+      </c>
+      <c r="X53" s="16">
+        <f>W10-X10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RMSE identity / RMSE naive, 1Q23–2Q26 (n 14; full-quarter rates = origin O3)</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>→ SQRT(SUMSQ)/n; point-in-time O1/O2 ratios are in block E</t>
+        </is>
+      </c>
+      <c r="C54" s="16">
+        <f>SQRT(SUMSQ(K52:X52)/14)</f>
+        <v/>
+      </c>
+      <c r="D54" s="16">
+        <f>SQRT(SUMSQ(K53:X53)/14)</f>
+        <v/>
+      </c>
+      <c r="E54" s="14">
+        <f>C54/D54</f>
+        <v/>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>ratio (pass line ≤ 0.75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    P10 of the ex-ante band (pp)</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>engine: moving-block bootstrap of daily FX returns on the unobserved days, 4,000 paths</t>
+        </is>
+      </c>
+      <c r="Y56" s="11" t="n">
+        <v>0.3554832912187216</v>
+      </c>
+      <c r="Z56" s="11" t="n">
+        <v>-1.056443106322889</v>
+      </c>
+      <c r="AA56" s="11" t="n">
+        <v>-3.200007379665376</v>
+      </c>
+      <c r="AB56" s="11" t="n">
+        <v>-3.901622399508339</v>
+      </c>
+      <c r="AC56" s="11" t="n">
+        <v>-4.338399164474799</v>
+      </c>
+      <c r="AD56" s="11" t="n">
+        <v>-4.335432026064073</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    P50</t>
+        </is>
+      </c>
+      <c r="Y57" s="11" t="n">
+        <v>0.4162724067598822</v>
+      </c>
+      <c r="Z57" s="11" t="n">
+        <v>0.5819984442006085</v>
+      </c>
+      <c r="AA57" s="11" t="n">
+        <v>-0.2358180743680651</v>
+      </c>
+      <c r="AB57" s="11" t="n">
+        <v>-0.2273049348370149</v>
+      </c>
+      <c r="AC57" s="11" t="n">
+        <v>0.0305520770005595</v>
+      </c>
+      <c r="AD57" s="11" t="n">
+        <v>0.2339589346106644</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    P90</t>
+        </is>
+      </c>
+      <c r="Y58" s="11" t="n">
+        <v>0.4805092671220062</v>
+      </c>
+      <c r="Z58" s="11" t="n">
+        <v>2.259472345394851</v>
+      </c>
+      <c r="AA58" s="11" t="n">
+        <v>2.777955631158125</v>
+      </c>
+      <c r="AB58" s="11" t="n">
+        <v>3.680185402603735</v>
+      </c>
+      <c r="AC58" s="11" t="n">
+        <v>4.855838910725363</v>
+      </c>
+      <c r="AD58" s="11" t="n">
+        <v>5.115411667119529</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>C. Ex-FX ADR mechanism: ex-FX y/y = core + bundle (laps on filed dates) + geo mix (from the nights line) + unit size + LOS + seats + interaction</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
+      <c r="Q60" s="5" t="n"/>
+      <c r="R60" s="5" t="n"/>
+      <c r="S60" s="5" t="n"/>
+      <c r="T60" s="5" t="n"/>
+      <c r="U60" s="5" t="n"/>
+      <c r="V60" s="5" t="n"/>
+      <c r="W60" s="5" t="n"/>
+      <c r="X60" s="5" t="n"/>
+      <c r="Y60" s="5" t="n"/>
+      <c r="Z60" s="5" t="n"/>
+      <c r="AA60" s="5" t="n"/>
+      <c r="AB60" s="5" t="n"/>
+      <c r="AC60" s="5" t="n"/>
+      <c r="AD60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Disclosed ex-FX ADR y/y (pp)</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>→ link to row 9</t>
+        </is>
+      </c>
+      <c r="K61" s="20">
+        <f>K9</f>
+        <v/>
+      </c>
+      <c r="L61" s="20">
+        <f>L9</f>
+        <v/>
+      </c>
+      <c r="M61" s="20">
+        <f>M9</f>
+        <v/>
+      </c>
+      <c r="N61" s="20">
+        <f>N9</f>
+        <v/>
+      </c>
+      <c r="O61" s="20">
+        <f>O9</f>
+        <v/>
+      </c>
+      <c r="P61" s="20">
+        <f>P9</f>
+        <v/>
+      </c>
+      <c r="Q61" s="20">
+        <f>Q9</f>
+        <v/>
+      </c>
+      <c r="R61" s="20">
+        <f>R9</f>
+        <v/>
+      </c>
+      <c r="S61" s="20">
+        <f>S9</f>
+        <v/>
+      </c>
+      <c r="T61" s="20">
+        <f>T9</f>
+        <v/>
+      </c>
+      <c r="U61" s="20">
+        <f>U9</f>
+        <v/>
+      </c>
+      <c r="V61" s="20">
+        <f>V9</f>
+        <v/>
+      </c>
+      <c r="W61" s="20">
+        <f>W9</f>
+        <v/>
+      </c>
+      <c r="X61" s="20">
+        <f>X9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    geographic mix (pp)</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>history: H decomposition adr_history_components.csv; forward: block C1 arithmetic on the nights line's regional path</t>
+        </is>
+      </c>
+      <c r="K62" s="12" t="n">
+        <v>-1.351797894609108</v>
+      </c>
+      <c r="L62" s="12" t="n">
+        <v>-0.9030804532740522</v>
+      </c>
+      <c r="M62" s="12" t="n">
+        <v>-1.167207984169072</v>
+      </c>
+      <c r="N62" s="12" t="n">
+        <v>-0.939076865441546</v>
+      </c>
+      <c r="O62" s="12" t="n">
+        <v>-1.325072509344749</v>
+      </c>
+      <c r="P62" s="12" t="n">
+        <v>-1.131644617522953</v>
+      </c>
+      <c r="Q62" s="12" t="n">
+        <v>-1.119615766385351</v>
+      </c>
+      <c r="R62" s="12" t="n">
+        <v>-1.791887454358232</v>
+      </c>
+      <c r="S62" s="12" t="n">
+        <v>-1.89435030033076</v>
+      </c>
+      <c r="T62" s="12" t="n">
+        <v>-1.701590426211275</v>
+      </c>
+      <c r="U62" s="12" t="n">
+        <v>-1.593234059968984</v>
+      </c>
+      <c r="V62" s="12" t="n">
+        <v>-1.457397157766538</v>
+      </c>
+      <c r="W62" s="12" t="n">
+        <v>-1.043067743533466</v>
+      </c>
+      <c r="X62" s="12" t="n">
+        <v>-1.267224393230371</v>
+      </c>
+      <c r="Y62" s="18">
+        <f>Y91</f>
+        <v/>
+      </c>
+      <c r="Z62" s="18">
+        <f>Z91</f>
+        <v/>
+      </c>
+      <c r="AA62" s="18">
+        <f>AA91</f>
+        <v/>
+      </c>
+      <c r="AB62" s="18">
+        <f>AB91</f>
+        <v/>
+      </c>
+      <c r="AC62" s="18">
+        <f>AC91</f>
+        <v/>
+      </c>
+      <c r="AD62" s="18">
+        <f>AD91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    unit size / party size (pp)</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>history: H; forward: card v3 measured 3Q26 term +0.797 carried (I_mix_terms_3q26.csv)</t>
+        </is>
+      </c>
+      <c r="K63" s="12" t="n">
+        <v>0.4620912842772667</v>
+      </c>
+      <c r="L63" s="12" t="n">
+        <v>0.3621440282039081</v>
+      </c>
+      <c r="M63" s="12" t="n">
+        <v>0.4098973686879872</v>
+      </c>
+      <c r="N63" s="12" t="n">
+        <v>0.2906539573280417</v>
+      </c>
+      <c r="O63" s="12" t="n">
+        <v>0.9633505413705318</v>
+      </c>
+      <c r="P63" s="12" t="n">
+        <v>0.7721595803184097</v>
+      </c>
+      <c r="Q63" s="12" t="n">
+        <v>0.8903157468661863</v>
+      </c>
+      <c r="R63" s="12" t="n">
+        <v>0.7066747659259102</v>
+      </c>
+      <c r="S63" s="12" t="n">
+        <v>0.6690991824547088</v>
+      </c>
+      <c r="T63" s="12" t="n">
+        <v>0.7324103132323075</v>
+      </c>
+      <c r="U63" s="12" t="n">
+        <v>0.7481509563315145</v>
+      </c>
+      <c r="V63" s="12" t="n">
+        <v>0.8224227396698655</v>
+      </c>
+      <c r="W63" s="12" t="n">
+        <v>0.9450489445563696</v>
+      </c>
+      <c r="X63" s="12" t="n">
+        <v>0.7004681684496338</v>
+      </c>
+      <c r="Y63" s="12" t="n">
+        <v>0.796672</v>
+      </c>
+      <c r="Z63" s="12" t="n">
+        <v>0.796672</v>
+      </c>
+      <c r="AA63" s="12" t="n">
+        <v>0.796672</v>
+      </c>
+      <c r="AB63" s="12" t="n">
+        <v>0.796672</v>
+      </c>
+      <c r="AC63" s="12" t="n">
+        <v>0.796672</v>
+      </c>
+      <c r="AD63" s="12" t="n">
+        <v>0.796672</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    length-of-stay mix (pp)</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>history: H; forward: card +0.056 carried</t>
+        </is>
+      </c>
+      <c r="K64" s="12" t="n">
+        <v>0.4626252943505493</v>
+      </c>
+      <c r="L64" s="12" t="n">
+        <v>0.1183751453729842</v>
+      </c>
+      <c r="M64" s="12" t="n">
+        <v>0.3015954388247532</v>
+      </c>
+      <c r="N64" s="12" t="n">
+        <v>0.3639387380400816</v>
+      </c>
+      <c r="O64" s="12" t="n">
+        <v>0.2125302124850181</v>
+      </c>
+      <c r="P64" s="12" t="n">
+        <v>0.2316928734386047</v>
+      </c>
+      <c r="Q64" s="12" t="n">
+        <v>0.2526948668717388</v>
+      </c>
+      <c r="R64" s="12" t="n">
+        <v>0.4315510396297295</v>
+      </c>
+      <c r="S64" s="12" t="n">
+        <v>0.2787347156817832</v>
+      </c>
+      <c r="T64" s="12" t="n">
+        <v>0.3484146139979049</v>
+      </c>
+      <c r="U64" s="12" t="n">
+        <v>0.3076491557727268</v>
+      </c>
+      <c r="V64" s="12" t="n">
+        <v>0.2210184783094426</v>
+      </c>
+      <c r="W64" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X64" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y64" s="12" t="n">
+        <v>0.056264</v>
+      </c>
+      <c r="Z64" s="12" t="n">
+        <v>0.056264</v>
+      </c>
+      <c r="AA64" s="12" t="n">
+        <v>0.056264</v>
+      </c>
+      <c r="AB64" s="12" t="n">
+        <v>0.056264</v>
+      </c>
+      <c r="AC64" s="12" t="n">
+        <v>0.056264</v>
+      </c>
+      <c r="AD64" s="12" t="n">
+        <v>0.056264</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    seats / new business dilution (pp)</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>history: H 15_seats_dilution; forward: −0.483 (2026), −0.565 (2027), assumed</t>
+        </is>
+      </c>
+      <c r="K65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="12" t="n">
+        <v>-0.1765366347734276</v>
+      </c>
+      <c r="T65" s="12" t="n">
+        <v>-0.1765366347734276</v>
+      </c>
+      <c r="U65" s="12" t="n">
+        <v>-0.1765366347734276</v>
+      </c>
+      <c r="V65" s="12" t="n">
+        <v>-0.1765366347734276</v>
+      </c>
+      <c r="W65" s="12" t="n">
+        <v>-0.4825701517057523</v>
+      </c>
+      <c r="X65" s="12" t="n">
+        <v>-0.4825701517057523</v>
+      </c>
+      <c r="Y65" s="12" t="n">
+        <v>-0.48257</v>
+      </c>
+      <c r="Z65" s="12" t="n">
+        <v>-0.48257</v>
+      </c>
+      <c r="AA65" s="12" t="n">
+        <v>-0.5649999999999999</v>
+      </c>
+      <c r="AB65" s="12" t="n">
+        <v>-0.5649999999999999</v>
+      </c>
+      <c r="AC65" s="12" t="n">
+        <v>-0.5649999999999999</v>
+      </c>
+      <c r="AD65" s="12" t="n">
+        <v>-0.5649999999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    interaction (pp)</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>H, descriptive −0.10</t>
+        </is>
+      </c>
+      <c r="K66" s="12" t="n">
+        <v>-0.0494786368971566</v>
+      </c>
+      <c r="L66" s="12" t="n">
+        <v>-0.0494786368971566</v>
+      </c>
+      <c r="M66" s="12" t="n">
+        <v>-0.0494786368971566</v>
+      </c>
+      <c r="N66" s="12" t="n">
+        <v>-0.0494786368971566</v>
+      </c>
+      <c r="O66" s="12" t="n">
+        <v>-0.1065834527970392</v>
+      </c>
+      <c r="P66" s="12" t="n">
+        <v>-0.1065834527970392</v>
+      </c>
+      <c r="Q66" s="12" t="n">
+        <v>-0.1065834527970392</v>
+      </c>
+      <c r="R66" s="12" t="n">
+        <v>-0.1065834527970392</v>
+      </c>
+      <c r="S66" s="12" t="n">
+        <v>-0.1083206075608631</v>
+      </c>
+      <c r="T66" s="12" t="n">
+        <v>-0.1083206075608631</v>
+      </c>
+      <c r="U66" s="12" t="n">
+        <v>-0.1083206075608631</v>
+      </c>
+      <c r="V66" s="12" t="n">
+        <v>-0.1083206075608631</v>
+      </c>
+      <c r="W66" s="12" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="X66" s="12" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="Y66" s="12" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="Z66" s="12" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AA66" s="12" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AB66" s="12" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC66" s="12" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AD66" s="12" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    like-for-like residual (pp) = ex-FX − the five terms above</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>history: formula; forward: core + bundle</t>
+        </is>
+      </c>
+      <c r="K67" s="16">
+        <f>K61-SUM(K62:K66)</f>
+        <v/>
+      </c>
+      <c r="L67" s="16">
+        <f>L61-SUM(L62:L66)</f>
+        <v/>
+      </c>
+      <c r="M67" s="16">
+        <f>M61-SUM(M62:M66)</f>
+        <v/>
+      </c>
+      <c r="N67" s="16">
+        <f>N61-SUM(N62:N66)</f>
+        <v/>
+      </c>
+      <c r="O67" s="16">
+        <f>O61-SUM(O62:O66)</f>
+        <v/>
+      </c>
+      <c r="P67" s="16">
+        <f>P61-SUM(P62:P66)</f>
+        <v/>
+      </c>
+      <c r="Q67" s="16">
+        <f>Q61-SUM(Q62:Q66)</f>
+        <v/>
+      </c>
+      <c r="R67" s="16">
+        <f>R61-SUM(R62:R66)</f>
+        <v/>
+      </c>
+      <c r="S67" s="16">
+        <f>S61-SUM(S62:S66)</f>
+        <v/>
+      </c>
+      <c r="T67" s="16">
+        <f>T61-SUM(T62:T66)</f>
+        <v/>
+      </c>
+      <c r="U67" s="16">
+        <f>U61-SUM(U62:U66)</f>
+        <v/>
+      </c>
+      <c r="V67" s="16">
+        <f>V61-SUM(V62:V66)</f>
+        <v/>
+      </c>
+      <c r="W67" s="16">
+        <f>W61-SUM(W62:W66)</f>
+        <v/>
+      </c>
+      <c r="X67" s="16">
+        <f>X61-SUM(X62:X66)</f>
+        <v/>
+      </c>
+      <c r="Y67" s="16">
+        <f>Y68+Y73</f>
+        <v/>
+      </c>
+      <c r="Z67" s="16">
+        <f>Z68+Z73</f>
+        <v/>
+      </c>
+      <c r="AA67" s="16">
+        <f>AA68+AA73</f>
+        <v/>
+      </c>
+      <c r="AB67" s="16">
+        <f>AB68+AB73</f>
+        <v/>
+      </c>
+      <c r="AC67" s="16">
+        <f>AC68+AC73</f>
+        <v/>
+      </c>
+      <c r="AD67" s="16">
+        <f>AD68+AD73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    core (pp) = residual − bundle live in the quarter</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>history: formula; forward: carried at the last observed value (2Q26) — the same carry rule the card applies to the residual</t>
+        </is>
+      </c>
+      <c r="K68" s="16">
+        <f>K67-K73</f>
+        <v/>
+      </c>
+      <c r="L68" s="16">
+        <f>L67-L73</f>
+        <v/>
+      </c>
+      <c r="M68" s="16">
+        <f>M67-M73</f>
+        <v/>
+      </c>
+      <c r="N68" s="16">
+        <f>N67-N73</f>
+        <v/>
+      </c>
+      <c r="O68" s="16">
+        <f>O67-O73</f>
+        <v/>
+      </c>
+      <c r="P68" s="16">
+        <f>P67-P73</f>
+        <v/>
+      </c>
+      <c r="Q68" s="16">
+        <f>Q67-Q73</f>
+        <v/>
+      </c>
+      <c r="R68" s="16">
+        <f>R67-R73</f>
+        <v/>
+      </c>
+      <c r="S68" s="16">
+        <f>S67-S73</f>
+        <v/>
+      </c>
+      <c r="T68" s="16">
+        <f>T67-T73</f>
+        <v/>
+      </c>
+      <c r="U68" s="16">
+        <f>U67-U73</f>
+        <v/>
+      </c>
+      <c r="V68" s="16">
+        <f>V67-V73</f>
+        <v/>
+      </c>
+      <c r="W68" s="16">
+        <f>W67-W73</f>
+        <v/>
+      </c>
+      <c r="X68" s="16">
+        <f>X67-X73</f>
+        <v/>
+      </c>
+      <c r="Y68" s="16">
+        <f>X68</f>
+        <v/>
+      </c>
+      <c r="Z68" s="16">
+        <f>X68</f>
+        <v/>
+      </c>
+      <c r="AA68" s="16">
+        <f>X68</f>
+        <v/>
+      </c>
+      <c r="AB68" s="16">
+        <f>X68</f>
+        <v/>
+      </c>
+      <c r="AC68" s="16">
+        <f>X68</f>
+        <v/>
+      </c>
+      <c r="AD68" s="16">
+        <f>X68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    bundle leg: RNPL North America (larger-home mix), live 3Q25–2Q26, laps 3Q26</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>ledger D014/D032 (~1pp bundle ADR, transcript-only) split by K4 residual steps 0.92:0.88</t>
+        </is>
+      </c>
+      <c r="K70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="12" t="n">
+        <v>0.5111111111111111</v>
+      </c>
+      <c r="V70" s="12" t="n">
+        <v>0.5111111111111111</v>
+      </c>
+      <c r="W70" s="12" t="n">
+        <v>0.5111111111111111</v>
+      </c>
+      <c r="X70" s="12" t="n">
+        <v>0.5111111111111111</v>
+      </c>
+      <c r="Y70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    bundle leg: cancellation redesign + single fee, live 4Q25–3Q26 (global), laps 4Q26</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>same sizing; dates ledger D012/D013/D024/D060</t>
+        </is>
+      </c>
+      <c r="K71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="12" t="n">
+        <v>0.4888888888888889</v>
+      </c>
+      <c r="W71" s="12" t="n">
+        <v>0.4888888888888889</v>
+      </c>
+      <c r="X71" s="12" t="n">
+        <v>0.4888888888888889</v>
+      </c>
+      <c r="Y71" s="12" t="n">
+        <v>0.4888888888888889</v>
+      </c>
+      <c r="Z71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    bundle leg: RNPL ex-NA (live 17 Feb 2026), base 0.0 (unsized by management); high 1.15</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>alternative in block F</t>
+        </is>
+      </c>
+      <c r="K72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    bundle live (pp)</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>→ sum of the three legs</t>
+        </is>
+      </c>
+      <c r="K73" s="16">
+        <f>SUM(K70:K72)</f>
+        <v/>
+      </c>
+      <c r="L73" s="16">
+        <f>SUM(L70:L72)</f>
+        <v/>
+      </c>
+      <c r="M73" s="16">
+        <f>SUM(M70:M72)</f>
+        <v/>
+      </c>
+      <c r="N73" s="16">
+        <f>SUM(N70:N72)</f>
+        <v/>
+      </c>
+      <c r="O73" s="16">
+        <f>SUM(O70:O72)</f>
+        <v/>
+      </c>
+      <c r="P73" s="16">
+        <f>SUM(P70:P72)</f>
+        <v/>
+      </c>
+      <c r="Q73" s="16">
+        <f>SUM(Q70:Q72)</f>
+        <v/>
+      </c>
+      <c r="R73" s="16">
+        <f>SUM(R70:R72)</f>
+        <v/>
+      </c>
+      <c r="S73" s="16">
+        <f>SUM(S70:S72)</f>
+        <v/>
+      </c>
+      <c r="T73" s="16">
+        <f>SUM(T70:T72)</f>
+        <v/>
+      </c>
+      <c r="U73" s="16">
+        <f>SUM(U70:U72)</f>
+        <v/>
+      </c>
+      <c r="V73" s="16">
+        <f>SUM(V70:V72)</f>
+        <v/>
+      </c>
+      <c r="W73" s="16">
+        <f>SUM(W70:W72)</f>
+        <v/>
+      </c>
+      <c r="X73" s="16">
+        <f>SUM(X70:X72)</f>
+        <v/>
+      </c>
+      <c r="Y73" s="16">
+        <f>SUM(Y70:Y72)</f>
+        <v/>
+      </c>
+      <c r="Z73" s="16">
+        <f>SUM(Z70:Z72)</f>
+        <v/>
+      </c>
+      <c r="AA73" s="16">
+        <f>SUM(AA70:AA72)</f>
+        <v/>
+      </c>
+      <c r="AB73" s="16">
+        <f>SUM(AB70:AB72)</f>
+        <v/>
+      </c>
+      <c r="AC73" s="16">
+        <f>SUM(AC70:AC72)</f>
+        <v/>
+      </c>
+      <c r="AD73" s="16">
+        <f>SUM(AD70:AD72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>EX-FX ADR y/y — mechanism (pp)</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>→ core + bundle + geo + unit + LOS + seats + interaction; history = disclosed</t>
+        </is>
+      </c>
+      <c r="K75" s="18">
+        <f>K61</f>
+        <v/>
+      </c>
+      <c r="L75" s="18">
+        <f>L61</f>
+        <v/>
+      </c>
+      <c r="M75" s="18">
+        <f>M61</f>
+        <v/>
+      </c>
+      <c r="N75" s="18">
+        <f>N61</f>
+        <v/>
+      </c>
+      <c r="O75" s="18">
+        <f>O61</f>
+        <v/>
+      </c>
+      <c r="P75" s="18">
+        <f>P61</f>
+        <v/>
+      </c>
+      <c r="Q75" s="18">
+        <f>Q61</f>
+        <v/>
+      </c>
+      <c r="R75" s="18">
+        <f>R61</f>
+        <v/>
+      </c>
+      <c r="S75" s="18">
+        <f>S61</f>
+        <v/>
+      </c>
+      <c r="T75" s="18">
+        <f>T61</f>
+        <v/>
+      </c>
+      <c r="U75" s="18">
+        <f>U61</f>
+        <v/>
+      </c>
+      <c r="V75" s="18">
+        <f>V61</f>
+        <v/>
+      </c>
+      <c r="W75" s="18">
+        <f>W61</f>
+        <v/>
+      </c>
+      <c r="X75" s="18">
+        <f>X61</f>
+        <v/>
+      </c>
+      <c r="Y75" s="14">
+        <f>Y68+Y73+SUM(Y62:Y66)</f>
+        <v/>
+      </c>
+      <c r="Z75" s="14">
+        <f>Z68+Z73+SUM(Z62:Z66)</f>
+        <v/>
+      </c>
+      <c r="AA75" s="14">
+        <f>AA68+AA73+SUM(AA62:AA66)</f>
+        <v/>
+      </c>
+      <c r="AB75" s="14">
+        <f>AB68+AB73+SUM(AB62:AB66)</f>
+        <v/>
+      </c>
+      <c r="AC75" s="14">
+        <f>AC68+AC73+SUM(AC62:AC66)</f>
+        <v/>
+      </c>
+      <c r="AD75" s="14">
+        <f>AD68+AD73+SUM(AD62:AD66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>C1. Geo-mix arithmetic for the forward quarters: regional nights growth from the nights line (nights_v2_design.md §2.1), base-quarter shares and regional ADR levels held</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>regional_growth_forward.csv; 04_regional_quarterly_wide.csv (disclosed-chained)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    nights growth, na (%)</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>NA = nights line; ex-NA = 2Q26 bucket pattern (EMEA 8 / LatAm 20 / APAC 18) scaled to the line's ex-NA rate</t>
+        </is>
+      </c>
+      <c r="Y78" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Z78" s="12" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AA78" s="12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB78" s="12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC78" s="12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD78" s="12" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    nights growth, emea (%)</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>NA = nights line; ex-NA = 2Q26 bucket pattern (EMEA 8 / LatAm 20 / APAC 18) scaled to the line's ex-NA rate</t>
+        </is>
+      </c>
+      <c r="Y79" s="12" t="n">
+        <v>7.078691068961446</v>
+      </c>
+      <c r="Z79" s="12" t="n">
+        <v>6.316615068619684</v>
+      </c>
+      <c r="AA79" s="12" t="n">
+        <v>6.53339354949878</v>
+      </c>
+      <c r="AB79" s="12" t="n">
+        <v>4.672499916460061</v>
+      </c>
+      <c r="AC79" s="12" t="n">
+        <v>4.672643449515583</v>
+      </c>
+      <c r="AD79" s="12" t="n">
+        <v>4.635721906664157</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    nights growth, latam (%)</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>NA = nights line; ex-NA = 2Q26 bucket pattern (EMEA 8 / LatAm 20 / APAC 18) scaled to the line's ex-NA rate</t>
+        </is>
+      </c>
+      <c r="Y80" s="12" t="n">
+        <v>17.69672767240361</v>
+      </c>
+      <c r="Z80" s="12" t="n">
+        <v>15.79153767154921</v>
+      </c>
+      <c r="AA80" s="12" t="n">
+        <v>16.33348387374695</v>
+      </c>
+      <c r="AB80" s="12" t="n">
+        <v>11.68124979115015</v>
+      </c>
+      <c r="AC80" s="12" t="n">
+        <v>11.68160862378896</v>
+      </c>
+      <c r="AD80" s="12" t="n">
+        <v>11.58930476666039</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    nights growth, apac (%)</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>NA = nights line; ex-NA = 2Q26 bucket pattern (EMEA 8 / LatAm 20 / APAC 18) scaled to the line's ex-NA rate</t>
+        </is>
+      </c>
+      <c r="Y81" s="12" t="n">
+        <v>15.92705490516325</v>
+      </c>
+      <c r="Z81" s="12" t="n">
+        <v>14.21238390439429</v>
+      </c>
+      <c r="AA81" s="12" t="n">
+        <v>14.70013548637226</v>
+      </c>
+      <c r="AB81" s="12" t="n">
+        <v>10.51312481203514</v>
+      </c>
+      <c r="AC81" s="12" t="n">
+        <v>10.51344776141006</v>
+      </c>
+      <c r="AD81" s="12" t="n">
+        <v>10.43037428999435</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    base-quarter nights share, na</t>
+        </is>
+      </c>
+      <c r="Y82" s="26" t="n">
+        <v>0.313935</v>
+      </c>
+      <c r="Z82" s="26" t="n">
+        <v>0.300561</v>
+      </c>
+      <c r="AA82" s="26" t="n">
+        <v>0.277286</v>
+      </c>
+      <c r="AB82" s="26" t="n">
+        <v>0.282553</v>
+      </c>
+      <c r="AC82" s="26" t="n">
+        <v>0.3016875153566846</v>
+      </c>
+      <c r="AD82" s="26" t="n">
+        <v>0.2870915142801668</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    base-quarter nights share, emea</t>
+        </is>
+      </c>
+      <c r="Y83" s="26" t="n">
+        <v>0.367798</v>
+      </c>
+      <c r="Z83" s="26" t="n">
+        <v>0.402575</v>
+      </c>
+      <c r="AA83" s="26" t="n">
+        <v>0.396427</v>
+      </c>
+      <c r="AB83" s="26" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="AC83" s="26" t="n">
+        <v>0.3583984312774203</v>
+      </c>
+      <c r="AD83" s="26" t="n">
+        <v>0.395724838071041</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    base-quarter nights share, latam</t>
+        </is>
+      </c>
+      <c r="Y84" s="26" t="n">
+        <v>0.169649</v>
+      </c>
+      <c r="Z84" s="26" t="n">
+        <v>0.174009</v>
+      </c>
+      <c r="AA84" s="26" t="n">
+        <v>0.179409</v>
+      </c>
+      <c r="AB84" s="26" t="n">
+        <v>0.178621</v>
+      </c>
+      <c r="AC84" s="26" t="n">
+        <v>0.1817060448724198</v>
+      </c>
+      <c r="AD84" s="26" t="n">
+        <v>0.1862918690301008</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    base-quarter nights share, apac</t>
+        </is>
+      </c>
+      <c r="Y85" s="26" t="n">
+        <v>0.148618</v>
+      </c>
+      <c r="Z85" s="26" t="n">
+        <v>0.122855</v>
+      </c>
+      <c r="AA85" s="26" t="n">
+        <v>0.146878</v>
+      </c>
+      <c r="AB85" s="26" t="n">
+        <v>0.123325</v>
+      </c>
+      <c r="AC85" s="26" t="n">
+        <v>0.1567869451881983</v>
+      </c>
+      <c r="AD85" s="26" t="n">
+        <v>0.1297332805511836</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    base-quarter regional ADR ($, anchored)</t>
+        </is>
+      </c>
+      <c r="Y86" s="11" t="n">
+        <v>249.337</v>
+      </c>
+      <c r="Z86" s="11" t="n">
+        <v>247.2078</v>
+      </c>
+      <c r="AA86" s="11" t="n">
+        <v>279.2009</v>
+      </c>
+      <c r="AB86" s="11" t="n">
+        <v>280.7511</v>
+      </c>
+      <c r="AC86" s="11" t="n">
+        <v>280.7511</v>
+      </c>
+      <c r="AD86" s="11" t="n">
+        <v>280.7511</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    base-quarter regional ADR ($, anchored)</t>
+        </is>
+      </c>
+      <c r="Y87" s="11" t="n">
+        <v>162.0721</v>
+      </c>
+      <c r="Z87" s="11" t="n">
+        <v>158.3398</v>
+      </c>
+      <c r="AA87" s="11" t="n">
+        <v>180.3991</v>
+      </c>
+      <c r="AB87" s="11" t="n">
+        <v>169.8482</v>
+      </c>
+      <c r="AC87" s="11" t="n">
+        <v>169.8482</v>
+      </c>
+      <c r="AD87" s="11" t="n">
+        <v>169.8482</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    base-quarter regional ADR ($, anchored)</t>
+        </is>
+      </c>
+      <c r="Y88" s="11" t="n">
+        <v>97.08110000000001</v>
+      </c>
+      <c r="Z88" s="11" t="n">
+        <v>95.50830000000001</v>
+      </c>
+      <c r="AA88" s="11" t="n">
+        <v>102.1656</v>
+      </c>
+      <c r="AB88" s="11" t="n">
+        <v>102.8022</v>
+      </c>
+      <c r="AC88" s="11" t="n">
+        <v>102.8022</v>
+      </c>
+      <c r="AD88" s="11" t="n">
+        <v>102.8022</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    base-quarter regional ADR ($, anchored)</t>
+        </is>
+      </c>
+      <c r="Y89" s="11" t="n">
+        <v>116.0255</v>
+      </c>
+      <c r="Z89" s="11" t="n">
+        <v>115.3398</v>
+      </c>
+      <c r="AA89" s="11" t="n">
+        <v>127.7091</v>
+      </c>
+      <c r="AB89" s="11" t="n">
+        <v>122.0612</v>
+      </c>
+      <c r="AC89" s="11" t="n">
+        <v>122.0612</v>
+      </c>
+      <c r="AD89" s="11" t="n">
+        <v>122.0612</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    total nights growth (%)</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>→ SUMPRODUCT(shares, growth)</t>
+        </is>
+      </c>
+      <c r="Y90" s="16">
+        <f>SUMPRODUCT(Y82:Y85,Y78:Y81)</f>
+        <v/>
+      </c>
+      <c r="Z90" s="16">
+        <f>SUMPRODUCT(Z82:Z85,Z78:Z81)</f>
+        <v/>
+      </c>
+      <c r="AA90" s="16">
+        <f>SUMPRODUCT(AA82:AA85,AA78:AA81)</f>
+        <v/>
+      </c>
+      <c r="AB90" s="16">
+        <f>SUMPRODUCT(AB82:AB85,AB78:AB81)</f>
+        <v/>
+      </c>
+      <c r="AC90" s="16">
+        <f>SUMPRODUCT(AC82:AC85,AC78:AC81)</f>
+        <v/>
+      </c>
+      <c r="AD90" s="16">
+        <f>SUMPRODUCT(AD82:AD85,AD78:AD81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    geo mix (pp)</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>→ (Σ share×(1+g)×ADR) / ((1+g_tot) × Σ share×ADR) − 1, ×100</t>
+        </is>
+      </c>
+      <c r="Y91" s="16">
+        <f>(SUMPRODUCT(Y82:Y85,1+Y78:Y81/100,Y86:Y89)/((1+Y90/100)*SUMPRODUCT(Y82:Y85,Y86:Y89))-1)*100</f>
+        <v/>
+      </c>
+      <c r="Z91" s="16">
+        <f>(SUMPRODUCT(Z82:Z85,1+Z78:Z81/100,Z86:Z89)/((1+Z90/100)*SUMPRODUCT(Z82:Z85,Z86:Z89))-1)*100</f>
+        <v/>
+      </c>
+      <c r="AA91" s="16">
+        <f>(SUMPRODUCT(AA82:AA85,1+AA78:AA81/100,AA86:AA89)/((1+AA90/100)*SUMPRODUCT(AA82:AA85,AA86:AA89))-1)*100</f>
+        <v/>
+      </c>
+      <c r="AB91" s="16">
+        <f>(SUMPRODUCT(AB82:AB85,1+AB78:AB81/100,AB86:AB89)/((1+AB90/100)*SUMPRODUCT(AB82:AB85,AB86:AB89))-1)*100</f>
+        <v/>
+      </c>
+      <c r="AC91" s="16">
+        <f>(SUMPRODUCT(AC82:AC85,1+AC78:AC81/100,AC86:AC89)/((1+AC90/100)*SUMPRODUCT(AC82:AC85,AC86:AC89))-1)*100</f>
+        <v/>
+      </c>
+      <c r="AD91" s="16">
+        <f>(SUMPRODUCT(AD82:AD85,1+AD78:AD81/100,AD86:AD89)/((1+AD90/100)*SUMPRODUCT(AD82:AD85,AD86:AD89))-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>D. Reported ADR path — ADR = year-ago ADR × (1 + (ex-FX mechanism + FX identity) / 100); band; the Street; GBV on the nights line</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="5" t="n"/>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="n"/>
+      <c r="M93" s="5" t="n"/>
+      <c r="N93" s="5" t="n"/>
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="5" t="n"/>
+      <c r="Q93" s="5" t="n"/>
+      <c r="R93" s="5" t="n"/>
+      <c r="S93" s="5" t="n"/>
+      <c r="T93" s="5" t="n"/>
+      <c r="U93" s="5" t="n"/>
+      <c r="V93" s="5" t="n"/>
+      <c r="W93" s="5" t="n"/>
+      <c r="X93" s="5" t="n"/>
+      <c r="Y93" s="5" t="n"/>
+      <c r="Z93" s="5" t="n"/>
+      <c r="AA93" s="5" t="n"/>
+      <c r="AB93" s="5" t="n"/>
+      <c r="AC93" s="5" t="n"/>
+      <c r="AD93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FX effect on ADR (pp)</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>→ block B identity</t>
+        </is>
+      </c>
+      <c r="Y94" s="18">
+        <f>Y51</f>
+        <v/>
+      </c>
+      <c r="Z94" s="18">
+        <f>Z51</f>
+        <v/>
+      </c>
+      <c r="AA94" s="18">
+        <f>AA51</f>
+        <v/>
+      </c>
+      <c r="AB94" s="18">
+        <f>AB51</f>
+        <v/>
+      </c>
+      <c r="AC94" s="18">
+        <f>AC51</f>
+        <v/>
+      </c>
+      <c r="AD94" s="18">
+        <f>AD51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reported ADR y/y (%)</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>→ ex-FX mechanism + FX</t>
+        </is>
+      </c>
+      <c r="Y95" s="16">
+        <f>Y75+Y94</f>
+        <v/>
+      </c>
+      <c r="Z95" s="16">
+        <f>Z75+Z94</f>
+        <v/>
+      </c>
+      <c r="AA95" s="16">
+        <f>AA75+AA94</f>
+        <v/>
+      </c>
+      <c r="AB95" s="16">
+        <f>AB75+AB94</f>
+        <v/>
+      </c>
+      <c r="AC95" s="16">
+        <f>AC75+AC94</f>
+        <v/>
+      </c>
+      <c r="AD95" s="16">
+        <f>AD75+AD94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>ADR ($) — the line</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>→ year-ago ADR × (1 + y/y/100)</t>
+        </is>
+      </c>
+      <c r="Y96" s="13">
+        <f>U7*(1+Y95/100)</f>
+        <v/>
+      </c>
+      <c r="Z96" s="13">
+        <f>V7*(1+Z95/100)</f>
+        <v/>
+      </c>
+      <c r="AA96" s="13">
+        <f>W7*(1+AA95/100)</f>
+        <v/>
+      </c>
+      <c r="AB96" s="13">
+        <f>X7*(1+AB95/100)</f>
+        <v/>
+      </c>
+      <c r="AC96" s="13">
+        <f>Y7*(1+AC95/100)</f>
+        <v/>
+      </c>
+      <c r="AD96" s="13">
+        <f>Z7*(1+AD95/100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    band half-width (pp)</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>engine exfx_envelope.csv: RSS of parameter half-ranges ⊕ FX bootstrap sd</t>
+        </is>
+      </c>
+      <c r="Y97" s="12" t="n">
+        <v>0.9775225447066912</v>
+      </c>
+      <c r="Z97" s="12" t="n">
+        <v>1.931880714226598</v>
+      </c>
+      <c r="AA97" s="12" t="n">
+        <v>2.742174489720473</v>
+      </c>
+      <c r="AB97" s="12" t="n">
+        <v>3.24814593997769</v>
+      </c>
+      <c r="AC97" s="12" t="n">
+        <v>3.756663072305037</v>
+      </c>
+      <c r="AD97" s="12" t="n">
+        <v>3.900045484266994</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ADR low ($)</t>
+        </is>
+      </c>
+      <c r="Y98" s="15">
+        <f>U7*(1+(Y95-Y97)/100)</f>
+        <v/>
+      </c>
+      <c r="Z98" s="15">
+        <f>V7*(1+(Z95-Z97)/100)</f>
+        <v/>
+      </c>
+      <c r="AA98" s="15">
+        <f>W7*(1+(AA95-AA97)/100)</f>
+        <v/>
+      </c>
+      <c r="AB98" s="15">
+        <f>X7*(1+(AB95-AB97)/100)</f>
+        <v/>
+      </c>
+      <c r="AC98" s="15">
+        <f>Y7*(1+(AC95-AC97)/100)</f>
+        <v/>
+      </c>
+      <c r="AD98" s="15">
+        <f>Z7*(1+(AD95-AD97)/100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ADR high ($)</t>
+        </is>
+      </c>
+      <c r="Y99" s="15">
+        <f>U7*(1+(Y95+Y97)/100)</f>
+        <v/>
+      </c>
+      <c r="Z99" s="15">
+        <f>V7*(1+(Z95+Z97)/100)</f>
+        <v/>
+      </c>
+      <c r="AA99" s="15">
+        <f>W7*(1+(AA95+AA97)/100)</f>
+        <v/>
+      </c>
+      <c r="AB99" s="15">
+        <f>X7*(1+(AB95+AB97)/100)</f>
+        <v/>
+      </c>
+      <c r="AC99" s="15">
+        <f>Y7*(1+(AC95+AC97)/100)</f>
+        <v/>
+      </c>
+      <c r="AD99" s="15">
+        <f>Z7*(1+(AD95+AD97)/100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Street ADR ($)</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Bloomberg MODL screenshot 12 Sep 2026 (Krish): 3Q26 177.06 n 26 (173.71–179.12), 4Q26 171.33 n 25; no FY row exists</t>
+        </is>
+      </c>
+      <c r="Y100" s="11" t="n">
+        <v>177.06</v>
+      </c>
+      <c r="Z100" s="11" t="n">
+        <v>171.33</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Street implied y/y (%)</t>
+        </is>
+      </c>
+      <c r="Y101" s="16">
+        <f>(Y100/U7-1)*100</f>
+        <v/>
+      </c>
+      <c r="Z101" s="16">
+        <f>(Z100/V7-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    z: (ours − Street) / band</t>
+        </is>
+      </c>
+      <c r="Y102" s="16">
+        <f>(Y95-Y101)/Y97</f>
+        <v/>
+      </c>
+      <c r="Z102" s="16">
+        <f>(Z95-Z101)/Z97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    P(print ≥ Street)</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>→ 1 − NORM.S.DIST((Street y/y − ours)/band, TRUE)</t>
+        </is>
+      </c>
+      <c r="Y103" s="10">
+        <f>1-NORM.S.DIST((Y101-Y95)/Y97,TRUE)</f>
+        <v/>
+      </c>
+      <c r="Z103" s="10">
+        <f>1-NORM.S.DIST((Z101-Z95)/Z97,TRUE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    nights (m) — line 1</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>→ Income_Statement row 5 (nights line)</t>
+        </is>
+      </c>
+      <c r="K104" s="20">
+        <f>Income_Statement!C5</f>
+        <v/>
+      </c>
+      <c r="L104" s="20">
+        <f>Income_Statement!D5</f>
+        <v/>
+      </c>
+      <c r="M104" s="20">
+        <f>Income_Statement!E5</f>
+        <v/>
+      </c>
+      <c r="N104" s="20">
+        <f>Income_Statement!F5</f>
+        <v/>
+      </c>
+      <c r="O104" s="20">
+        <f>Income_Statement!G5</f>
+        <v/>
+      </c>
+      <c r="P104" s="20">
+        <f>Income_Statement!H5</f>
+        <v/>
+      </c>
+      <c r="Q104" s="20">
+        <f>Income_Statement!I5</f>
+        <v/>
+      </c>
+      <c r="R104" s="20">
+        <f>Income_Statement!J5</f>
+        <v/>
+      </c>
+      <c r="S104" s="20">
+        <f>Income_Statement!K5</f>
+        <v/>
+      </c>
+      <c r="T104" s="20">
+        <f>Income_Statement!L5</f>
+        <v/>
+      </c>
+      <c r="U104" s="20">
+        <f>Income_Statement!M5</f>
+        <v/>
+      </c>
+      <c r="V104" s="20">
+        <f>Income_Statement!N5</f>
+        <v/>
+      </c>
+      <c r="W104" s="20">
+        <f>Income_Statement!O5</f>
+        <v/>
+      </c>
+      <c r="X104" s="20">
+        <f>Income_Statement!P5</f>
+        <v/>
+      </c>
+      <c r="Y104" s="20">
+        <f>Income_Statement!Q5</f>
+        <v/>
+      </c>
+      <c r="Z104" s="20">
+        <f>Income_Statement!R5</f>
+        <v/>
+      </c>
+      <c r="AA104" s="20">
+        <f>Income_Statement!S5</f>
+        <v/>
+      </c>
+      <c r="AB104" s="20">
+        <f>Income_Statement!T5</f>
+        <v/>
+      </c>
+      <c r="AC104" s="20">
+        <f>Income_Statement!U5</f>
+        <v/>
+      </c>
+      <c r="AD104" s="20">
+        <f>Income_Statement!V5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GBV ($bn) = nights × ADR</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>cross-check only; the take-rate line is built next</t>
+        </is>
+      </c>
+      <c r="K105" s="16">
+        <f>K104*K7/1000</f>
+        <v/>
+      </c>
+      <c r="L105" s="16">
+        <f>L104*L7/1000</f>
+        <v/>
+      </c>
+      <c r="M105" s="16">
+        <f>M104*M7/1000</f>
+        <v/>
+      </c>
+      <c r="N105" s="16">
+        <f>N104*N7/1000</f>
+        <v/>
+      </c>
+      <c r="O105" s="16">
+        <f>O104*O7/1000</f>
+        <v/>
+      </c>
+      <c r="P105" s="16">
+        <f>P104*P7/1000</f>
+        <v/>
+      </c>
+      <c r="Q105" s="16">
+        <f>Q104*Q7/1000</f>
+        <v/>
+      </c>
+      <c r="R105" s="16">
+        <f>R104*R7/1000</f>
+        <v/>
+      </c>
+      <c r="S105" s="16">
+        <f>S104*S7/1000</f>
+        <v/>
+      </c>
+      <c r="T105" s="16">
+        <f>T104*T7/1000</f>
+        <v/>
+      </c>
+      <c r="U105" s="16">
+        <f>U104*U7/1000</f>
+        <v/>
+      </c>
+      <c r="V105" s="16">
+        <f>V104*V7/1000</f>
+        <v/>
+      </c>
+      <c r="W105" s="16">
+        <f>W104*W7/1000</f>
+        <v/>
+      </c>
+      <c r="X105" s="16">
+        <f>X104*X7/1000</f>
+        <v/>
+      </c>
+      <c r="Y105" s="16">
+        <f>Y104*Y96/1000</f>
+        <v/>
+      </c>
+      <c r="Z105" s="16">
+        <f>Z104*Z96/1000</f>
+        <v/>
+      </c>
+      <c r="AA105" s="16">
+        <f>AA104*AA96/1000</f>
+        <v/>
+      </c>
+      <c r="AB105" s="16">
+        <f>AB104*AB96/1000</f>
+        <v/>
+      </c>
+      <c r="AC105" s="16">
+        <f>AC104*AC96/1000</f>
+        <v/>
+      </c>
+      <c r="AD105" s="16">
+        <f>AD104*AD96/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>E. Engine reference values (Python) — for tie-out after an Excel recalculation</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
+      <c r="E107" s="5" t="n"/>
+      <c r="F107" s="5" t="n"/>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="5" t="n"/>
+      <c r="I107" s="5" t="n"/>
+      <c r="J107" s="5" t="n"/>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="5" t="n"/>
+      <c r="M107" s="5" t="n"/>
+      <c r="N107" s="5" t="n"/>
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="5" t="n"/>
+      <c r="Q107" s="5" t="n"/>
+      <c r="R107" s="5" t="n"/>
+      <c r="S107" s="5" t="n"/>
+      <c r="T107" s="5" t="n"/>
+      <c r="U107" s="5" t="n"/>
+      <c r="V107" s="5" t="n"/>
+      <c r="W107" s="5" t="n"/>
+      <c r="X107" s="5" t="n"/>
+      <c r="Y107" s="5" t="n"/>
+      <c r="Z107" s="5" t="n"/>
+      <c r="AA107" s="5" t="n"/>
+      <c r="AB107" s="5" t="n"/>
+      <c r="AC107" s="5" t="n"/>
+      <c r="AD107" s="5" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>walk-forward RMSE ratio vs naive, V0 identity, W1 O1 / O2 / O3</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="n">
+        <v>0.4373436932602267</v>
+      </c>
+      <c r="D108" s="12" t="n">
+        <v>0.3437214310004852</v>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>0.3027325798499696</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>… W2 O1 / O2 / O3 (pass line ≤ 0.75 at O2 and O3 on both windows)</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="n">
+        <v>0.6248026109788748</v>
+      </c>
+      <c r="D109" s="12" t="n">
+        <v>0.3830864350268836</v>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>0.3172637032904287</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>V1 fitted pass-through, W1 O1 / O2 / O3</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="n">
+        <v>0.4971529699016717</v>
+      </c>
+      <c r="D110" s="12" t="n">
+        <v>0.3749859241803115</v>
+      </c>
+      <c r="E110" s="12" t="n">
+        <v>0.3372746081063169</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>euro-only OLS (comparator), W1 O1 / O2 / O3</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="n">
+        <v>0.3991041209797802</v>
+      </c>
+      <c r="D111" s="12" t="n">
+        <v>0.2700012303742727</v>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>0.2813206067080157</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>posterior pass-through β (NA / EMEA / LatAm / APAC), prior N(1, 0.25²)</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="n">
+        <v>0.9937220374665529</v>
+      </c>
+      <c r="D112" s="12" t="n">
+        <v>1.199117663499177</v>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>0.4595224116993439</v>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>1.266392840244777</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>FX effect 3Q26 / 4Q26 / 1Q27 / 2Q27 (pp, spot held)</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="n">
+        <v>0.4152814166247513</v>
+      </c>
+      <c r="D113" s="12" t="n">
+        <v>0.5136690253172425</v>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>-0.369013484663626</v>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>-0.4269361495661503</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>ADR $ 3Q26 / 4Q26 / 1Q27 / 2Q27 (engine)</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="n">
+        <v>177.6812219414954</v>
+      </c>
+      <c r="D114" s="12" t="n">
+        <v>173.0340496165458</v>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>190.6458188568733</v>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>188.3776100123214</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>ex-FX mechanism 3Q26 / 4Q26 / 1Q27 / 2Q27 (pp)</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="n">
+        <v>3.315947459255554</v>
+      </c>
+      <c r="D115" s="12" t="n">
+        <v>2.784074164071932</v>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>2.416877127139422</v>
+      </c>
+      <c r="F115" s="12" t="n">
+        <v>2.956523050083999</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>card v3 ADR $ 3Q26 / 4Q26 (DEC-0008, without K, midpoint FX −0.43 / +0.15)</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="n">
+        <v>176.88</v>
+      </c>
+      <c r="D116" s="12" t="n">
+        <v>173.94</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>geo-mix method check: mean |bucket arithmetic − H| on 2Q24–2Q26 (pp)</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="n">
+        <v>0.1344148709440589</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>F. Alternatives carried beside the base (never blended): ex-FX rule → reported ADR $ at the same FX</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n"/>
+      <c r="C119" s="5" t="n"/>
+      <c r="D119" s="5" t="n"/>
+      <c r="E119" s="5" t="n"/>
+      <c r="F119" s="5" t="n"/>
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="5" t="n"/>
+      <c r="I119" s="5" t="n"/>
+      <c r="J119" s="5" t="n"/>
+      <c r="K119" s="5" t="n"/>
+      <c r="L119" s="5" t="n"/>
+      <c r="M119" s="5" t="n"/>
+      <c r="N119" s="5" t="n"/>
+      <c r="O119" s="5" t="n"/>
+      <c r="P119" s="5" t="n"/>
+      <c r="Q119" s="5" t="n"/>
+      <c r="R119" s="5" t="n"/>
+      <c r="S119" s="5" t="n"/>
+      <c r="T119" s="5" t="n"/>
+      <c r="U119" s="5" t="n"/>
+      <c r="V119" s="5" t="n"/>
+      <c r="W119" s="5" t="n"/>
+      <c r="X119" s="5" t="n"/>
+      <c r="Y119" s="5" t="n"/>
+      <c r="Z119" s="5" t="n"/>
+      <c r="AA119" s="5" t="n"/>
+      <c r="AB119" s="5" t="n"/>
+      <c r="AC119" s="5" t="n"/>
+      <c r="AD119" s="5" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>quarter → ex-FX (pp) | ADR ($) | GBV ($bn)</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>3Q26</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>4Q26</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>1Q27</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>2Q27</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>base: core carry + bundle laps (nights-linked geo)</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="n">
+        <v>3.315947459255554</v>
+      </c>
+      <c r="D121" s="11" t="n">
+        <v>177.6812219414954</v>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>26.08360338101152</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>2.784074164071932</v>
+      </c>
+      <c r="G121" s="11" t="n">
+        <v>173.0340496165458</v>
+      </c>
+      <c r="H121" s="11" t="n">
+        <v>22.80588773946074</v>
+      </c>
+      <c r="I121" s="11" t="n">
+        <v>2.416877127139422</v>
+      </c>
+      <c r="J121" s="11" t="n">
+        <v>190.6458188568733</v>
+      </c>
+      <c r="K121" s="11" t="n">
+        <v>32.22295630318872</v>
+      </c>
+      <c r="L121" s="11" t="n">
+        <v>2.956523050083999</v>
+      </c>
+      <c r="M121" s="11" t="n">
+        <v>188.3776100123214</v>
+      </c>
+      <c r="N121" s="11" t="n">
+        <v>29.5941225329357</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>card v3: last_q residual carry, no lap (card geo)</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>3.69126637648649</v>
+      </c>
+      <c r="D122" s="11" t="n">
+        <v>178.3241057148202</v>
+      </c>
+      <c r="E122" s="11" t="n">
+        <v>26.17797871893561</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>3.69126637648649</v>
+      </c>
+      <c r="G122" s="11" t="n">
+        <v>174.5536872915614</v>
+      </c>
+      <c r="H122" s="11" t="n">
+        <v>23.0061759850278</v>
+      </c>
+      <c r="I122" s="11" t="n">
+        <v>3.60883637648649</v>
+      </c>
+      <c r="J122" s="11" t="n">
+        <v>192.8726371265034</v>
+      </c>
+      <c r="K122" s="11" t="n">
+        <v>32.59933312712161</v>
+      </c>
+      <c r="L122" s="11" t="n">
+        <v>3.60883637648649</v>
+      </c>
+      <c r="M122" s="11" t="n">
+        <v>189.5761052869207</v>
+      </c>
+      <c r="N122" s="11" t="n">
+        <v>29.78240614057524</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>full lap: ex-NA RNPL sized at the 1H26 residual steps</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="n">
+        <v>3.315947459255554</v>
+      </c>
+      <c r="D123" s="11" t="n">
+        <v>177.6812219414954</v>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v>26.08360338101152</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>2.784074164071932</v>
+      </c>
+      <c r="G123" s="11" t="n">
+        <v>173.0340496165458</v>
+      </c>
+      <c r="H123" s="11" t="n">
+        <v>22.80588773946074</v>
+      </c>
+      <c r="I123" s="11" t="n">
+        <v>1.956877127139422</v>
+      </c>
+      <c r="J123" s="11" t="n">
+        <v>189.7864468568733</v>
+      </c>
+      <c r="K123" s="11" t="n">
+        <v>32.07770524774872</v>
+      </c>
+      <c r="L123" s="11" t="n">
+        <v>1.806523050083998</v>
+      </c>
+      <c r="M123" s="11" t="n">
+        <v>186.2647150123214</v>
+      </c>
+      <c r="N123" s="11" t="n">
+        <v>29.2621867284357</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>core mean reversion to the 2023-25 mean</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>1.864621082769064</v>
+      </c>
+      <c r="D124" s="11" t="n">
+        <v>175.1952449912116</v>
+      </c>
+      <c r="E124" s="11" t="n">
+        <v>25.71866196470987</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>1.332747787585442</v>
+      </c>
+      <c r="G124" s="11" t="n">
+        <v>170.6029328032933</v>
+      </c>
+      <c r="H124" s="11" t="n">
+        <v>22.48546654347406</v>
+      </c>
+      <c r="I124" s="11" t="n">
+        <v>0.9655507506529332</v>
+      </c>
+      <c r="J124" s="11" t="n">
+        <v>187.9344509203212</v>
+      </c>
+      <c r="K124" s="11" t="n">
+        <v>31.7646808945527</v>
+      </c>
+      <c r="L124" s="11" t="n">
+        <v>1.505196673597509</v>
+      </c>
+      <c r="M124" s="11" t="n">
+        <v>185.7110880608028</v>
+      </c>
+      <c r="N124" s="11" t="n">
+        <v>29.17521193435212</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>AR(1) on core (K4 rho 0.747)</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>3.092067886004471</v>
+      </c>
+      <c r="D125" s="11" t="n">
+        <v>177.2977386204736</v>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v>26.02730802948552</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>2.392956549602292</v>
+      </c>
+      <c r="G125" s="11" t="n">
+        <v>172.3788885005477</v>
+      </c>
+      <c r="H125" s="11" t="n">
+        <v>22.71953750437219</v>
+      </c>
+      <c r="I125" s="11" t="n">
+        <v>1.90083269587952</v>
+      </c>
+      <c r="J125" s="11" t="n">
+        <v>189.6817446503935</v>
+      </c>
+      <c r="K125" s="11" t="n">
+        <v>32.06000848080952</v>
+      </c>
+      <c r="L125" s="11" t="n">
+        <v>2.347158286681769</v>
+      </c>
+      <c r="M125" s="11" t="n">
+        <v>187.2580241325226</v>
+      </c>
+      <c r="N125" s="11" t="n">
+        <v>29.41823559121929</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>base + fee-migration K line (DEC-0008 sensitivity)</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>3.487447459255554</v>
+      </c>
+      <c r="D126" s="11" t="n">
+        <v>177.9749842914954</v>
+      </c>
+      <c r="E126" s="11" t="n">
+        <v>26.12672769399152</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>3.158574164071932</v>
+      </c>
+      <c r="G126" s="11" t="n">
+        <v>173.6613745665458</v>
+      </c>
+      <c r="H126" s="11" t="n">
+        <v>22.88856916787073</v>
+      </c>
+      <c r="I126" s="11" t="n">
+        <v>2.761977127139422</v>
+      </c>
+      <c r="J126" s="11" t="n">
+        <v>191.2905346768732</v>
+      </c>
+      <c r="K126" s="11" t="n">
+        <v>32.33192617108512</v>
+      </c>
+      <c r="L126" s="11" t="n">
+        <v>3.267323050083998</v>
+      </c>
+      <c r="M126" s="11" t="n">
+        <v>188.9486428523214</v>
+      </c>
+      <c r="N126" s="11" t="n">
+        <v>29.6838317920997</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>chart helper: ADR $ (printed, then engine)</t>
+        </is>
+      </c>
+      <c r="O129" s="20">
+        <f>O7</f>
+        <v/>
+      </c>
+      <c r="P129" s="20">
+        <f>P7</f>
+        <v/>
+      </c>
+      <c r="Q129" s="20">
+        <f>Q7</f>
+        <v/>
+      </c>
+      <c r="R129" s="20">
+        <f>R7</f>
+        <v/>
+      </c>
+      <c r="S129" s="20">
+        <f>S7</f>
+        <v/>
+      </c>
+      <c r="T129" s="20">
+        <f>T7</f>
+        <v/>
+      </c>
+      <c r="U129" s="20">
+        <f>U7</f>
+        <v/>
+      </c>
+      <c r="V129" s="20">
+        <f>V7</f>
+        <v/>
+      </c>
+      <c r="W129" s="20">
+        <f>W7</f>
+        <v/>
+      </c>
+      <c r="X129" s="20">
+        <f>X7</f>
+        <v/>
+      </c>
+      <c r="Y129" s="20">
+        <f>Y7</f>
+        <v/>
+      </c>
+      <c r="Z129" s="20">
+        <f>Z7</f>
+        <v/>
+      </c>
+      <c r="AA129" s="20">
+        <f>AA7</f>
+        <v/>
+      </c>
+      <c r="AB129" s="20">
+        <f>AB7</f>
+        <v/>
+      </c>
+      <c r="AC129" s="20">
+        <f>AC7</f>
+        <v/>
+      </c>
+      <c r="AD129" s="20">
+        <f>AD7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>chart helper: Street ADR $</t>
+        </is>
+      </c>
+      <c r="Y130" s="20">
+        <f>Y100</f>
+        <v/>
+      </c>
+      <c r="Z130" s="20">
+        <f>Z100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>chart helper: FX identity (pp)</t>
+        </is>
+      </c>
+      <c r="O131" s="20">
+        <f>O51</f>
+        <v/>
+      </c>
+      <c r="P131" s="20">
+        <f>P51</f>
+        <v/>
+      </c>
+      <c r="Q131" s="20">
+        <f>Q51</f>
+        <v/>
+      </c>
+      <c r="R131" s="20">
+        <f>R51</f>
+        <v/>
+      </c>
+      <c r="S131" s="20">
+        <f>S51</f>
+        <v/>
+      </c>
+      <c r="T131" s="20">
+        <f>T51</f>
+        <v/>
+      </c>
+      <c r="U131" s="20">
+        <f>U51</f>
+        <v/>
+      </c>
+      <c r="V131" s="20">
+        <f>V51</f>
+        <v/>
+      </c>
+      <c r="W131" s="20">
+        <f>W51</f>
+        <v/>
+      </c>
+      <c r="X131" s="20">
+        <f>X51</f>
+        <v/>
+      </c>
+      <c r="Y131" s="20">
+        <f>Y51</f>
+        <v/>
+      </c>
+      <c r="Z131" s="20">
+        <f>Z51</f>
+        <v/>
+      </c>
+      <c r="AA131" s="20">
+        <f>AA51</f>
+        <v/>
+      </c>
+      <c r="AB131" s="20">
+        <f>AB51</f>
+        <v/>
+      </c>
+      <c r="AC131" s="20">
+        <f>AC51</f>
+        <v/>
+      </c>
+      <c r="AD131" s="20">
+        <f>AD51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="8" t="inlineStr">
+        <is>
+          <t>chart helper: disclosed FX (pp)</t>
+        </is>
+      </c>
+      <c r="O132" s="20">
+        <f>O10</f>
+        <v/>
+      </c>
+      <c r="P132" s="20">
+        <f>P10</f>
+        <v/>
+      </c>
+      <c r="Q132" s="20">
+        <f>Q10</f>
+        <v/>
+      </c>
+      <c r="R132" s="20">
+        <f>R10</f>
+        <v/>
+      </c>
+      <c r="S132" s="20">
+        <f>S10</f>
+        <v/>
+      </c>
+      <c r="T132" s="20">
+        <f>T10</f>
+        <v/>
+      </c>
+      <c r="U132" s="20">
+        <f>U10</f>
+        <v/>
+      </c>
+      <c r="V132" s="20">
+        <f>V10</f>
+        <v/>
+      </c>
+      <c r="W132" s="20">
+        <f>W10</f>
+        <v/>
+      </c>
+      <c r="X132" s="20">
+        <f>X10</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5139,7 +12182,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Row 5 nights: green = link to Nights_Engine. Other lines: labels only until built together (yellow = to build). Quarters A = printed, E = engine forecast.</t>
+          <t>Row 5 nights: green = link to Nights_Engine. Rows 8–11 GBV and ADR: link to ADR_Engine (line 2). Other lines: labels only until built together (yellow = to build). Quarters A = printed, E = engine.</t>
         </is>
       </c>
     </row>
@@ -5289,83 +12332,83 @@
           <t>Nights_Engine: printed (A), base print path (E)</t>
         </is>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="27">
         <f>Nights_Engine!K7</f>
         <v/>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="27">
         <f>Nights_Engine!L7</f>
         <v/>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="27">
         <f>Nights_Engine!M7</f>
         <v/>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="27">
         <f>Nights_Engine!N7</f>
         <v/>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="27">
         <f>Nights_Engine!O7</f>
         <v/>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="27">
         <f>Nights_Engine!P7</f>
         <v/>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="27">
         <f>Nights_Engine!Q7</f>
         <v/>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="27">
         <f>Nights_Engine!R7</f>
         <v/>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="27">
         <f>Nights_Engine!S7</f>
         <v/>
       </c>
-      <c r="L5" s="25">
+      <c r="L5" s="27">
         <f>Nights_Engine!T7</f>
         <v/>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="27">
         <f>Nights_Engine!U7</f>
         <v/>
       </c>
-      <c r="N5" s="25">
+      <c r="N5" s="27">
         <f>Nights_Engine!V7</f>
         <v/>
       </c>
-      <c r="O5" s="25">
+      <c r="O5" s="27">
         <f>Nights_Engine!W7</f>
         <v/>
       </c>
-      <c r="P5" s="25">
+      <c r="P5" s="27">
         <f>Nights_Engine!X7</f>
         <v/>
       </c>
-      <c r="Q5" s="26">
+      <c r="Q5" s="28">
         <f>Nights_Engine!Y85</f>
         <v/>
       </c>
-      <c r="R5" s="26">
+      <c r="R5" s="28">
         <f>Nights_Engine!Z85</f>
         <v/>
       </c>
-      <c r="S5" s="26">
+      <c r="S5" s="28">
         <f>Nights_Engine!AA85</f>
         <v/>
       </c>
-      <c r="T5" s="26">
+      <c r="T5" s="28">
         <f>Nights_Engine!AB85</f>
         <v/>
       </c>
-      <c r="U5" s="26">
+      <c r="U5" s="28">
         <f>Nights_Engine!AC85</f>
         <v/>
       </c>
-      <c r="V5" s="26">
+      <c r="V5" s="28">
         <f>Nights_Engine!AD85</f>
         <v/>
       </c>
@@ -5381,11 +12424,11 @@
         <f>K5+L5+M5+N5</f>
         <v/>
       </c>
-      <c r="AA5" s="27">
+      <c r="AA5" s="29">
         <f>O5+P5+Q5+R5</f>
         <v/>
       </c>
-      <c r="AB5" s="27">
+      <c r="AB5" s="29">
         <f>S5+T5+U5+V5</f>
         <v/>
       </c>
@@ -5401,19 +12444,19 @@
           <t>→ nights / four quarters earlier − 1</t>
         </is>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="30">
         <f>Nights_Engine!K8</f>
         <v/>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="30">
         <f>Nights_Engine!L8</f>
         <v/>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="30">
         <f>Nights_Engine!M8</f>
         <v/>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="30">
         <f>Nights_Engine!N8</f>
         <v/>
       </c>
@@ -5534,17 +12577,96 @@
       <c r="AC7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Gross booking value ($bn)</t>
         </is>
       </c>
-      <c r="Q8" s="29" t="n"/>
-      <c r="R8" s="29" t="n"/>
-      <c r="S8" s="29" t="n"/>
-      <c r="T8" s="29" t="n"/>
-      <c r="U8" s="29" t="n"/>
-      <c r="V8" s="29" t="n"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>→ nights × ADR ÷ 1000 (line 1 × line 2)</t>
+        </is>
+      </c>
+      <c r="C8" s="16">
+        <f>C5*C10/1000</f>
+        <v/>
+      </c>
+      <c r="D8" s="16">
+        <f>D5*D10/1000</f>
+        <v/>
+      </c>
+      <c r="E8" s="16">
+        <f>E5*E10/1000</f>
+        <v/>
+      </c>
+      <c r="F8" s="16">
+        <f>F5*F10/1000</f>
+        <v/>
+      </c>
+      <c r="G8" s="16">
+        <f>G5*G10/1000</f>
+        <v/>
+      </c>
+      <c r="H8" s="16">
+        <f>H5*H10/1000</f>
+        <v/>
+      </c>
+      <c r="I8" s="16">
+        <f>I5*I10/1000</f>
+        <v/>
+      </c>
+      <c r="J8" s="16">
+        <f>J5*J10/1000</f>
+        <v/>
+      </c>
+      <c r="K8" s="16">
+        <f>K5*K10/1000</f>
+        <v/>
+      </c>
+      <c r="L8" s="16">
+        <f>L5*L10/1000</f>
+        <v/>
+      </c>
+      <c r="M8" s="16">
+        <f>M5*M10/1000</f>
+        <v/>
+      </c>
+      <c r="N8" s="16">
+        <f>N5*N10/1000</f>
+        <v/>
+      </c>
+      <c r="O8" s="16">
+        <f>O5*O10/1000</f>
+        <v/>
+      </c>
+      <c r="P8" s="16">
+        <f>P5*P10/1000</f>
+        <v/>
+      </c>
+      <c r="Q8" s="16">
+        <f>Q5*Q10/1000</f>
+        <v/>
+      </c>
+      <c r="R8" s="16">
+        <f>R5*R10/1000</f>
+        <v/>
+      </c>
+      <c r="S8" s="16">
+        <f>S5*S10/1000</f>
+        <v/>
+      </c>
+      <c r="T8" s="16">
+        <f>T5*T10/1000</f>
+        <v/>
+      </c>
+      <c r="U8" s="16">
+        <f>U5*U10/1000</f>
+        <v/>
+      </c>
+      <c r="V8" s="16">
+        <f>V5*V10/1000</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -5552,25 +12674,162 @@
           <t xml:space="preserve">    y/y</t>
         </is>
       </c>
-      <c r="Q9" s="29" t="n"/>
-      <c r="R9" s="29" t="n"/>
-      <c r="S9" s="29" t="n"/>
-      <c r="T9" s="29" t="n"/>
-      <c r="U9" s="29" t="n"/>
-      <c r="V9" s="29" t="n"/>
+      <c r="G9" s="10">
+        <f>G8/C8-1</f>
+        <v/>
+      </c>
+      <c r="H9" s="10">
+        <f>H8/D8-1</f>
+        <v/>
+      </c>
+      <c r="I9" s="10">
+        <f>I8/E8-1</f>
+        <v/>
+      </c>
+      <c r="J9" s="10">
+        <f>J8/F8-1</f>
+        <v/>
+      </c>
+      <c r="K9" s="10">
+        <f>K8/G8-1</f>
+        <v/>
+      </c>
+      <c r="L9" s="10">
+        <f>L8/H8-1</f>
+        <v/>
+      </c>
+      <c r="M9" s="10">
+        <f>M8/I8-1</f>
+        <v/>
+      </c>
+      <c r="N9" s="10">
+        <f>N8/J8-1</f>
+        <v/>
+      </c>
+      <c r="O9" s="10">
+        <f>O8/K8-1</f>
+        <v/>
+      </c>
+      <c r="P9" s="10">
+        <f>P8/L8-1</f>
+        <v/>
+      </c>
+      <c r="Q9" s="10">
+        <f>Q8/M8-1</f>
+        <v/>
+      </c>
+      <c r="R9" s="10">
+        <f>R8/N8-1</f>
+        <v/>
+      </c>
+      <c r="S9" s="10">
+        <f>S8/O8-1</f>
+        <v/>
+      </c>
+      <c r="T9" s="10">
+        <f>T8/P8-1</f>
+        <v/>
+      </c>
+      <c r="U9" s="10">
+        <f>U8/Q8-1</f>
+        <v/>
+      </c>
+      <c r="V9" s="10">
+        <f>V8/R8-1</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>ADR ($ = GBV / nights)</t>
         </is>
       </c>
-      <c r="Q10" s="29" t="n"/>
-      <c r="R10" s="29" t="n"/>
-      <c r="S10" s="29" t="n"/>
-      <c r="T10" s="29" t="n"/>
-      <c r="U10" s="29" t="n"/>
-      <c r="V10" s="29" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ADR_Engine: printed (A), engine path (E) — line 2</t>
+        </is>
+      </c>
+      <c r="C10" s="20">
+        <f>ADR_Engine!K7</f>
+        <v/>
+      </c>
+      <c r="D10" s="20">
+        <f>ADR_Engine!L7</f>
+        <v/>
+      </c>
+      <c r="E10" s="20">
+        <f>ADR_Engine!M7</f>
+        <v/>
+      </c>
+      <c r="F10" s="20">
+        <f>ADR_Engine!N7</f>
+        <v/>
+      </c>
+      <c r="G10" s="20">
+        <f>ADR_Engine!O7</f>
+        <v/>
+      </c>
+      <c r="H10" s="20">
+        <f>ADR_Engine!P7</f>
+        <v/>
+      </c>
+      <c r="I10" s="20">
+        <f>ADR_Engine!Q7</f>
+        <v/>
+      </c>
+      <c r="J10" s="20">
+        <f>ADR_Engine!R7</f>
+        <v/>
+      </c>
+      <c r="K10" s="20">
+        <f>ADR_Engine!S7</f>
+        <v/>
+      </c>
+      <c r="L10" s="20">
+        <f>ADR_Engine!T7</f>
+        <v/>
+      </c>
+      <c r="M10" s="20">
+        <f>ADR_Engine!U7</f>
+        <v/>
+      </c>
+      <c r="N10" s="20">
+        <f>ADR_Engine!V7</f>
+        <v/>
+      </c>
+      <c r="O10" s="20">
+        <f>ADR_Engine!W7</f>
+        <v/>
+      </c>
+      <c r="P10" s="20">
+        <f>ADR_Engine!X7</f>
+        <v/>
+      </c>
+      <c r="Q10" s="20">
+        <f>ADR_Engine!Y7</f>
+        <v/>
+      </c>
+      <c r="R10" s="20">
+        <f>ADR_Engine!Z7</f>
+        <v/>
+      </c>
+      <c r="S10" s="20">
+        <f>ADR_Engine!AA7</f>
+        <v/>
+      </c>
+      <c r="T10" s="20">
+        <f>ADR_Engine!AB7</f>
+        <v/>
+      </c>
+      <c r="U10" s="20">
+        <f>ADR_Engine!AC7</f>
+        <v/>
+      </c>
+      <c r="V10" s="20">
+        <f>ADR_Engine!AD7</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -5578,12 +12837,86 @@
           <t xml:space="preserve">    y/y</t>
         </is>
       </c>
-      <c r="Q11" s="29" t="n"/>
-      <c r="R11" s="29" t="n"/>
-      <c r="S11" s="29" t="n"/>
-      <c r="T11" s="29" t="n"/>
-      <c r="U11" s="29" t="n"/>
-      <c r="V11" s="29" t="n"/>
+      <c r="C11" s="30">
+        <f>ADR_Engine!K8</f>
+        <v/>
+      </c>
+      <c r="D11" s="30">
+        <f>ADR_Engine!L8</f>
+        <v/>
+      </c>
+      <c r="E11" s="30">
+        <f>ADR_Engine!M8</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
+        <f>ADR_Engine!N8</f>
+        <v/>
+      </c>
+      <c r="G11" s="10">
+        <f>G10/C10-1</f>
+        <v/>
+      </c>
+      <c r="H11" s="10">
+        <f>H10/D10-1</f>
+        <v/>
+      </c>
+      <c r="I11" s="10">
+        <f>I10/E10-1</f>
+        <v/>
+      </c>
+      <c r="J11" s="10">
+        <f>J10/F10-1</f>
+        <v/>
+      </c>
+      <c r="K11" s="10">
+        <f>K10/G10-1</f>
+        <v/>
+      </c>
+      <c r="L11" s="10">
+        <f>L10/H10-1</f>
+        <v/>
+      </c>
+      <c r="M11" s="10">
+        <f>M10/I10-1</f>
+        <v/>
+      </c>
+      <c r="N11" s="10">
+        <f>N10/J10-1</f>
+        <v/>
+      </c>
+      <c r="O11" s="10">
+        <f>O10/K10-1</f>
+        <v/>
+      </c>
+      <c r="P11" s="10">
+        <f>P10/L10-1</f>
+        <v/>
+      </c>
+      <c r="Q11" s="10">
+        <f>Q10/M10-1</f>
+        <v/>
+      </c>
+      <c r="R11" s="10">
+        <f>R10/N10-1</f>
+        <v/>
+      </c>
+      <c r="S11" s="10">
+        <f>S10/O10-1</f>
+        <v/>
+      </c>
+      <c r="T11" s="10">
+        <f>T10/P10-1</f>
+        <v/>
+      </c>
+      <c r="U11" s="10">
+        <f>U10/Q10-1</f>
+        <v/>
+      </c>
+      <c r="V11" s="10">
+        <f>V10/R10-1</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5591,12 +12924,12 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="Q12" s="29" t="n"/>
-      <c r="R12" s="29" t="n"/>
-      <c r="S12" s="29" t="n"/>
-      <c r="T12" s="29" t="n"/>
-      <c r="U12" s="29" t="n"/>
-      <c r="V12" s="29" t="n"/>
+      <c r="Q12" s="31" t="n"/>
+      <c r="R12" s="31" t="n"/>
+      <c r="S12" s="31" t="n"/>
+      <c r="T12" s="31" t="n"/>
+      <c r="U12" s="31" t="n"/>
+      <c r="V12" s="31" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -5604,12 +12937,12 @@
           <t xml:space="preserve">    y/y</t>
         </is>
       </c>
-      <c r="Q13" s="29" t="n"/>
-      <c r="R13" s="29" t="n"/>
-      <c r="S13" s="29" t="n"/>
-      <c r="T13" s="29" t="n"/>
-      <c r="U13" s="29" t="n"/>
-      <c r="V13" s="29" t="n"/>
+      <c r="Q13" s="31" t="n"/>
+      <c r="R13" s="31" t="n"/>
+      <c r="S13" s="31" t="n"/>
+      <c r="T13" s="31" t="n"/>
+      <c r="U13" s="31" t="n"/>
+      <c r="V13" s="31" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -5617,12 +12950,12 @@
           <t xml:space="preserve">    Take rate (revenue / GBV)</t>
         </is>
       </c>
-      <c r="Q14" s="29" t="n"/>
-      <c r="R14" s="29" t="n"/>
-      <c r="S14" s="29" t="n"/>
-      <c r="T14" s="29" t="n"/>
-      <c r="U14" s="29" t="n"/>
-      <c r="V14" s="29" t="n"/>
+      <c r="Q14" s="31" t="n"/>
+      <c r="R14" s="31" t="n"/>
+      <c r="S14" s="31" t="n"/>
+      <c r="T14" s="31" t="n"/>
+      <c r="U14" s="31" t="n"/>
+      <c r="V14" s="31" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -5630,12 +12963,12 @@
           <t xml:space="preserve">    Cost of revenue (cash)</t>
         </is>
       </c>
-      <c r="Q16" s="29" t="n"/>
-      <c r="R16" s="29" t="n"/>
-      <c r="S16" s="29" t="n"/>
-      <c r="T16" s="29" t="n"/>
-      <c r="U16" s="29" t="n"/>
-      <c r="V16" s="29" t="n"/>
+      <c r="Q16" s="31" t="n"/>
+      <c r="R16" s="31" t="n"/>
+      <c r="S16" s="31" t="n"/>
+      <c r="T16" s="31" t="n"/>
+      <c r="U16" s="31" t="n"/>
+      <c r="V16" s="31" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -5643,12 +12976,12 @@
           <t xml:space="preserve">    Operations &amp; support (cash)</t>
         </is>
       </c>
-      <c r="Q17" s="29" t="n"/>
-      <c r="R17" s="29" t="n"/>
-      <c r="S17" s="29" t="n"/>
-      <c r="T17" s="29" t="n"/>
-      <c r="U17" s="29" t="n"/>
-      <c r="V17" s="29" t="n"/>
+      <c r="Q17" s="31" t="n"/>
+      <c r="R17" s="31" t="n"/>
+      <c r="S17" s="31" t="n"/>
+      <c r="T17" s="31" t="n"/>
+      <c r="U17" s="31" t="n"/>
+      <c r="V17" s="31" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -5656,12 +12989,12 @@
           <t xml:space="preserve">    Product development (cash)</t>
         </is>
       </c>
-      <c r="Q18" s="29" t="n"/>
-      <c r="R18" s="29" t="n"/>
-      <c r="S18" s="29" t="n"/>
-      <c r="T18" s="29" t="n"/>
-      <c r="U18" s="29" t="n"/>
-      <c r="V18" s="29" t="n"/>
+      <c r="Q18" s="31" t="n"/>
+      <c r="R18" s="31" t="n"/>
+      <c r="S18" s="31" t="n"/>
+      <c r="T18" s="31" t="n"/>
+      <c r="U18" s="31" t="n"/>
+      <c r="V18" s="31" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -5669,12 +13002,12 @@
           <t xml:space="preserve">    Sales &amp; marketing (cash)</t>
         </is>
       </c>
-      <c r="Q19" s="29" t="n"/>
-      <c r="R19" s="29" t="n"/>
-      <c r="S19" s="29" t="n"/>
-      <c r="T19" s="29" t="n"/>
-      <c r="U19" s="29" t="n"/>
-      <c r="V19" s="29" t="n"/>
+      <c r="Q19" s="31" t="n"/>
+      <c r="R19" s="31" t="n"/>
+      <c r="S19" s="31" t="n"/>
+      <c r="T19" s="31" t="n"/>
+      <c r="U19" s="31" t="n"/>
+      <c r="V19" s="31" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -5682,12 +13015,12 @@
           <t xml:space="preserve">    General &amp; administrative (cash, ex lodging-tax reserves)</t>
         </is>
       </c>
-      <c r="Q20" s="29" t="n"/>
-      <c r="R20" s="29" t="n"/>
-      <c r="S20" s="29" t="n"/>
-      <c r="T20" s="29" t="n"/>
-      <c r="U20" s="29" t="n"/>
-      <c r="V20" s="29" t="n"/>
+      <c r="Q20" s="31" t="n"/>
+      <c r="R20" s="31" t="n"/>
+      <c r="S20" s="31" t="n"/>
+      <c r="T20" s="31" t="n"/>
+      <c r="U20" s="31" t="n"/>
+      <c r="V20" s="31" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -5695,12 +13028,12 @@
           <t>Total cash costs</t>
         </is>
       </c>
-      <c r="Q21" s="29" t="n"/>
-      <c r="R21" s="29" t="n"/>
-      <c r="S21" s="29" t="n"/>
-      <c r="T21" s="29" t="n"/>
-      <c r="U21" s="29" t="n"/>
-      <c r="V21" s="29" t="n"/>
+      <c r="Q21" s="31" t="n"/>
+      <c r="R21" s="31" t="n"/>
+      <c r="S21" s="31" t="n"/>
+      <c r="T21" s="31" t="n"/>
+      <c r="U21" s="31" t="n"/>
+      <c r="V21" s="31" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -5708,12 +13041,12 @@
           <t xml:space="preserve">    % of revenue</t>
         </is>
       </c>
-      <c r="Q22" s="29" t="n"/>
-      <c r="R22" s="29" t="n"/>
-      <c r="S22" s="29" t="n"/>
-      <c r="T22" s="29" t="n"/>
-      <c r="U22" s="29" t="n"/>
-      <c r="V22" s="29" t="n"/>
+      <c r="Q22" s="31" t="n"/>
+      <c r="R22" s="31" t="n"/>
+      <c r="S22" s="31" t="n"/>
+      <c r="T22" s="31" t="n"/>
+      <c r="U22" s="31" t="n"/>
+      <c r="V22" s="31" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -5721,12 +13054,12 @@
           <t xml:space="preserve">    Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="Q23" s="29" t="n"/>
-      <c r="R23" s="29" t="n"/>
-      <c r="S23" s="29" t="n"/>
-      <c r="T23" s="29" t="n"/>
-      <c r="U23" s="29" t="n"/>
-      <c r="V23" s="29" t="n"/>
+      <c r="Q23" s="31" t="n"/>
+      <c r="R23" s="31" t="n"/>
+      <c r="S23" s="31" t="n"/>
+      <c r="T23" s="31" t="n"/>
+      <c r="U23" s="31" t="n"/>
+      <c r="V23" s="31" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5734,12 +13067,12 @@
           <t>Adjusted EBITDA</t>
         </is>
       </c>
-      <c r="Q24" s="29" t="n"/>
-      <c r="R24" s="29" t="n"/>
-      <c r="S24" s="29" t="n"/>
-      <c r="T24" s="29" t="n"/>
-      <c r="U24" s="29" t="n"/>
-      <c r="V24" s="29" t="n"/>
+      <c r="Q24" s="31" t="n"/>
+      <c r="R24" s="31" t="n"/>
+      <c r="S24" s="31" t="n"/>
+      <c r="T24" s="31" t="n"/>
+      <c r="U24" s="31" t="n"/>
+      <c r="V24" s="31" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -5747,12 +13080,12 @@
           <t xml:space="preserve">    Adjusted EBITDA margin</t>
         </is>
       </c>
-      <c r="Q25" s="29" t="n"/>
-      <c r="R25" s="29" t="n"/>
-      <c r="S25" s="29" t="n"/>
-      <c r="T25" s="29" t="n"/>
-      <c r="U25" s="29" t="n"/>
-      <c r="V25" s="29" t="n"/>
+      <c r="Q25" s="31" t="n"/>
+      <c r="R25" s="31" t="n"/>
+      <c r="S25" s="31" t="n"/>
+      <c r="T25" s="31" t="n"/>
+      <c r="U25" s="31" t="n"/>
+      <c r="V25" s="31" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -5760,12 +13093,12 @@
           <t xml:space="preserve">    Stock-based compensation</t>
         </is>
       </c>
-      <c r="Q27" s="29" t="n"/>
-      <c r="R27" s="29" t="n"/>
-      <c r="S27" s="29" t="n"/>
-      <c r="T27" s="29" t="n"/>
-      <c r="U27" s="29" t="n"/>
-      <c r="V27" s="29" t="n"/>
+      <c r="Q27" s="31" t="n"/>
+      <c r="R27" s="31" t="n"/>
+      <c r="S27" s="31" t="n"/>
+      <c r="T27" s="31" t="n"/>
+      <c r="U27" s="31" t="n"/>
+      <c r="V27" s="31" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5773,12 +13106,12 @@
           <t>Operating income (GAAP)</t>
         </is>
       </c>
-      <c r="Q28" s="29" t="n"/>
-      <c r="R28" s="29" t="n"/>
-      <c r="S28" s="29" t="n"/>
-      <c r="T28" s="29" t="n"/>
-      <c r="U28" s="29" t="n"/>
-      <c r="V28" s="29" t="n"/>
+      <c r="Q28" s="31" t="n"/>
+      <c r="R28" s="31" t="n"/>
+      <c r="S28" s="31" t="n"/>
+      <c r="T28" s="31" t="n"/>
+      <c r="U28" s="31" t="n"/>
+      <c r="V28" s="31" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -5786,12 +13119,12 @@
           <t xml:space="preserve">    Interest income</t>
         </is>
       </c>
-      <c r="Q29" s="29" t="n"/>
-      <c r="R29" s="29" t="n"/>
-      <c r="S29" s="29" t="n"/>
-      <c r="T29" s="29" t="n"/>
-      <c r="U29" s="29" t="n"/>
-      <c r="V29" s="29" t="n"/>
+      <c r="Q29" s="31" t="n"/>
+      <c r="R29" s="31" t="n"/>
+      <c r="S29" s="31" t="n"/>
+      <c r="T29" s="31" t="n"/>
+      <c r="U29" s="31" t="n"/>
+      <c r="V29" s="31" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -5799,12 +13132,12 @@
           <t xml:space="preserve">    Interest expense</t>
         </is>
       </c>
-      <c r="Q30" s="29" t="n"/>
-      <c r="R30" s="29" t="n"/>
-      <c r="S30" s="29" t="n"/>
-      <c r="T30" s="29" t="n"/>
-      <c r="U30" s="29" t="n"/>
-      <c r="V30" s="29" t="n"/>
+      <c r="Q30" s="31" t="n"/>
+      <c r="R30" s="31" t="n"/>
+      <c r="S30" s="31" t="n"/>
+      <c r="T30" s="31" t="n"/>
+      <c r="U30" s="31" t="n"/>
+      <c r="V30" s="31" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -5812,12 +13145,12 @@
           <t xml:space="preserve">    Other income / (expense), net</t>
         </is>
       </c>
-      <c r="Q31" s="29" t="n"/>
-      <c r="R31" s="29" t="n"/>
-      <c r="S31" s="29" t="n"/>
-      <c r="T31" s="29" t="n"/>
-      <c r="U31" s="29" t="n"/>
-      <c r="V31" s="29" t="n"/>
+      <c r="Q31" s="31" t="n"/>
+      <c r="R31" s="31" t="n"/>
+      <c r="S31" s="31" t="n"/>
+      <c r="T31" s="31" t="n"/>
+      <c r="U31" s="31" t="n"/>
+      <c r="V31" s="31" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5825,12 +13158,12 @@
           <t>Pre-tax income</t>
         </is>
       </c>
-      <c r="Q32" s="29" t="n"/>
-      <c r="R32" s="29" t="n"/>
-      <c r="S32" s="29" t="n"/>
-      <c r="T32" s="29" t="n"/>
-      <c r="U32" s="29" t="n"/>
-      <c r="V32" s="29" t="n"/>
+      <c r="Q32" s="31" t="n"/>
+      <c r="R32" s="31" t="n"/>
+      <c r="S32" s="31" t="n"/>
+      <c r="T32" s="31" t="n"/>
+      <c r="U32" s="31" t="n"/>
+      <c r="V32" s="31" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -5838,12 +13171,12 @@
           <t xml:space="preserve">    Income tax</t>
         </is>
       </c>
-      <c r="Q33" s="29" t="n"/>
-      <c r="R33" s="29" t="n"/>
-      <c r="S33" s="29" t="n"/>
-      <c r="T33" s="29" t="n"/>
-      <c r="U33" s="29" t="n"/>
-      <c r="V33" s="29" t="n"/>
+      <c r="Q33" s="31" t="n"/>
+      <c r="R33" s="31" t="n"/>
+      <c r="S33" s="31" t="n"/>
+      <c r="T33" s="31" t="n"/>
+      <c r="U33" s="31" t="n"/>
+      <c r="V33" s="31" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -5851,12 +13184,12 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="Q34" s="29" t="n"/>
-      <c r="R34" s="29" t="n"/>
-      <c r="S34" s="29" t="n"/>
-      <c r="T34" s="29" t="n"/>
-      <c r="U34" s="29" t="n"/>
-      <c r="V34" s="29" t="n"/>
+      <c r="Q34" s="31" t="n"/>
+      <c r="R34" s="31" t="n"/>
+      <c r="S34" s="31" t="n"/>
+      <c r="T34" s="31" t="n"/>
+      <c r="U34" s="31" t="n"/>
+      <c r="V34" s="31" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -5864,12 +13197,12 @@
           <t xml:space="preserve">    Diluted shares (m)</t>
         </is>
       </c>
-      <c r="Q35" s="29" t="n"/>
-      <c r="R35" s="29" t="n"/>
-      <c r="S35" s="29" t="n"/>
-      <c r="T35" s="29" t="n"/>
-      <c r="U35" s="29" t="n"/>
-      <c r="V35" s="29" t="n"/>
+      <c r="Q35" s="31" t="n"/>
+      <c r="R35" s="31" t="n"/>
+      <c r="S35" s="31" t="n"/>
+      <c r="T35" s="31" t="n"/>
+      <c r="U35" s="31" t="n"/>
+      <c r="V35" s="31" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -5877,25 +13210,25 @@
           <t>Diluted EPS ($)</t>
         </is>
       </c>
-      <c r="Q36" s="29" t="n"/>
-      <c r="R36" s="29" t="n"/>
-      <c r="S36" s="29" t="n"/>
-      <c r="T36" s="29" t="n"/>
-      <c r="U36" s="29" t="n"/>
-      <c r="V36" s="29" t="n"/>
+      <c r="Q36" s="31" t="n"/>
+      <c r="R36" s="31" t="n"/>
+      <c r="S36" s="31" t="n"/>
+      <c r="T36" s="31" t="n"/>
+      <c r="U36" s="31" t="n"/>
+      <c r="V36" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6099,6 +13432,159 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>ADR, ex-FX ADR, FX effect (letters)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>data/processed/overnight/02_kpi_panel_quarterly.csv (adr_usd, adr_yoy_exfx_pct, fx_pts_adr)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>X1 §2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Daily FX (FRED H.10, 9 bilaterals + broad dollar)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>data/processed/pitch_model_v2/adr_engine/fx_daily_2026-09-21.csv (fetch_fx.py)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>adr_fx_prereg §1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Destination-currency baskets κ</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>data/processed/forecast_methods/fx_lag_v2/01b_basket_weights_used.csv (judgement, frozen)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>adr_fx_prereg §2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Regional GBV shares (10-K Geographic Mix)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>data/processed/adr/01_regional_annual.csv gbv_share_pct</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>adr_fx_prereg §2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Ex-FX decomposition history</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>data/processed/q3nowcast/H/adr_history_components.csv; adrq3/I/I_mix_terms_3q26.csv; adrv3/K/K4_*</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>D4, adr_v1_design §3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Bundle ADR contribution (~1pp, transcript-only)</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>ledger D014 (4Q25 call), D032 (1Q26 call); filed substitute D031 'roughly 20% of GBV from RNPL'</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>adr_v1_design §3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Regional ADR levels and shares</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>data/processed/adr/04_regional_quarterly_wide.csv (disclosed-chained)</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>adr_v1_design §3.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Street ADR</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Bloomberg MODL screenshot 12 Sep 2026 (3Q26 n 26, 4Q26 n 25)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>DEC-0005 / V1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>ADR engine outputs</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>data/processed/pitch_model_v2/adr_engine/ (fx_scores.csv, fx_forecast_asof.csv, adr_path.csv, …)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>adr_fx_prereg §9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/model/ABNB_official_model.xlsx
+++ b/model/ABNB_official_model.xlsx
@@ -787,7 +787,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$129:$AD$129</f>
+              <f>'ADR_Engine'!$O$130:$AD$130</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -818,7 +818,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$130:$AD$130</f>
+              <f>'ADR_Engine'!$O$131:$AD$131</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -906,7 +906,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$131:$AD$131</f>
+              <f>'ADR_Engine'!$O$132:$AD$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -937,7 +937,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$132:$AD$132</f>
+              <f>'ADR_Engine'!$O$133:$AD$133</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1076,7 +1076,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>133</row>
+      <row>134</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="2880000"/>
@@ -1098,7 +1098,7 @@
     <from>
       <col>13</col>
       <colOff>0</colOff>
-      <row>133</row>
+      <row>134</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="2880000"/>
@@ -5365,7 +5365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD132"/>
+  <dimension ref="A1:AD133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -11684,418 +11684,461 @@
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>card v3: last_q residual carry, no lap (card geo)</t>
+          <t>lap-only (K4 residual steps): every 2025-26 residual step laps at its anniversary</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>3.69126637648649</v>
+        <v>2.910732193880174</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>178.3241057148202</v>
+        <v>176.9871287134339</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>26.17797871893561</v>
+        <v>25.9817104951321</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>3.69126637648649</v>
+        <v>1.990747787585442</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>174.5536872915614</v>
+        <v>171.7051486032933</v>
       </c>
       <c r="H122" s="11" t="n">
-        <v>23.0061759850278</v>
+        <v>22.63073858591405</v>
       </c>
       <c r="I122" s="11" t="n">
-        <v>3.60883637648649</v>
+        <v>0.9435507506529328</v>
       </c>
       <c r="J122" s="11" t="n">
-        <v>192.8726371265034</v>
+        <v>187.8933505203212</v>
       </c>
       <c r="K122" s="11" t="n">
-        <v>32.59933312712161</v>
+        <v>31.75773410494469</v>
       </c>
       <c r="L122" s="11" t="n">
-        <v>3.60883637648649</v>
+        <v>1.013196673597509</v>
       </c>
       <c r="M122" s="11" t="n">
-        <v>189.5761052869207</v>
+        <v>184.8071364608028</v>
       </c>
       <c r="N122" s="11" t="n">
-        <v>29.78240614057524</v>
+        <v>29.03320113799212</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>full lap: ex-NA RNPL sized at the 1H26 residual steps</t>
+          <t>card v3: last_q residual carry, no lap (card geo)</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>3.315947459255554</v>
+        <v>3.69126637648649</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>177.6812219414954</v>
+        <v>178.3241057148202</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>26.08360338101152</v>
+        <v>26.17797871893561</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>2.784074164071932</v>
+        <v>3.69126637648649</v>
       </c>
       <c r="G123" s="11" t="n">
-        <v>173.0340496165458</v>
+        <v>174.5536872915614</v>
       </c>
       <c r="H123" s="11" t="n">
-        <v>22.80588773946074</v>
+        <v>23.0061759850278</v>
       </c>
       <c r="I123" s="11" t="n">
-        <v>1.956877127139422</v>
+        <v>3.60883637648649</v>
       </c>
       <c r="J123" s="11" t="n">
-        <v>189.7864468568733</v>
+        <v>192.8726371265034</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>32.07770524774872</v>
+        <v>32.59933312712161</v>
       </c>
       <c r="L123" s="11" t="n">
-        <v>1.806523050083998</v>
+        <v>3.60883637648649</v>
       </c>
       <c r="M123" s="11" t="n">
-        <v>186.2647150123214</v>
+        <v>189.5761052869207</v>
       </c>
       <c r="N123" s="11" t="n">
-        <v>29.2621867284357</v>
+        <v>29.78240614057524</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>core mean reversion to the 2023-25 mean</t>
+          <t>full lap: ex-NA RNPL sized at the 1H26 residual steps</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1.864621082769064</v>
+        <v>3.315947459255554</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>175.1952449912116</v>
+        <v>177.6812219414954</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>25.71866196470987</v>
+        <v>26.08360338101152</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1.332747787585442</v>
+        <v>2.784074164071932</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>170.6029328032933</v>
+        <v>173.0340496165458</v>
       </c>
       <c r="H124" s="11" t="n">
-        <v>22.48546654347406</v>
+        <v>22.80588773946074</v>
       </c>
       <c r="I124" s="11" t="n">
-        <v>0.9655507506529332</v>
+        <v>1.956877127139422</v>
       </c>
       <c r="J124" s="11" t="n">
-        <v>187.9344509203212</v>
+        <v>189.7864468568733</v>
       </c>
       <c r="K124" s="11" t="n">
-        <v>31.7646808945527</v>
+        <v>32.07770524774872</v>
       </c>
       <c r="L124" s="11" t="n">
-        <v>1.505196673597509</v>
+        <v>1.806523050083998</v>
       </c>
       <c r="M124" s="11" t="n">
-        <v>185.7110880608028</v>
+        <v>186.2647150123214</v>
       </c>
       <c r="N124" s="11" t="n">
-        <v>29.17521193435212</v>
+        <v>29.2621867284357</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>AR(1) on core (K4 rho 0.747)</t>
+          <t>core mean reversion to the 2023-25 mean</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>3.092067886004471</v>
+        <v>1.864621082769064</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>177.2977386204736</v>
+        <v>175.1952449912116</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>26.02730802948552</v>
+        <v>25.71866196470987</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>2.392956549602292</v>
+        <v>1.332747787585442</v>
       </c>
       <c r="G125" s="11" t="n">
-        <v>172.3788885005477</v>
+        <v>170.6029328032933</v>
       </c>
       <c r="H125" s="11" t="n">
-        <v>22.71953750437219</v>
+        <v>22.48546654347406</v>
       </c>
       <c r="I125" s="11" t="n">
-        <v>1.90083269587952</v>
+        <v>0.9655507506529332</v>
       </c>
       <c r="J125" s="11" t="n">
-        <v>189.6817446503935</v>
+        <v>187.9344509203212</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>32.06000848080952</v>
+        <v>31.7646808945527</v>
       </c>
       <c r="L125" s="11" t="n">
-        <v>2.347158286681769</v>
+        <v>1.505196673597509</v>
       </c>
       <c r="M125" s="11" t="n">
-        <v>187.2580241325226</v>
+        <v>185.7110880608028</v>
       </c>
       <c r="N125" s="11" t="n">
-        <v>29.41823559121929</v>
+        <v>29.17521193435212</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
+          <t>AR(1) on core (K4 rho 0.747)</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>3.092067886004471</v>
+      </c>
+      <c r="D126" s="11" t="n">
+        <v>177.2977386204736</v>
+      </c>
+      <c r="E126" s="11" t="n">
+        <v>26.02730802948552</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>2.392956549602292</v>
+      </c>
+      <c r="G126" s="11" t="n">
+        <v>172.3788885005477</v>
+      </c>
+      <c r="H126" s="11" t="n">
+        <v>22.71953750437219</v>
+      </c>
+      <c r="I126" s="11" t="n">
+        <v>1.90083269587952</v>
+      </c>
+      <c r="J126" s="11" t="n">
+        <v>189.6817446503935</v>
+      </c>
+      <c r="K126" s="11" t="n">
+        <v>32.06000848080952</v>
+      </c>
+      <c r="L126" s="11" t="n">
+        <v>2.347158286681769</v>
+      </c>
+      <c r="M126" s="11" t="n">
+        <v>187.2580241325226</v>
+      </c>
+      <c r="N126" s="11" t="n">
+        <v>29.41823559121929</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
           <t>base + fee-migration K line (DEC-0008 sensitivity)</t>
         </is>
       </c>
-      <c r="C126" s="11" t="n">
+      <c r="C127" s="11" t="n">
         <v>3.487447459255554</v>
       </c>
-      <c r="D126" s="11" t="n">
+      <c r="D127" s="11" t="n">
         <v>177.9749842914954</v>
       </c>
-      <c r="E126" s="11" t="n">
+      <c r="E127" s="11" t="n">
         <v>26.12672769399152</v>
       </c>
-      <c r="F126" s="11" t="n">
+      <c r="F127" s="11" t="n">
         <v>3.158574164071932</v>
       </c>
-      <c r="G126" s="11" t="n">
+      <c r="G127" s="11" t="n">
         <v>173.6613745665458</v>
       </c>
-      <c r="H126" s="11" t="n">
+      <c r="H127" s="11" t="n">
         <v>22.88856916787073</v>
       </c>
-      <c r="I126" s="11" t="n">
+      <c r="I127" s="11" t="n">
         <v>2.761977127139422</v>
       </c>
-      <c r="J126" s="11" t="n">
+      <c r="J127" s="11" t="n">
         <v>191.2905346768732</v>
       </c>
-      <c r="K126" s="11" t="n">
+      <c r="K127" s="11" t="n">
         <v>32.33192617108512</v>
       </c>
-      <c r="L126" s="11" t="n">
+      <c r="L127" s="11" t="n">
         <v>3.267323050083998</v>
       </c>
-      <c r="M126" s="11" t="n">
+      <c r="M127" s="11" t="n">
         <v>188.9486428523214</v>
       </c>
-      <c r="N126" s="11" t="n">
+      <c r="N127" s="11" t="n">
         <v>29.6838317920997</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="8" t="inlineStr">
-        <is>
-          <t>chart helper: ADR $ (printed, then engine)</t>
-        </is>
-      </c>
-      <c r="O129" s="20">
-        <f>O7</f>
-        <v/>
-      </c>
-      <c r="P129" s="20">
-        <f>P7</f>
-        <v/>
-      </c>
-      <c r="Q129" s="20">
-        <f>Q7</f>
-        <v/>
-      </c>
-      <c r="R129" s="20">
-        <f>R7</f>
-        <v/>
-      </c>
-      <c r="S129" s="20">
-        <f>S7</f>
-        <v/>
-      </c>
-      <c r="T129" s="20">
-        <f>T7</f>
-        <v/>
-      </c>
-      <c r="U129" s="20">
-        <f>U7</f>
-        <v/>
-      </c>
-      <c r="V129" s="20">
-        <f>V7</f>
-        <v/>
-      </c>
-      <c r="W129" s="20">
-        <f>W7</f>
-        <v/>
-      </c>
-      <c r="X129" s="20">
-        <f>X7</f>
-        <v/>
-      </c>
-      <c r="Y129" s="20">
-        <f>Y7</f>
-        <v/>
-      </c>
-      <c r="Z129" s="20">
-        <f>Z7</f>
-        <v/>
-      </c>
-      <c r="AA129" s="20">
-        <f>AA7</f>
-        <v/>
-      </c>
-      <c r="AB129" s="20">
-        <f>AB7</f>
-        <v/>
-      </c>
-      <c r="AC129" s="20">
-        <f>AC7</f>
-        <v/>
-      </c>
-      <c r="AD129" s="20">
-        <f>AD7</f>
-        <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t>chart helper: Street ADR $</t>
-        </is>
+          <t>chart helper: ADR $ (printed, then engine)</t>
+        </is>
+      </c>
+      <c r="O130" s="20">
+        <f>O7</f>
+        <v/>
+      </c>
+      <c r="P130" s="20">
+        <f>P7</f>
+        <v/>
+      </c>
+      <c r="Q130" s="20">
+        <f>Q7</f>
+        <v/>
+      </c>
+      <c r="R130" s="20">
+        <f>R7</f>
+        <v/>
+      </c>
+      <c r="S130" s="20">
+        <f>S7</f>
+        <v/>
+      </c>
+      <c r="T130" s="20">
+        <f>T7</f>
+        <v/>
+      </c>
+      <c r="U130" s="20">
+        <f>U7</f>
+        <v/>
+      </c>
+      <c r="V130" s="20">
+        <f>V7</f>
+        <v/>
+      </c>
+      <c r="W130" s="20">
+        <f>W7</f>
+        <v/>
+      </c>
+      <c r="X130" s="20">
+        <f>X7</f>
+        <v/>
       </c>
       <c r="Y130" s="20">
-        <f>Y100</f>
+        <f>Y7</f>
         <v/>
       </c>
       <c r="Z130" s="20">
-        <f>Z100</f>
+        <f>Z7</f>
+        <v/>
+      </c>
+      <c r="AA130" s="20">
+        <f>AA7</f>
+        <v/>
+      </c>
+      <c r="AB130" s="20">
+        <f>AB7</f>
+        <v/>
+      </c>
+      <c r="AC130" s="20">
+        <f>AC7</f>
+        <v/>
+      </c>
+      <c r="AD130" s="20">
+        <f>AD7</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>chart helper: FX identity (pp)</t>
-        </is>
-      </c>
-      <c r="O131" s="20">
-        <f>O51</f>
-        <v/>
-      </c>
-      <c r="P131" s="20">
-        <f>P51</f>
-        <v/>
-      </c>
-      <c r="Q131" s="20">
-        <f>Q51</f>
-        <v/>
-      </c>
-      <c r="R131" s="20">
-        <f>R51</f>
-        <v/>
-      </c>
-      <c r="S131" s="20">
-        <f>S51</f>
-        <v/>
-      </c>
-      <c r="T131" s="20">
-        <f>T51</f>
-        <v/>
-      </c>
-      <c r="U131" s="20">
-        <f>U51</f>
-        <v/>
-      </c>
-      <c r="V131" s="20">
-        <f>V51</f>
-        <v/>
-      </c>
-      <c r="W131" s="20">
-        <f>W51</f>
-        <v/>
-      </c>
-      <c r="X131" s="20">
-        <f>X51</f>
-        <v/>
+          <t>chart helper: Street ADR $</t>
+        </is>
       </c>
       <c r="Y131" s="20">
-        <f>Y51</f>
+        <f>Y100</f>
         <v/>
       </c>
       <c r="Z131" s="20">
-        <f>Z51</f>
-        <v/>
-      </c>
-      <c r="AA131" s="20">
-        <f>AA51</f>
-        <v/>
-      </c>
-      <c r="AB131" s="20">
-        <f>AB51</f>
-        <v/>
-      </c>
-      <c r="AC131" s="20">
-        <f>AC51</f>
-        <v/>
-      </c>
-      <c r="AD131" s="20">
-        <f>AD51</f>
+        <f>Z100</f>
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
         <is>
+          <t>chart helper: FX identity (pp)</t>
+        </is>
+      </c>
+      <c r="O132" s="20">
+        <f>O51</f>
+        <v/>
+      </c>
+      <c r="P132" s="20">
+        <f>P51</f>
+        <v/>
+      </c>
+      <c r="Q132" s="20">
+        <f>Q51</f>
+        <v/>
+      </c>
+      <c r="R132" s="20">
+        <f>R51</f>
+        <v/>
+      </c>
+      <c r="S132" s="20">
+        <f>S51</f>
+        <v/>
+      </c>
+      <c r="T132" s="20">
+        <f>T51</f>
+        <v/>
+      </c>
+      <c r="U132" s="20">
+        <f>U51</f>
+        <v/>
+      </c>
+      <c r="V132" s="20">
+        <f>V51</f>
+        <v/>
+      </c>
+      <c r="W132" s="20">
+        <f>W51</f>
+        <v/>
+      </c>
+      <c r="X132" s="20">
+        <f>X51</f>
+        <v/>
+      </c>
+      <c r="Y132" s="20">
+        <f>Y51</f>
+        <v/>
+      </c>
+      <c r="Z132" s="20">
+        <f>Z51</f>
+        <v/>
+      </c>
+      <c r="AA132" s="20">
+        <f>AA51</f>
+        <v/>
+      </c>
+      <c r="AB132" s="20">
+        <f>AB51</f>
+        <v/>
+      </c>
+      <c r="AC132" s="20">
+        <f>AC51</f>
+        <v/>
+      </c>
+      <c r="AD132" s="20">
+        <f>AD51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
           <t>chart helper: disclosed FX (pp)</t>
         </is>
       </c>
-      <c r="O132" s="20">
+      <c r="O133" s="20">
         <f>O10</f>
         <v/>
       </c>
-      <c r="P132" s="20">
+      <c r="P133" s="20">
         <f>P10</f>
         <v/>
       </c>
-      <c r="Q132" s="20">
+      <c r="Q133" s="20">
         <f>Q10</f>
         <v/>
       </c>
-      <c r="R132" s="20">
+      <c r="R133" s="20">
         <f>R10</f>
         <v/>
       </c>
-      <c r="S132" s="20">
+      <c r="S133" s="20">
         <f>S10</f>
         <v/>
       </c>
-      <c r="T132" s="20">
+      <c r="T133" s="20">
         <f>T10</f>
         <v/>
       </c>
-      <c r="U132" s="20">
+      <c r="U133" s="20">
         <f>U10</f>
         <v/>
       </c>
-      <c r="V132" s="20">
+      <c r="V133" s="20">
         <f>V10</f>
         <v/>
       </c>
-      <c r="W132" s="20">
+      <c r="W133" s="20">
         <f>W10</f>
         <v/>
       </c>
-      <c r="X132" s="20">
+      <c r="X133" s="20">
         <f>X10</f>
         <v/>
       </c>

--- a/model/ABNB_official_model.xlsx
+++ b/model/ABNB_official_model.xlsx
@@ -787,7 +787,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$130:$AD$130</f>
+              <f>'ADR_Engine'!$O$132:$AD$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -818,7 +818,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$131:$AD$131</f>
+              <f>'ADR_Engine'!$O$133:$AD$133</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -906,7 +906,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$132:$AD$132</f>
+              <f>'ADR_Engine'!$O$134:$AD$134</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -937,7 +937,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$133:$AD$133</f>
+              <f>'ADR_Engine'!$O$135:$AD$135</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1076,7 +1076,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>134</row>
+      <row>136</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="2880000"/>
@@ -1098,7 +1098,7 @@
     <from>
       <col>13</col>
       <colOff>0</colOff>
-      <row>134</row>
+      <row>136</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="2880000"/>
@@ -5365,7 +5365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD133"/>
+  <dimension ref="A1:AD135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -11684,461 +11684,547 @@
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>lap-only (K4 residual steps): every 2025-26 residual step laps at its anniversary</t>
+          <t>base + sub-regional country mix (v2 H3, Inside Airbnb panel)</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>2.910732193880174</v>
+        <v>3.182081964103476</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>176.9871287134339</v>
+        <v>177.4519237348494</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>25.9817104951321</v>
+        <v>26.04994240427589</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1.990747787585442</v>
+        <v>2.640676678321757</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>171.7051486032933</v>
+        <v>172.7938444881657</v>
       </c>
       <c r="H122" s="11" t="n">
-        <v>22.63073858591405</v>
+        <v>22.77422870354024</v>
       </c>
       <c r="I122" s="11" t="n">
-        <v>0.9435507506529328</v>
+        <v>2.265309708688182</v>
       </c>
       <c r="J122" s="11" t="n">
-        <v>187.8933505203212</v>
+        <v>190.3626606057227</v>
       </c>
       <c r="K122" s="11" t="n">
-        <v>31.75773410494469</v>
+        <v>32.17509689557925</v>
       </c>
       <c r="L122" s="11" t="n">
-        <v>1.013196673597509</v>
+        <v>2.795333000538972</v>
       </c>
       <c r="M122" s="11" t="n">
-        <v>184.8071364608028</v>
+        <v>188.0814555342924</v>
       </c>
       <c r="N122" s="11" t="n">
-        <v>29.03320113799212</v>
+        <v>29.54759666443733</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>card v3: last_q residual carry, no lap (card geo)</t>
+          <t>base + sub-regional + composition tilt B (EMEA 5 / LatAm 30 / APAC 25)</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>3.69126637648649</v>
+        <v>2.800767198387953</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>178.3241057148202</v>
+        <v>176.7987696726552</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>26.17797871893561</v>
+        <v>25.95405938794579</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>3.69126637648649</v>
+        <v>2.276405895791162</v>
       </c>
       <c r="G123" s="11" t="n">
-        <v>174.5536872915614</v>
+        <v>172.1836545003487</v>
       </c>
       <c r="H123" s="11" t="n">
-        <v>23.0061759850278</v>
+        <v>22.69380566314596</v>
       </c>
       <c r="I123" s="11" t="n">
-        <v>3.60883637648649</v>
+        <v>1.845411024644575</v>
       </c>
       <c r="J123" s="11" t="n">
-        <v>192.8726371265034</v>
+        <v>189.5782058841924</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>32.59933312712161</v>
+        <v>32.0425083585462</v>
       </c>
       <c r="L123" s="11" t="n">
-        <v>3.60883637648649</v>
+        <v>2.514402127934693</v>
       </c>
       <c r="M123" s="11" t="n">
-        <v>189.5761052869207</v>
+        <v>187.5653012420565</v>
       </c>
       <c r="N123" s="11" t="n">
-        <v>29.78240614057524</v>
+        <v>29.46650882512708</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>full lap: ex-NA RNPL sized at the 1H26 residual steps</t>
+          <t>lap-only (K4 residual steps): every 2025-26 residual step laps at its anniversary</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>3.315947459255554</v>
+        <v>2.910732193880174</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>177.6812219414954</v>
+        <v>176.9871287134339</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>26.08360338101152</v>
+        <v>25.9817104951321</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>2.784074164071932</v>
+        <v>1.990747787585442</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>173.0340496165458</v>
+        <v>171.7051486032933</v>
       </c>
       <c r="H124" s="11" t="n">
-        <v>22.80588773946074</v>
+        <v>22.63073858591405</v>
       </c>
       <c r="I124" s="11" t="n">
-        <v>1.956877127139422</v>
+        <v>0.9435507506529328</v>
       </c>
       <c r="J124" s="11" t="n">
-        <v>189.7864468568733</v>
+        <v>187.8933505203212</v>
       </c>
       <c r="K124" s="11" t="n">
-        <v>32.07770524774872</v>
+        <v>31.75773410494469</v>
       </c>
       <c r="L124" s="11" t="n">
-        <v>1.806523050083998</v>
+        <v>1.013196673597509</v>
       </c>
       <c r="M124" s="11" t="n">
-        <v>186.2647150123214</v>
+        <v>184.8071364608028</v>
       </c>
       <c r="N124" s="11" t="n">
-        <v>29.2621867284357</v>
+        <v>29.03320113799212</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>core mean reversion to the 2023-25 mean</t>
+          <t>card v3: last_q residual carry, no lap (card geo)</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>1.864621082769064</v>
+        <v>3.69126637648649</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>175.1952449912116</v>
+        <v>178.3241057148202</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>25.71866196470987</v>
+        <v>26.17797871893561</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1.332747787585442</v>
+        <v>3.69126637648649</v>
       </c>
       <c r="G125" s="11" t="n">
-        <v>170.6029328032933</v>
+        <v>174.5536872915614</v>
       </c>
       <c r="H125" s="11" t="n">
-        <v>22.48546654347406</v>
+        <v>23.0061759850278</v>
       </c>
       <c r="I125" s="11" t="n">
-        <v>0.9655507506529332</v>
+        <v>3.60883637648649</v>
       </c>
       <c r="J125" s="11" t="n">
-        <v>187.9344509203212</v>
+        <v>192.8726371265034</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>31.7646808945527</v>
+        <v>32.59933312712161</v>
       </c>
       <c r="L125" s="11" t="n">
-        <v>1.505196673597509</v>
+        <v>3.60883637648649</v>
       </c>
       <c r="M125" s="11" t="n">
-        <v>185.7110880608028</v>
+        <v>189.5761052869207</v>
       </c>
       <c r="N125" s="11" t="n">
-        <v>29.17521193435212</v>
+        <v>29.78240614057524</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>AR(1) on core (K4 rho 0.747)</t>
+          <t>full lap: ex-NA RNPL sized at the 1H26 residual steps</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>3.092067886004471</v>
+        <v>3.315947459255554</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>177.2977386204736</v>
+        <v>177.6812219414954</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>26.02730802948552</v>
+        <v>26.08360338101152</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>2.392956549602292</v>
+        <v>2.784074164071932</v>
       </c>
       <c r="G126" s="11" t="n">
-        <v>172.3788885005477</v>
+        <v>173.0340496165458</v>
       </c>
       <c r="H126" s="11" t="n">
-        <v>22.71953750437219</v>
+        <v>22.80588773946074</v>
       </c>
       <c r="I126" s="11" t="n">
-        <v>1.90083269587952</v>
+        <v>1.956877127139422</v>
       </c>
       <c r="J126" s="11" t="n">
-        <v>189.6817446503935</v>
+        <v>189.7864468568733</v>
       </c>
       <c r="K126" s="11" t="n">
-        <v>32.06000848080952</v>
+        <v>32.07770524774872</v>
       </c>
       <c r="L126" s="11" t="n">
-        <v>2.347158286681769</v>
+        <v>1.806523050083998</v>
       </c>
       <c r="M126" s="11" t="n">
-        <v>187.2580241325226</v>
+        <v>186.2647150123214</v>
       </c>
       <c r="N126" s="11" t="n">
-        <v>29.41823559121929</v>
+        <v>29.2621867284357</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
+          <t>core mean reversion to the 2023-25 mean</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="n">
+        <v>1.864621082769064</v>
+      </c>
+      <c r="D127" s="11" t="n">
+        <v>175.1952449912116</v>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v>25.71866196470987</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>1.332747787585442</v>
+      </c>
+      <c r="G127" s="11" t="n">
+        <v>170.6029328032933</v>
+      </c>
+      <c r="H127" s="11" t="n">
+        <v>22.48546654347406</v>
+      </c>
+      <c r="I127" s="11" t="n">
+        <v>0.9655507506529332</v>
+      </c>
+      <c r="J127" s="11" t="n">
+        <v>187.9344509203212</v>
+      </c>
+      <c r="K127" s="11" t="n">
+        <v>31.7646808945527</v>
+      </c>
+      <c r="L127" s="11" t="n">
+        <v>1.505196673597509</v>
+      </c>
+      <c r="M127" s="11" t="n">
+        <v>185.7110880608028</v>
+      </c>
+      <c r="N127" s="11" t="n">
+        <v>29.17521193435212</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>AR(1) on core (K4 rho 0.747)</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="n">
+        <v>3.092067886004471</v>
+      </c>
+      <c r="D128" s="11" t="n">
+        <v>177.2977386204736</v>
+      </c>
+      <c r="E128" s="11" t="n">
+        <v>26.02730802948552</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>2.392956549602292</v>
+      </c>
+      <c r="G128" s="11" t="n">
+        <v>172.3788885005477</v>
+      </c>
+      <c r="H128" s="11" t="n">
+        <v>22.71953750437219</v>
+      </c>
+      <c r="I128" s="11" t="n">
+        <v>1.90083269587952</v>
+      </c>
+      <c r="J128" s="11" t="n">
+        <v>189.6817446503935</v>
+      </c>
+      <c r="K128" s="11" t="n">
+        <v>32.06000848080952</v>
+      </c>
+      <c r="L128" s="11" t="n">
+        <v>2.347158286681769</v>
+      </c>
+      <c r="M128" s="11" t="n">
+        <v>187.2580241325226</v>
+      </c>
+      <c r="N128" s="11" t="n">
+        <v>29.41823559121929</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
           <t>base + fee-migration K line (DEC-0008 sensitivity)</t>
         </is>
       </c>
-      <c r="C127" s="11" t="n">
+      <c r="C129" s="11" t="n">
         <v>3.487447459255554</v>
       </c>
-      <c r="D127" s="11" t="n">
+      <c r="D129" s="11" t="n">
         <v>177.9749842914954</v>
       </c>
-      <c r="E127" s="11" t="n">
+      <c r="E129" s="11" t="n">
         <v>26.12672769399152</v>
       </c>
-      <c r="F127" s="11" t="n">
+      <c r="F129" s="11" t="n">
         <v>3.158574164071932</v>
       </c>
-      <c r="G127" s="11" t="n">
+      <c r="G129" s="11" t="n">
         <v>173.6613745665458</v>
       </c>
-      <c r="H127" s="11" t="n">
+      <c r="H129" s="11" t="n">
         <v>22.88856916787073</v>
       </c>
-      <c r="I127" s="11" t="n">
+      <c r="I129" s="11" t="n">
         <v>2.761977127139422</v>
       </c>
-      <c r="J127" s="11" t="n">
+      <c r="J129" s="11" t="n">
         <v>191.2905346768732</v>
       </c>
-      <c r="K127" s="11" t="n">
+      <c r="K129" s="11" t="n">
         <v>32.33192617108512</v>
       </c>
-      <c r="L127" s="11" t="n">
+      <c r="L129" s="11" t="n">
         <v>3.267323050083998</v>
       </c>
-      <c r="M127" s="11" t="n">
+      <c r="M129" s="11" t="n">
         <v>188.9486428523214</v>
       </c>
-      <c r="N127" s="11" t="n">
+      <c r="N129" s="11" t="n">
         <v>29.6838317920997</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="8" t="inlineStr">
-        <is>
-          <t>chart helper: ADR $ (printed, then engine)</t>
-        </is>
-      </c>
-      <c r="O130" s="20">
-        <f>O7</f>
-        <v/>
-      </c>
-      <c r="P130" s="20">
-        <f>P7</f>
-        <v/>
-      </c>
-      <c r="Q130" s="20">
-        <f>Q7</f>
-        <v/>
-      </c>
-      <c r="R130" s="20">
-        <f>R7</f>
-        <v/>
-      </c>
-      <c r="S130" s="20">
-        <f>S7</f>
-        <v/>
-      </c>
-      <c r="T130" s="20">
-        <f>T7</f>
-        <v/>
-      </c>
-      <c r="U130" s="20">
-        <f>U7</f>
-        <v/>
-      </c>
-      <c r="V130" s="20">
-        <f>V7</f>
-        <v/>
-      </c>
-      <c r="W130" s="20">
-        <f>W7</f>
-        <v/>
-      </c>
-      <c r="X130" s="20">
-        <f>X7</f>
-        <v/>
-      </c>
-      <c r="Y130" s="20">
-        <f>Y7</f>
-        <v/>
-      </c>
-      <c r="Z130" s="20">
-        <f>Z7</f>
-        <v/>
-      </c>
-      <c r="AA130" s="20">
-        <f>AA7</f>
-        <v/>
-      </c>
-      <c r="AB130" s="20">
-        <f>AB7</f>
-        <v/>
-      </c>
-      <c r="AC130" s="20">
-        <f>AC7</f>
-        <v/>
-      </c>
-      <c r="AD130" s="20">
-        <f>AD7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="8" t="inlineStr">
-        <is>
-          <t>chart helper: Street ADR $</t>
-        </is>
-      </c>
-      <c r="Y131" s="20">
-        <f>Y100</f>
-        <v/>
-      </c>
-      <c r="Z131" s="20">
-        <f>Z100</f>
-        <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t>chart helper: FX identity (pp)</t>
+          <t>chart helper: ADR $ (printed, then engine)</t>
         </is>
       </c>
       <c r="O132" s="20">
-        <f>O51</f>
+        <f>O7</f>
         <v/>
       </c>
       <c r="P132" s="20">
-        <f>P51</f>
+        <f>P7</f>
         <v/>
       </c>
       <c r="Q132" s="20">
-        <f>Q51</f>
+        <f>Q7</f>
         <v/>
       </c>
       <c r="R132" s="20">
-        <f>R51</f>
+        <f>R7</f>
         <v/>
       </c>
       <c r="S132" s="20">
-        <f>S51</f>
+        <f>S7</f>
         <v/>
       </c>
       <c r="T132" s="20">
-        <f>T51</f>
+        <f>T7</f>
         <v/>
       </c>
       <c r="U132" s="20">
-        <f>U51</f>
+        <f>U7</f>
         <v/>
       </c>
       <c r="V132" s="20">
-        <f>V51</f>
+        <f>V7</f>
         <v/>
       </c>
       <c r="W132" s="20">
-        <f>W51</f>
+        <f>W7</f>
         <v/>
       </c>
       <c r="X132" s="20">
-        <f>X51</f>
+        <f>X7</f>
         <v/>
       </c>
       <c r="Y132" s="20">
-        <f>Y51</f>
+        <f>Y7</f>
         <v/>
       </c>
       <c r="Z132" s="20">
-        <f>Z51</f>
+        <f>Z7</f>
         <v/>
       </c>
       <c r="AA132" s="20">
-        <f>AA51</f>
+        <f>AA7</f>
         <v/>
       </c>
       <c r="AB132" s="20">
-        <f>AB51</f>
+        <f>AB7</f>
         <v/>
       </c>
       <c r="AC132" s="20">
-        <f>AC51</f>
+        <f>AC7</f>
         <v/>
       </c>
       <c r="AD132" s="20">
-        <f>AD51</f>
+        <f>AD7</f>
         <v/>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
+          <t>chart helper: Street ADR $</t>
+        </is>
+      </c>
+      <c r="Y133" s="20">
+        <f>Y100</f>
+        <v/>
+      </c>
+      <c r="Z133" s="20">
+        <f>Z100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>chart helper: FX identity (pp)</t>
+        </is>
+      </c>
+      <c r="O134" s="20">
+        <f>O51</f>
+        <v/>
+      </c>
+      <c r="P134" s="20">
+        <f>P51</f>
+        <v/>
+      </c>
+      <c r="Q134" s="20">
+        <f>Q51</f>
+        <v/>
+      </c>
+      <c r="R134" s="20">
+        <f>R51</f>
+        <v/>
+      </c>
+      <c r="S134" s="20">
+        <f>S51</f>
+        <v/>
+      </c>
+      <c r="T134" s="20">
+        <f>T51</f>
+        <v/>
+      </c>
+      <c r="U134" s="20">
+        <f>U51</f>
+        <v/>
+      </c>
+      <c r="V134" s="20">
+        <f>V51</f>
+        <v/>
+      </c>
+      <c r="W134" s="20">
+        <f>W51</f>
+        <v/>
+      </c>
+      <c r="X134" s="20">
+        <f>X51</f>
+        <v/>
+      </c>
+      <c r="Y134" s="20">
+        <f>Y51</f>
+        <v/>
+      </c>
+      <c r="Z134" s="20">
+        <f>Z51</f>
+        <v/>
+      </c>
+      <c r="AA134" s="20">
+        <f>AA51</f>
+        <v/>
+      </c>
+      <c r="AB134" s="20">
+        <f>AB51</f>
+        <v/>
+      </c>
+      <c r="AC134" s="20">
+        <f>AC51</f>
+        <v/>
+      </c>
+      <c r="AD134" s="20">
+        <f>AD51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
           <t>chart helper: disclosed FX (pp)</t>
         </is>
       </c>
-      <c r="O133" s="20">
+      <c r="O135" s="20">
         <f>O10</f>
         <v/>
       </c>
-      <c r="P133" s="20">
+      <c r="P135" s="20">
         <f>P10</f>
         <v/>
       </c>
-      <c r="Q133" s="20">
+      <c r="Q135" s="20">
         <f>Q10</f>
         <v/>
       </c>
-      <c r="R133" s="20">
+      <c r="R135" s="20">
         <f>R10</f>
         <v/>
       </c>
-      <c r="S133" s="20">
+      <c r="S135" s="20">
         <f>S10</f>
         <v/>
       </c>
-      <c r="T133" s="20">
+      <c r="T135" s="20">
         <f>T10</f>
         <v/>
       </c>
-      <c r="U133" s="20">
+      <c r="U135" s="20">
         <f>U10</f>
         <v/>
       </c>
-      <c r="V133" s="20">
+      <c r="V135" s="20">
         <f>V10</f>
         <v/>
       </c>
-      <c r="W133" s="20">
+      <c r="W135" s="20">
         <f>W10</f>
         <v/>
       </c>
-      <c r="X133" s="20">
+      <c r="X135" s="20">
         <f>X10</f>
         <v/>
       </c>

--- a/model/ABNB_official_model.xlsx
+++ b/model/ABNB_official_model.xlsx
@@ -11688,40 +11688,40 @@
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>3.182081964103476</v>
+        <v>3.178728196637815</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>177.4519237348494</v>
+        <v>177.4461790665574</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>26.04994240427589</v>
+        <v>26.04909908697064</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>2.640676678321757</v>
+        <v>2.637266387956136</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>172.7938444881657</v>
+        <v>172.7881319107742</v>
       </c>
       <c r="H122" s="11" t="n">
-        <v>22.77422870354024</v>
+        <v>22.77347578584005</v>
       </c>
       <c r="I122" s="11" t="n">
-        <v>2.265309708688182</v>
+        <v>2.261923490219556</v>
       </c>
       <c r="J122" s="11" t="n">
-        <v>190.3626606057227</v>
+        <v>190.3563344723796</v>
       </c>
       <c r="K122" s="11" t="n">
-        <v>32.17509689557925</v>
+        <v>32.1740276525216</v>
       </c>
       <c r="L122" s="11" t="n">
-        <v>2.795333000538972</v>
+        <v>2.79184921359367</v>
       </c>
       <c r="M122" s="11" t="n">
-        <v>188.0814555342924</v>
+        <v>188.0750547725378</v>
       </c>
       <c r="N122" s="11" t="n">
-        <v>29.54759666443733</v>
+        <v>29.54659110476569</v>
       </c>
     </row>
     <row r="123">
@@ -11731,40 +11731,40 @@
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>2.800767198387953</v>
+        <v>2.797413430922292</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>176.7987696726552</v>
+        <v>176.7930250043633</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>25.95405938794579</v>
+        <v>25.95321607064054</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>2.276405895791162</v>
+        <v>2.27299560542554</v>
       </c>
       <c r="G123" s="11" t="n">
-        <v>172.1836545003487</v>
+        <v>172.1779419229572</v>
       </c>
       <c r="H123" s="11" t="n">
-        <v>22.69380566314596</v>
+        <v>22.69305274544576</v>
       </c>
       <c r="I123" s="11" t="n">
-        <v>1.845411024644575</v>
+        <v>1.842024806175949</v>
       </c>
       <c r="J123" s="11" t="n">
-        <v>189.5782058841924</v>
+        <v>189.5718797508493</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>32.0425083585462</v>
+        <v>32.04143911548855</v>
       </c>
       <c r="L123" s="11" t="n">
-        <v>2.514402127934693</v>
+        <v>2.510918340989391</v>
       </c>
       <c r="M123" s="11" t="n">
-        <v>187.5653012420565</v>
+        <v>187.5589004803019</v>
       </c>
       <c r="N123" s="11" t="n">
-        <v>29.46650882512708</v>
+        <v>29.46550326545543</v>
       </c>
     </row>
     <row r="124">

--- a/model/ABNB_official_model.xlsx
+++ b/model/ABNB_official_model.xlsx
@@ -787,7 +787,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$132:$AD$132</f>
+              <f>'ADR_Engine'!$O$133:$AD$133</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -818,7 +818,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$133:$AD$133</f>
+              <f>'ADR_Engine'!$O$134:$AD$134</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -906,7 +906,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$134:$AD$134</f>
+              <f>'ADR_Engine'!$O$135:$AD$135</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -937,7 +937,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$135:$AD$135</f>
+              <f>'ADR_Engine'!$O$136:$AD$136</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1076,7 +1076,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>136</row>
+      <row>137</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="2880000"/>
@@ -1098,7 +1098,7 @@
     <from>
       <col>13</col>
       <colOff>0</colOff>
-      <row>136</row>
+      <row>137</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="2880000"/>
@@ -5365,7 +5365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD135"/>
+  <dimension ref="A1:AD136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -11706,7 +11706,7 @@
         <v>22.77347578584005</v>
       </c>
       <c r="I122" s="11" t="n">
-        <v>2.261923490219556</v>
+        <v>2.261923490219557</v>
       </c>
       <c r="J122" s="11" t="n">
         <v>190.3563344723796</v>
@@ -11715,7 +11715,7 @@
         <v>32.1740276525216</v>
       </c>
       <c r="L122" s="11" t="n">
-        <v>2.79184921359367</v>
+        <v>2.791849213593684</v>
       </c>
       <c r="M122" s="11" t="n">
         <v>188.0750547725378</v>
@@ -11727,504 +11727,547 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>base + sub-regional + composition tilt B (EMEA 5 / LatAm 30 / APAC 25)</t>
+          <t>base + sub-regional + measured origin-destination tilt (upgrade 2: EMEA 10.5 / LatAm 16.4 / APAC 14.9)</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>2.797413430922292</v>
+        <v>3.441974423799111</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>176.7930250043633</v>
+        <v>177.897093529062</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>25.95321607064054</v>
+        <v>26.11529333006631</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>2.27299560542554</v>
+        <v>2.878353163829614</v>
       </c>
       <c r="G123" s="11" t="n">
-        <v>172.1779419229572</v>
+        <v>173.1919763690399</v>
       </c>
       <c r="H123" s="11" t="n">
-        <v>22.69305274544576</v>
+        <v>22.82670248543946</v>
       </c>
       <c r="I123" s="11" t="n">
-        <v>1.842024806175949</v>
+        <v>2.547238721983384</v>
       </c>
       <c r="J123" s="11" t="n">
-        <v>189.5718797508493</v>
+        <v>190.8893603883608</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>32.04143911548855</v>
+        <v>32.26411969284074</v>
       </c>
       <c r="L123" s="11" t="n">
-        <v>2.510918340989391</v>
+        <v>2.977560195437551</v>
       </c>
       <c r="M123" s="11" t="n">
-        <v>187.5589004803019</v>
+        <v>188.4162615594795</v>
       </c>
       <c r="N123" s="11" t="n">
-        <v>29.46550326545543</v>
+        <v>29.60019469099423</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>lap-only (K4 residual steps): every 2025-26 residual step laps at its anniversary</t>
+          <t>base + sub-regional + composition tilt B (EMEA 5 / LatAm 30 / APAC 25) — retired by upgrade 2</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>2.910732193880174</v>
+        <v>2.797413430922292</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>176.9871287134339</v>
+        <v>176.7930250043633</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>25.9817104951321</v>
+        <v>25.95321607064054</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1.990747787585442</v>
+        <v>2.27299560542554</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>171.7051486032933</v>
+        <v>172.1779419229572</v>
       </c>
       <c r="H124" s="11" t="n">
-        <v>22.63073858591405</v>
+        <v>22.69305274544576</v>
       </c>
       <c r="I124" s="11" t="n">
-        <v>0.9435507506529328</v>
+        <v>1.84202480617595</v>
       </c>
       <c r="J124" s="11" t="n">
-        <v>187.8933505203212</v>
+        <v>189.5718797508493</v>
       </c>
       <c r="K124" s="11" t="n">
-        <v>31.75773410494469</v>
+        <v>32.04143911548855</v>
       </c>
       <c r="L124" s="11" t="n">
-        <v>1.013196673597509</v>
+        <v>2.510918340989404</v>
       </c>
       <c r="M124" s="11" t="n">
-        <v>184.8071364608028</v>
+        <v>187.5589004803019</v>
       </c>
       <c r="N124" s="11" t="n">
-        <v>29.03320113799212</v>
+        <v>29.46550326545543</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>card v3: last_q residual carry, no lap (card geo)</t>
+          <t>lap-only (K4 residual steps): every 2025-26 residual step laps at its anniversary</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>3.69126637648649</v>
+        <v>2.910732193880174</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>178.3241057148202</v>
+        <v>176.9871287134339</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>26.17797871893561</v>
+        <v>25.9817104951321</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>3.69126637648649</v>
+        <v>1.990747787585442</v>
       </c>
       <c r="G125" s="11" t="n">
-        <v>174.5536872915614</v>
+        <v>171.7051486032933</v>
       </c>
       <c r="H125" s="11" t="n">
-        <v>23.0061759850278</v>
+        <v>22.63073858591405</v>
       </c>
       <c r="I125" s="11" t="n">
-        <v>3.60883637648649</v>
+        <v>0.9435507506529328</v>
       </c>
       <c r="J125" s="11" t="n">
-        <v>192.8726371265034</v>
+        <v>187.8933505203212</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>32.59933312712161</v>
+        <v>31.75773410494469</v>
       </c>
       <c r="L125" s="11" t="n">
-        <v>3.60883637648649</v>
+        <v>1.013196673597509</v>
       </c>
       <c r="M125" s="11" t="n">
-        <v>189.5761052869207</v>
+        <v>184.8071364608028</v>
       </c>
       <c r="N125" s="11" t="n">
-        <v>29.78240614057524</v>
+        <v>29.03320113799212</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>full lap: ex-NA RNPL sized at the 1H26 residual steps</t>
+          <t>card v3: last_q residual carry, no lap (card geo)</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>3.315947459255554</v>
+        <v>3.69126637648649</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>177.6812219414954</v>
+        <v>178.3241057148202</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>26.08360338101152</v>
+        <v>26.17797871893561</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>2.784074164071932</v>
+        <v>3.69126637648649</v>
       </c>
       <c r="G126" s="11" t="n">
-        <v>173.0340496165458</v>
+        <v>174.5536872915614</v>
       </c>
       <c r="H126" s="11" t="n">
-        <v>22.80588773946074</v>
+        <v>23.0061759850278</v>
       </c>
       <c r="I126" s="11" t="n">
-        <v>1.956877127139422</v>
+        <v>3.60883637648649</v>
       </c>
       <c r="J126" s="11" t="n">
-        <v>189.7864468568733</v>
+        <v>192.8726371265034</v>
       </c>
       <c r="K126" s="11" t="n">
-        <v>32.07770524774872</v>
+        <v>32.59933312712161</v>
       </c>
       <c r="L126" s="11" t="n">
-        <v>1.806523050083998</v>
+        <v>3.60883637648649</v>
       </c>
       <c r="M126" s="11" t="n">
-        <v>186.2647150123214</v>
+        <v>189.5761052869207</v>
       </c>
       <c r="N126" s="11" t="n">
-        <v>29.2621867284357</v>
+        <v>29.78240614057524</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>core mean reversion to the 2023-25 mean</t>
+          <t>full lap: ex-NA RNPL sized at the 1H26 residual steps</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>1.864621082769064</v>
+        <v>3.315947459255554</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>175.1952449912116</v>
+        <v>177.6812219414954</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>25.71866196470987</v>
+        <v>26.08360338101152</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1.332747787585442</v>
+        <v>2.784074164071932</v>
       </c>
       <c r="G127" s="11" t="n">
-        <v>170.6029328032933</v>
+        <v>173.0340496165458</v>
       </c>
       <c r="H127" s="11" t="n">
-        <v>22.48546654347406</v>
+        <v>22.80588773946074</v>
       </c>
       <c r="I127" s="11" t="n">
-        <v>0.9655507506529332</v>
+        <v>1.956877127139422</v>
       </c>
       <c r="J127" s="11" t="n">
-        <v>187.9344509203212</v>
+        <v>189.7864468568733</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>31.7646808945527</v>
+        <v>32.07770524774872</v>
       </c>
       <c r="L127" s="11" t="n">
-        <v>1.505196673597509</v>
+        <v>1.806523050083998</v>
       </c>
       <c r="M127" s="11" t="n">
-        <v>185.7110880608028</v>
+        <v>186.2647150123214</v>
       </c>
       <c r="N127" s="11" t="n">
-        <v>29.17521193435212</v>
+        <v>29.2621867284357</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t>AR(1) on core (K4 rho 0.747)</t>
+          <t>core mean reversion to the 2023-25 mean</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>3.092067886004471</v>
+        <v>1.864621082769064</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>177.2977386204736</v>
+        <v>175.1952449912116</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>26.02730802948552</v>
+        <v>25.71866196470987</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>2.392956549602292</v>
+        <v>1.332747787585442</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>172.3788885005477</v>
+        <v>170.6029328032933</v>
       </c>
       <c r="H128" s="11" t="n">
-        <v>22.71953750437219</v>
+        <v>22.48546654347406</v>
       </c>
       <c r="I128" s="11" t="n">
-        <v>1.90083269587952</v>
+        <v>0.9655507506529332</v>
       </c>
       <c r="J128" s="11" t="n">
-        <v>189.6817446503935</v>
+        <v>187.9344509203212</v>
       </c>
       <c r="K128" s="11" t="n">
-        <v>32.06000848080952</v>
+        <v>31.7646808945527</v>
       </c>
       <c r="L128" s="11" t="n">
-        <v>2.347158286681769</v>
+        <v>1.505196673597509</v>
       </c>
       <c r="M128" s="11" t="n">
-        <v>187.2580241325226</v>
+        <v>185.7110880608028</v>
       </c>
       <c r="N128" s="11" t="n">
-        <v>29.41823559121929</v>
+        <v>29.17521193435212</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
+          <t>AR(1) on core (K4 rho 0.747)</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="n">
+        <v>3.092067886004471</v>
+      </c>
+      <c r="D129" s="11" t="n">
+        <v>177.2977386204736</v>
+      </c>
+      <c r="E129" s="11" t="n">
+        <v>26.02730802948552</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>2.392956549602292</v>
+      </c>
+      <c r="G129" s="11" t="n">
+        <v>172.3788885005477</v>
+      </c>
+      <c r="H129" s="11" t="n">
+        <v>22.71953750437219</v>
+      </c>
+      <c r="I129" s="11" t="n">
+        <v>1.90083269587952</v>
+      </c>
+      <c r="J129" s="11" t="n">
+        <v>189.6817446503935</v>
+      </c>
+      <c r="K129" s="11" t="n">
+        <v>32.06000848080952</v>
+      </c>
+      <c r="L129" s="11" t="n">
+        <v>2.347158286681769</v>
+      </c>
+      <c r="M129" s="11" t="n">
+        <v>187.2580241325226</v>
+      </c>
+      <c r="N129" s="11" t="n">
+        <v>29.41823559121929</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
           <t>base + fee-migration K line (DEC-0008 sensitivity)</t>
         </is>
       </c>
-      <c r="C129" s="11" t="n">
+      <c r="C130" s="11" t="n">
         <v>3.487447459255554</v>
       </c>
-      <c r="D129" s="11" t="n">
+      <c r="D130" s="11" t="n">
         <v>177.9749842914954</v>
       </c>
-      <c r="E129" s="11" t="n">
+      <c r="E130" s="11" t="n">
         <v>26.12672769399152</v>
       </c>
-      <c r="F129" s="11" t="n">
+      <c r="F130" s="11" t="n">
         <v>3.158574164071932</v>
       </c>
-      <c r="G129" s="11" t="n">
+      <c r="G130" s="11" t="n">
         <v>173.6613745665458</v>
       </c>
-      <c r="H129" s="11" t="n">
+      <c r="H130" s="11" t="n">
         <v>22.88856916787073</v>
       </c>
-      <c r="I129" s="11" t="n">
+      <c r="I130" s="11" t="n">
         <v>2.761977127139422</v>
       </c>
-      <c r="J129" s="11" t="n">
+      <c r="J130" s="11" t="n">
         <v>191.2905346768732</v>
       </c>
-      <c r="K129" s="11" t="n">
+      <c r="K130" s="11" t="n">
         <v>32.33192617108512</v>
       </c>
-      <c r="L129" s="11" t="n">
+      <c r="L130" s="11" t="n">
         <v>3.267323050083998</v>
       </c>
-      <c r="M129" s="11" t="n">
+      <c r="M130" s="11" t="n">
         <v>188.9486428523214</v>
       </c>
-      <c r="N129" s="11" t="n">
+      <c r="N130" s="11" t="n">
         <v>29.6838317920997</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t>chart helper: ADR $ (printed, then engine)</t>
-        </is>
-      </c>
-      <c r="O132" s="20">
-        <f>O7</f>
-        <v/>
-      </c>
-      <c r="P132" s="20">
-        <f>P7</f>
-        <v/>
-      </c>
-      <c r="Q132" s="20">
-        <f>Q7</f>
-        <v/>
-      </c>
-      <c r="R132" s="20">
-        <f>R7</f>
-        <v/>
-      </c>
-      <c r="S132" s="20">
-        <f>S7</f>
-        <v/>
-      </c>
-      <c r="T132" s="20">
-        <f>T7</f>
-        <v/>
-      </c>
-      <c r="U132" s="20">
-        <f>U7</f>
-        <v/>
-      </c>
-      <c r="V132" s="20">
-        <f>V7</f>
-        <v/>
-      </c>
-      <c r="W132" s="20">
-        <f>W7</f>
-        <v/>
-      </c>
-      <c r="X132" s="20">
-        <f>X7</f>
-        <v/>
-      </c>
-      <c r="Y132" s="20">
-        <f>Y7</f>
-        <v/>
-      </c>
-      <c r="Z132" s="20">
-        <f>Z7</f>
-        <v/>
-      </c>
-      <c r="AA132" s="20">
-        <f>AA7</f>
-        <v/>
-      </c>
-      <c r="AB132" s="20">
-        <f>AB7</f>
-        <v/>
-      </c>
-      <c r="AC132" s="20">
-        <f>AC7</f>
-        <v/>
-      </c>
-      <c r="AD132" s="20">
-        <f>AD7</f>
-        <v/>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>chart helper: Street ADR $</t>
-        </is>
+          <t>chart helper: ADR $ (printed, then engine)</t>
+        </is>
+      </c>
+      <c r="O133" s="20">
+        <f>O7</f>
+        <v/>
+      </c>
+      <c r="P133" s="20">
+        <f>P7</f>
+        <v/>
+      </c>
+      <c r="Q133" s="20">
+        <f>Q7</f>
+        <v/>
+      </c>
+      <c r="R133" s="20">
+        <f>R7</f>
+        <v/>
+      </c>
+      <c r="S133" s="20">
+        <f>S7</f>
+        <v/>
+      </c>
+      <c r="T133" s="20">
+        <f>T7</f>
+        <v/>
+      </c>
+      <c r="U133" s="20">
+        <f>U7</f>
+        <v/>
+      </c>
+      <c r="V133" s="20">
+        <f>V7</f>
+        <v/>
+      </c>
+      <c r="W133" s="20">
+        <f>W7</f>
+        <v/>
+      </c>
+      <c r="X133" s="20">
+        <f>X7</f>
+        <v/>
       </c>
       <c r="Y133" s="20">
-        <f>Y100</f>
+        <f>Y7</f>
         <v/>
       </c>
       <c r="Z133" s="20">
-        <f>Z100</f>
+        <f>Z7</f>
+        <v/>
+      </c>
+      <c r="AA133" s="20">
+        <f>AA7</f>
+        <v/>
+      </c>
+      <c r="AB133" s="20">
+        <f>AB7</f>
+        <v/>
+      </c>
+      <c r="AC133" s="20">
+        <f>AC7</f>
+        <v/>
+      </c>
+      <c r="AD133" s="20">
+        <f>AD7</f>
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t>chart helper: FX identity (pp)</t>
-        </is>
-      </c>
-      <c r="O134" s="20">
-        <f>O51</f>
-        <v/>
-      </c>
-      <c r="P134" s="20">
-        <f>P51</f>
-        <v/>
-      </c>
-      <c r="Q134" s="20">
-        <f>Q51</f>
-        <v/>
-      </c>
-      <c r="R134" s="20">
-        <f>R51</f>
-        <v/>
-      </c>
-      <c r="S134" s="20">
-        <f>S51</f>
-        <v/>
-      </c>
-      <c r="T134" s="20">
-        <f>T51</f>
-        <v/>
-      </c>
-      <c r="U134" s="20">
-        <f>U51</f>
-        <v/>
-      </c>
-      <c r="V134" s="20">
-        <f>V51</f>
-        <v/>
-      </c>
-      <c r="W134" s="20">
-        <f>W51</f>
-        <v/>
-      </c>
-      <c r="X134" s="20">
-        <f>X51</f>
-        <v/>
+          <t>chart helper: Street ADR $</t>
+        </is>
       </c>
       <c r="Y134" s="20">
-        <f>Y51</f>
+        <f>Y100</f>
         <v/>
       </c>
       <c r="Z134" s="20">
-        <f>Z51</f>
-        <v/>
-      </c>
-      <c r="AA134" s="20">
-        <f>AA51</f>
-        <v/>
-      </c>
-      <c r="AB134" s="20">
-        <f>AB51</f>
-        <v/>
-      </c>
-      <c r="AC134" s="20">
-        <f>AC51</f>
-        <v/>
-      </c>
-      <c r="AD134" s="20">
-        <f>AD51</f>
+        <f>Z100</f>
         <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
+          <t>chart helper: FX identity (pp)</t>
+        </is>
+      </c>
+      <c r="O135" s="20">
+        <f>O51</f>
+        <v/>
+      </c>
+      <c r="P135" s="20">
+        <f>P51</f>
+        <v/>
+      </c>
+      <c r="Q135" s="20">
+        <f>Q51</f>
+        <v/>
+      </c>
+      <c r="R135" s="20">
+        <f>R51</f>
+        <v/>
+      </c>
+      <c r="S135" s="20">
+        <f>S51</f>
+        <v/>
+      </c>
+      <c r="T135" s="20">
+        <f>T51</f>
+        <v/>
+      </c>
+      <c r="U135" s="20">
+        <f>U51</f>
+        <v/>
+      </c>
+      <c r="V135" s="20">
+        <f>V51</f>
+        <v/>
+      </c>
+      <c r="W135" s="20">
+        <f>W51</f>
+        <v/>
+      </c>
+      <c r="X135" s="20">
+        <f>X51</f>
+        <v/>
+      </c>
+      <c r="Y135" s="20">
+        <f>Y51</f>
+        <v/>
+      </c>
+      <c r="Z135" s="20">
+        <f>Z51</f>
+        <v/>
+      </c>
+      <c r="AA135" s="20">
+        <f>AA51</f>
+        <v/>
+      </c>
+      <c r="AB135" s="20">
+        <f>AB51</f>
+        <v/>
+      </c>
+      <c r="AC135" s="20">
+        <f>AC51</f>
+        <v/>
+      </c>
+      <c r="AD135" s="20">
+        <f>AD51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="8" t="inlineStr">
+        <is>
           <t>chart helper: disclosed FX (pp)</t>
         </is>
       </c>
-      <c r="O135" s="20">
+      <c r="O136" s="20">
         <f>O10</f>
         <v/>
       </c>
-      <c r="P135" s="20">
+      <c r="P136" s="20">
         <f>P10</f>
         <v/>
       </c>
-      <c r="Q135" s="20">
+      <c r="Q136" s="20">
         <f>Q10</f>
         <v/>
       </c>
-      <c r="R135" s="20">
+      <c r="R136" s="20">
         <f>R10</f>
         <v/>
       </c>
-      <c r="S135" s="20">
+      <c r="S136" s="20">
         <f>S10</f>
         <v/>
       </c>
-      <c r="T135" s="20">
+      <c r="T136" s="20">
         <f>T10</f>
         <v/>
       </c>
-      <c r="U135" s="20">
+      <c r="U136" s="20">
         <f>U10</f>
         <v/>
       </c>
-      <c r="V135" s="20">
+      <c r="V136" s="20">
         <f>V10</f>
         <v/>
       </c>
-      <c r="W135" s="20">
+      <c r="W136" s="20">
         <f>W10</f>
         <v/>
       </c>
-      <c r="X135" s="20">
+      <c r="X136" s="20">
         <f>X10</f>
         <v/>
       </c>

--- a/model/ABNB_official_model.xlsx
+++ b/model/ABNB_official_model.xlsx
@@ -787,7 +787,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$133:$AD$133</f>
+              <f>'ADR_Engine'!$O$146:$AD$146</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -818,7 +818,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$134:$AD$134</f>
+              <f>'ADR_Engine'!$O$147:$AD$147</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -906,7 +906,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$135:$AD$135</f>
+              <f>'ADR_Engine'!$O$148:$AD$148</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -937,7 +937,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'ADR_Engine'!$O$136:$AD$136</f>
+              <f>'ADR_Engine'!$O$149:$AD$149</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1076,7 +1076,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>137</row>
+      <row>150</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="2880000"/>
@@ -1098,7 +1098,7 @@
     <from>
       <col>13</col>
       <colOff>0</colOff>
-      <row>137</row>
+      <row>150</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="2880000"/>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nights: built (DEC-0029 base 146.8m). ADR: built (ADR_Engine; pre-registered FX identity promoted, ex-FX mechanism with the bundle lapping on filed dates; proposed DEC-0034/0035 pending Theo). GBV = nights × ADR on Income_Statement row 8. Next: take rate / revenue, together, one at a time.</t>
+          <t>Nights: built (DEC-0029 base 146.8m). ADR: built (ADR_Engine; pre-registered FX identity promoted, ex-FX mechanism with the bundle lapping on filed dates; proposed DEC-0034/0035 pending Theo), then extended with the v2 geo-mix layer and hardened by the four mitigations of 22 Sep (block G; DEC-0037–0041 pending Theo). Base ADR path unchanged by the mitigations: 3Q26 $177.68, 4Q26 $173.03. GBV = nights × ADR on Income_Statement row 8. Next: take rate / revenue, together, one at a time.</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD136"/>
+  <dimension ref="A1:AD149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -12068,206 +12068,679 @@
         <v>29.6838317920997</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>G. Evidence behind line 2 — the v2 geo-mix layer and the four mitigations of 22 Sep. Labelled attribution and falsifiers; none of this is in the base path above.</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n"/>
+      <c r="C132" s="5" t="n"/>
+      <c r="D132" s="5" t="n"/>
+      <c r="E132" s="5" t="n"/>
+      <c r="F132" s="5" t="n"/>
+      <c r="G132" s="5" t="n"/>
+      <c r="H132" s="5" t="n"/>
+      <c r="I132" s="5" t="n"/>
+      <c r="J132" s="5" t="n"/>
+      <c r="K132" s="5" t="n"/>
+      <c r="L132" s="5" t="n"/>
+      <c r="M132" s="5" t="n"/>
+      <c r="N132" s="5" t="n"/>
+      <c r="O132" s="5" t="n"/>
+      <c r="P132" s="5" t="n"/>
+      <c r="Q132" s="5" t="n"/>
+      <c r="R132" s="5" t="n"/>
+      <c r="S132" s="5" t="n"/>
+      <c r="T132" s="5" t="n"/>
+      <c r="U132" s="5" t="n"/>
+      <c r="V132" s="5" t="n"/>
+      <c r="W132" s="5" t="n"/>
+      <c r="X132" s="5" t="n"/>
+      <c r="Y132" s="5" t="n"/>
+      <c r="Z132" s="5" t="n"/>
+      <c r="AA132" s="5" t="n"/>
+      <c r="AB132" s="5" t="n"/>
+      <c r="AC132" s="5" t="n"/>
+      <c r="AD132" s="5" t="n"/>
+    </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>chart helper: ADR $ (printed, then engine)</t>
-        </is>
-      </c>
-      <c r="O133" s="20">
-        <f>O7</f>
-        <v/>
-      </c>
-      <c r="P133" s="20">
-        <f>P7</f>
-        <v/>
-      </c>
-      <c r="Q133" s="20">
-        <f>Q7</f>
-        <v/>
-      </c>
-      <c r="R133" s="20">
-        <f>R7</f>
-        <v/>
-      </c>
-      <c r="S133" s="20">
-        <f>S7</f>
-        <v/>
-      </c>
-      <c r="T133" s="20">
-        <f>T7</f>
-        <v/>
-      </c>
-      <c r="U133" s="20">
-        <f>U7</f>
-        <v/>
-      </c>
-      <c r="V133" s="20">
-        <f>V7</f>
-        <v/>
-      </c>
-      <c r="W133" s="20">
-        <f>W7</f>
-        <v/>
-      </c>
-      <c r="X133" s="20">
-        <f>X7</f>
-        <v/>
-      </c>
-      <c r="Y133" s="20">
-        <f>Y7</f>
-        <v/>
-      </c>
-      <c r="Z133" s="20">
-        <f>Z7</f>
-        <v/>
-      </c>
-      <c r="AA133" s="20">
-        <f>AA7</f>
-        <v/>
-      </c>
-      <c r="AB133" s="20">
-        <f>AB7</f>
-        <v/>
-      </c>
-      <c r="AC133" s="20">
-        <f>AC7</f>
-        <v/>
-      </c>
-      <c r="AD133" s="20">
-        <f>AD7</f>
-        <v/>
+          <t>G1. Sub-regional (within-region country) mix, pp of ADR — DEC-0038: attribution + forward row, NOT the base</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>mean 1Q23–2Q26</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="n">
+        <v>-0.4533850498510343</v>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>last 4 q to 2Q26</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="n">
+        <v>-0.151696241914275</v>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>fwd 3Q26</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="n">
+        <v>-0.1372192626177384</v>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>fwd 4Q26</t>
+        </is>
+      </c>
+      <c r="J133" s="12" t="n">
+        <v>-0.1468077761157966</v>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>4Q26 ADR effect ($)</t>
+        </is>
+      </c>
+      <c r="L133" s="12" t="n">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t>chart helper: Street ADR $</t>
-        </is>
-      </c>
-      <c r="Y134" s="20">
-        <f>Y100</f>
-        <v/>
-      </c>
-      <c r="Z134" s="20">
-        <f>Z100</f>
-        <v/>
+          <t xml:space="preserve">      H2 forecast-content test, RMSE ratio vs the residual carry — pass line 0.75 on BOTH windows → FAILS, so the term stays out of the base</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>W1 (n 10)</t>
+        </is>
+      </c>
+      <c r="D134" s="12" t="n">
+        <v>0.908921731098177</v>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>W2 (n 6)</t>
+        </is>
+      </c>
+      <c r="F134" s="12" t="n">
+        <v>0.7190490218012525</v>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>pass line</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>chart helper: FX identity (pp)</t>
-        </is>
-      </c>
-      <c r="O135" s="20">
-        <f>O51</f>
-        <v/>
-      </c>
-      <c r="P135" s="20">
-        <f>P51</f>
-        <v/>
-      </c>
-      <c r="Q135" s="20">
-        <f>Q51</f>
-        <v/>
-      </c>
-      <c r="R135" s="20">
-        <f>R51</f>
-        <v/>
-      </c>
-      <c r="S135" s="20">
-        <f>S51</f>
-        <v/>
-      </c>
-      <c r="T135" s="20">
-        <f>T51</f>
-        <v/>
-      </c>
-      <c r="U135" s="20">
-        <f>U51</f>
-        <v/>
-      </c>
-      <c r="V135" s="20">
-        <f>V51</f>
-        <v/>
-      </c>
-      <c r="W135" s="20">
-        <f>W51</f>
-        <v/>
-      </c>
-      <c r="X135" s="20">
-        <f>X51</f>
-        <v/>
-      </c>
-      <c r="Y135" s="20">
-        <f>Y51</f>
-        <v/>
-      </c>
-      <c r="Z135" s="20">
-        <f>Z51</f>
-        <v/>
-      </c>
-      <c r="AA135" s="20">
-        <f>AA51</f>
-        <v/>
-      </c>
-      <c r="AB135" s="20">
-        <f>AB51</f>
-        <v/>
-      </c>
-      <c r="AC135" s="20">
-        <f>AC51</f>
-        <v/>
-      </c>
-      <c r="AD135" s="20">
-        <f>AD51</f>
-        <v/>
+          <t>G2. Reconciliation to the company's own accounting (mitigation C): disclosed constant-currency rate minus regional accommodation inflation, regressed on our within-region mix. The identity implies a slope of 1.0.</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>slope</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="n">
+        <v>1.127000224086993</v>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>cluster-by-region p</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="n">
+        <v>0.0422384883788224</v>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>90% lo</t>
+        </is>
+      </c>
+      <c r="H135" s="12" t="n">
+        <v>0.3485695458913359</v>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>90% hi</t>
+        </is>
+      </c>
+      <c r="J135" s="12" t="n">
+        <v>1.90543090228265</v>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>n prints</t>
+        </is>
+      </c>
+      <c r="L135" s="12" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">      the slope is carried by ONE region — leave-one-region-out (LatAm's own comparator is Brazil alone, 24–33% coverage)</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>drop LatAm</t>
+        </is>
+      </c>
+      <c r="D136" s="12" t="n">
+        <v>-0.3022250248696609</v>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>drop EMEA</t>
+        </is>
+      </c>
+      <c r="F136" s="12" t="n">
+        <v>1.235024164906723</v>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>drop NAM</t>
+        </is>
+      </c>
+      <c r="H136" s="12" t="n">
+        <v>1.127000224086993</v>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>drop APAC</t>
+        </is>
+      </c>
+      <c r="J136" s="12" t="n">
+        <v>1.247277823606619</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      and the earlier EMEA-only reading is window-dependent: admitting two further disclosed quarters flips its sign</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>EMEA only, n 7</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="n">
+        <v>1.085196796156045</v>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>EMEA only, n 9</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="n">
+        <v>-0.3813639149721989</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t>G3. Implied like-for-like price by year, pp — DEC-0040 route: H size</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="n">
+        <v>2.952684569536031</v>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="n">
+        <v>2.754115232397859</v>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="n">
+        <v>2.934235120207423</v>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>2025 size term</t>
+        </is>
+      </c>
+      <c r="J138" s="12" t="n">
+        <v>0.7394814142426782</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      same, route: H size + H LOS</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="n">
+        <v>3.258281481684737</v>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="n">
+        <v>2.685030249211593</v>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="n">
+        <v>2.67892135148754</v>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>2025 size term</t>
+        </is>
+      </c>
+      <c r="J139" s="12" t="n">
+        <v>0.7394814142426782</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      same, route: as filed (withdrawn)</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D140" s="12" t="n">
+        <v>3.339449526200775</v>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="n">
+        <v>3.153691779081526</v>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="n">
+        <v>3.925055242507793</v>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>2025 size term</t>
+        </is>
+      </c>
+      <c r="J140" s="12" t="n">
+        <v>-0.2513387080576912</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      DEC-0040: the filed route's NEGATIVE 2025 size term is a Paris-weighting artefact; the H route is adopted and sits inside the filed bedroom-nights bracket. 2025 like-for-like price is FLAT, so the 2026 core step is LARGER, not smaller — stated against our own interest.</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>bracket lo</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>bracket hi</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>G4. Price-to-utilisation elasticity, market-level panel (mitigation B) — registered pass line b&gt;0 and p≤0.05 → FAILS. Buys at most 0.6pp of the core and in the wrong direction for a give-back; the fix is a Sept-2026 capture wave.</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>elasticity b</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="n">
+        <v>0.08289400619632679</v>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="n">
+        <v>0.7940309342115639</v>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>CI lo</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="n">
+        <v>-0.5394032328684883</v>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>CI hi</t>
+        </is>
+      </c>
+      <c r="J142" s="12" t="n">
+        <v>0.7051912452611422</v>
+      </c>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>n pairs</t>
+        </is>
+      </c>
+      <c r="L142" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="M142" s="4" t="inlineStr">
+        <is>
+          <t>ex-US b</t>
+        </is>
+      </c>
+      <c r="N142" s="12" t="n">
+        <v>0.041103455300918</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>G5. Guest-origin rotation, priced (mitigation D) — day-matched LTM windows 2024→2026 on 53m reviews; within a market a non-English-reviewed listing is cheaper, so the rotation itself costs price.</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>non-English +%</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="n">
+        <v>81.04407474280026</v>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>English +%</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="n">
+        <v>39.95589163021235</v>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>English share 2024 %</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="n">
+        <v>62.94056049407353</v>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>English share 2026 %</t>
+        </is>
+      </c>
+      <c r="J143" s="12" t="n">
+        <v>56.76462986468275</v>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>non-En price vs En</t>
+        </is>
+      </c>
+      <c r="L143" s="12" t="n">
+        <v>0.8656500630082349</v>
+      </c>
+      <c r="M143" s="4" t="inlineStr">
+        <is>
+          <t>mix effect %/yr</t>
+        </is>
+      </c>
+      <c r="N143" s="12" t="n">
+        <v>-0.3449220567665853</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>chart helper: ADR $ (printed, then engine)</t>
+        </is>
+      </c>
+      <c r="O146" s="20">
+        <f>O7</f>
+        <v/>
+      </c>
+      <c r="P146" s="20">
+        <f>P7</f>
+        <v/>
+      </c>
+      <c r="Q146" s="20">
+        <f>Q7</f>
+        <v/>
+      </c>
+      <c r="R146" s="20">
+        <f>R7</f>
+        <v/>
+      </c>
+      <c r="S146" s="20">
+        <f>S7</f>
+        <v/>
+      </c>
+      <c r="T146" s="20">
+        <f>T7</f>
+        <v/>
+      </c>
+      <c r="U146" s="20">
+        <f>U7</f>
+        <v/>
+      </c>
+      <c r="V146" s="20">
+        <f>V7</f>
+        <v/>
+      </c>
+      <c r="W146" s="20">
+        <f>W7</f>
+        <v/>
+      </c>
+      <c r="X146" s="20">
+        <f>X7</f>
+        <v/>
+      </c>
+      <c r="Y146" s="20">
+        <f>Y7</f>
+        <v/>
+      </c>
+      <c r="Z146" s="20">
+        <f>Z7</f>
+        <v/>
+      </c>
+      <c r="AA146" s="20">
+        <f>AA7</f>
+        <v/>
+      </c>
+      <c r="AB146" s="20">
+        <f>AB7</f>
+        <v/>
+      </c>
+      <c r="AC146" s="20">
+        <f>AC7</f>
+        <v/>
+      </c>
+      <c r="AD146" s="20">
+        <f>AD7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>chart helper: Street ADR $</t>
+        </is>
+      </c>
+      <c r="Y147" s="20">
+        <f>Y100</f>
+        <v/>
+      </c>
+      <c r="Z147" s="20">
+        <f>Z100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="8" t="inlineStr">
+        <is>
+          <t>chart helper: FX identity (pp)</t>
+        </is>
+      </c>
+      <c r="O148" s="20">
+        <f>O51</f>
+        <v/>
+      </c>
+      <c r="P148" s="20">
+        <f>P51</f>
+        <v/>
+      </c>
+      <c r="Q148" s="20">
+        <f>Q51</f>
+        <v/>
+      </c>
+      <c r="R148" s="20">
+        <f>R51</f>
+        <v/>
+      </c>
+      <c r="S148" s="20">
+        <f>S51</f>
+        <v/>
+      </c>
+      <c r="T148" s="20">
+        <f>T51</f>
+        <v/>
+      </c>
+      <c r="U148" s="20">
+        <f>U51</f>
+        <v/>
+      </c>
+      <c r="V148" s="20">
+        <f>V51</f>
+        <v/>
+      </c>
+      <c r="W148" s="20">
+        <f>W51</f>
+        <v/>
+      </c>
+      <c r="X148" s="20">
+        <f>X51</f>
+        <v/>
+      </c>
+      <c r="Y148" s="20">
+        <f>Y51</f>
+        <v/>
+      </c>
+      <c r="Z148" s="20">
+        <f>Z51</f>
+        <v/>
+      </c>
+      <c r="AA148" s="20">
+        <f>AA51</f>
+        <v/>
+      </c>
+      <c r="AB148" s="20">
+        <f>AB51</f>
+        <v/>
+      </c>
+      <c r="AC148" s="20">
+        <f>AC51</f>
+        <v/>
+      </c>
+      <c r="AD148" s="20">
+        <f>AD51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
           <t>chart helper: disclosed FX (pp)</t>
         </is>
       </c>
-      <c r="O136" s="20">
+      <c r="O149" s="20">
         <f>O10</f>
         <v/>
       </c>
-      <c r="P136" s="20">
+      <c r="P149" s="20">
         <f>P10</f>
         <v/>
       </c>
-      <c r="Q136" s="20">
+      <c r="Q149" s="20">
         <f>Q10</f>
         <v/>
       </c>
-      <c r="R136" s="20">
+      <c r="R149" s="20">
         <f>R10</f>
         <v/>
       </c>
-      <c r="S136" s="20">
+      <c r="S149" s="20">
         <f>S10</f>
         <v/>
       </c>
-      <c r="T136" s="20">
+      <c r="T149" s="20">
         <f>T10</f>
         <v/>
       </c>
-      <c r="U136" s="20">
+      <c r="U149" s="20">
         <f>U10</f>
         <v/>
       </c>
-      <c r="V136" s="20">
+      <c r="V149" s="20">
         <f>V10</f>
         <v/>
       </c>
-      <c r="W136" s="20">
+      <c r="W149" s="20">
         <f>W10</f>
         <v/>
       </c>
-      <c r="X136" s="20">
+      <c r="X149" s="20">
         <f>X10</f>
         <v/>
       </c>
@@ -13400,7 +13873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -13757,6 +14230,57 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Sub-regional mix inputs (v2)</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Inside Airbnb capture store → refresh_prices.py: 123 markets, 30 priced countries</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>adr_v2_geomix_prereg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Origin→destination flows</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>NTTO, JNTO, ABS, StatCan arrivals by origin (od_layer.py)</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>adr_v2_upgrade2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Mitigation outputs (block G)</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>adr_engine/: reconcile_pooled_regressions.csv, sizemix_rebased_plug.csv, market_panel_scores.csv, origin_lang_*.csv</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>adr_v2_mitigation_A–D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/model/ABNB_official_model.xlsx
+++ b/model/ABNB_official_model.xlsx
@@ -20,12 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.000%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -117,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,7 +154,11 @@
     <xf numFmtId="164" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1479,7 +1484,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nights: built (DEC-0029 base 146.8m). ADR: built (ADR_Engine; pre-registered FX identity promoted, ex-FX mechanism with the bundle lapping on filed dates; proposed DEC-0034/0035 pending Theo), then extended with the v2 geo-mix layer and hardened by the four mitigations of 22 Sep (block G; DEC-0037–0041 pending Theo). Base ADR path unchanged by the mitigations: 3Q26 $177.68, 4Q26 $173.03. GBV = nights × ADR on Income_Statement row 8. Next: take rate / revenue, together, one at a time.</t>
+          <t>Nights: built (DEC-0029 base 146.8m). ADR: built (ADR_Engine; pre-registered FX identity promoted, ex-FX mechanism with the bundle lapping on filed dates; proposed DEC-0034/0035 pending Theo), then extended with the v2 geo-mix layer and hardened by the four mitigations of 22 Sep (block G; DEC-0037–0041 pending Theo). Base ADR path unchanged by the mitigations: 3Q26 $177.68, 4Q26 $173.03. GBV = nights × ADR on Income_Statement row 8. Income statement: history 1Q23-2Q26 plugged from the reconciled financial panel; forecast cost lines, SBC, D&amp;A and below-the-line plugged from the 40_line_build base (DEC-0022); take rate Street-implied for 3Q26-4Q26 (DEC-0018) and seasonal naive thereafter, so the margin is an output of our own nights x ADR. Open: DEC-0023 hosting step.</t>
         </is>
       </c>
     </row>
@@ -12757,7 +12762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -13192,7 +13197,11 @@
           <t>Lines to build together (in order) — empty until each has its rationale file</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>history 1Q23-2Q26 plugged from 02_panel_quarterly.csv (reported); forecast cost lines and below-the-line plugged from 40_line_build base (DEC-0022); blue = plug, black = formula</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
@@ -13569,12 +13578,97 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="Q12" s="31" t="n"/>
-      <c r="R12" s="31" t="n"/>
-      <c r="S12" s="31" t="n"/>
-      <c r="T12" s="31" t="n"/>
-      <c r="U12" s="31" t="n"/>
-      <c r="V12" s="31" t="n"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>A: reported. E: = GBV x take rate (DEC-0018), so revenue is an output of lines 1-2</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>1818</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>2484</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>3397</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>2218</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <v>2142</v>
+      </c>
+      <c r="H12" s="31" t="n">
+        <v>2748</v>
+      </c>
+      <c r="I12" s="31" t="n">
+        <v>3732</v>
+      </c>
+      <c r="J12" s="31" t="n">
+        <v>2480</v>
+      </c>
+      <c r="K12" s="31" t="n">
+        <v>2272</v>
+      </c>
+      <c r="L12" s="31" t="n">
+        <v>3096</v>
+      </c>
+      <c r="M12" s="31" t="n">
+        <v>4095</v>
+      </c>
+      <c r="N12" s="31" t="n">
+        <v>2778</v>
+      </c>
+      <c r="O12" s="31" t="n">
+        <v>2678</v>
+      </c>
+      <c r="P12" s="31" t="n">
+        <v>3608</v>
+      </c>
+      <c r="Q12" s="32">
+        <f>Q8*1000*Q14</f>
+        <v/>
+      </c>
+      <c r="R12" s="32">
+        <f>R8*1000*R14</f>
+        <v/>
+      </c>
+      <c r="S12" s="32">
+        <f>S8*1000*S14</f>
+        <v/>
+      </c>
+      <c r="T12" s="32">
+        <f>T8*1000*T14</f>
+        <v/>
+      </c>
+      <c r="U12" s="32">
+        <f>U8*1000*U14</f>
+        <v/>
+      </c>
+      <c r="V12" s="32">
+        <f>V8*1000*V14</f>
+        <v/>
+      </c>
+      <c r="X12" s="32">
+        <f>SUM(C12:F12)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="32">
+        <f>SUM(G12:J12)</f>
+        <v/>
+      </c>
+      <c r="Z12" s="32">
+        <f>SUM(K12:N12)</f>
+        <v/>
+      </c>
+      <c r="AA12" s="32">
+        <f>SUM(O12:R12)</f>
+        <v/>
+      </c>
+      <c r="AB12" s="32">
+        <f>SUM(S12:V12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -13582,12 +13676,86 @@
           <t xml:space="preserve">    y/y</t>
         </is>
       </c>
-      <c r="Q13" s="31" t="n"/>
-      <c r="R13" s="31" t="n"/>
-      <c r="S13" s="31" t="n"/>
-      <c r="T13" s="31" t="n"/>
-      <c r="U13" s="31" t="n"/>
-      <c r="V13" s="31" t="n"/>
+      <c r="G13" s="33">
+        <f>G12/C12-1</f>
+        <v/>
+      </c>
+      <c r="H13" s="33">
+        <f>H12/D12-1</f>
+        <v/>
+      </c>
+      <c r="I13" s="33">
+        <f>I12/E12-1</f>
+        <v/>
+      </c>
+      <c r="J13" s="33">
+        <f>J12/F12-1</f>
+        <v/>
+      </c>
+      <c r="K13" s="33">
+        <f>K12/G12-1</f>
+        <v/>
+      </c>
+      <c r="L13" s="33">
+        <f>L12/H12-1</f>
+        <v/>
+      </c>
+      <c r="M13" s="33">
+        <f>M12/I12-1</f>
+        <v/>
+      </c>
+      <c r="N13" s="33">
+        <f>N12/J12-1</f>
+        <v/>
+      </c>
+      <c r="O13" s="33">
+        <f>O12/K12-1</f>
+        <v/>
+      </c>
+      <c r="P13" s="33">
+        <f>P12/L12-1</f>
+        <v/>
+      </c>
+      <c r="Q13" s="33">
+        <f>Q12/M12-1</f>
+        <v/>
+      </c>
+      <c r="R13" s="33">
+        <f>R12/N12-1</f>
+        <v/>
+      </c>
+      <c r="S13" s="33">
+        <f>S12/O12-1</f>
+        <v/>
+      </c>
+      <c r="T13" s="33">
+        <f>T12/P12-1</f>
+        <v/>
+      </c>
+      <c r="U13" s="33">
+        <f>U12/Q12-1</f>
+        <v/>
+      </c>
+      <c r="V13" s="33">
+        <f>V12/R12-1</f>
+        <v/>
+      </c>
+      <c r="Y13" s="33">
+        <f>Y12/X12-1</f>
+        <v/>
+      </c>
+      <c r="Z13" s="33">
+        <f>Z12/Y12-1</f>
+        <v/>
+      </c>
+      <c r="AA13" s="33">
+        <f>AA12/Z12-1</f>
+        <v/>
+      </c>
+      <c r="AB13" s="33">
+        <f>AB12/AA12-1</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -13595,12 +13763,105 @@
           <t xml:space="preserve">    Take rate (revenue / GBV)</t>
         </is>
       </c>
-      <c r="Q14" s="31" t="n"/>
-      <c r="R14" s="31" t="n"/>
-      <c r="S14" s="31" t="n"/>
-      <c r="T14" s="31" t="n"/>
-      <c r="U14" s="31" t="n"/>
-      <c r="V14" s="31" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>A: = revenue / GBV. E: 3Q26-4Q26 Street-implied; 1Q27+ seasonal naive tau[q-4], no drift</t>
+        </is>
+      </c>
+      <c r="C14" s="34">
+        <f>C12/(C8*1000)</f>
+        <v/>
+      </c>
+      <c r="D14" s="34">
+        <f>D12/(D8*1000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="34">
+        <f>E12/(E8*1000)</f>
+        <v/>
+      </c>
+      <c r="F14" s="34">
+        <f>F12/(F8*1000)</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>G12/(G8*1000)</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>H12/(H8*1000)</f>
+        <v/>
+      </c>
+      <c r="I14" s="34">
+        <f>I12/(I8*1000)</f>
+        <v/>
+      </c>
+      <c r="J14" s="34">
+        <f>J12/(J8*1000)</f>
+        <v/>
+      </c>
+      <c r="K14" s="34">
+        <f>K12/(K8*1000)</f>
+        <v/>
+      </c>
+      <c r="L14" s="34">
+        <f>L12/(L8*1000)</f>
+        <v/>
+      </c>
+      <c r="M14" s="34">
+        <f>M12/(M8*1000)</f>
+        <v/>
+      </c>
+      <c r="N14" s="34">
+        <f>N12/(N8*1000)</f>
+        <v/>
+      </c>
+      <c r="O14" s="34">
+        <f>O12/(O8*1000)</f>
+        <v/>
+      </c>
+      <c r="P14" s="34">
+        <f>P12/(P8*1000)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="35" t="n">
+        <v>0.1798321124223617</v>
+      </c>
+      <c r="R14" s="35" t="n">
+        <v>0.137720607259622</v>
+      </c>
+      <c r="S14" s="35" t="n">
+        <v>0.09171</v>
+      </c>
+      <c r="T14" s="35" t="n">
+        <v>0.13265</v>
+      </c>
+      <c r="U14" s="35" t="n">
+        <v>0.1798321124223617</v>
+      </c>
+      <c r="V14" s="35" t="n">
+        <v>0.137720607259622</v>
+      </c>
+      <c r="X14" s="34">
+        <f>X12/(SUM(C8:F8)*1000)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="34">
+        <f>Y12/(SUM(G8:J8)*1000)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="34">
+        <f>Z12/(SUM(K8:N8)*1000)</f>
+        <v/>
+      </c>
+      <c r="AA14" s="34">
+        <f>AA12/(SUM(O8:R8)*1000)</f>
+        <v/>
+      </c>
+      <c r="AB14" s="34">
+        <f>AB12/(SUM(S8:V8)*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -13608,12 +13869,91 @@
           <t xml:space="preserve">    Cost of revenue (cash)</t>
         </is>
       </c>
-      <c r="Q16" s="31" t="n"/>
-      <c r="R16" s="31" t="n"/>
-      <c r="S16" s="31" t="n"/>
-      <c r="T16" s="31" t="n"/>
-      <c r="U16" s="31" t="n"/>
-      <c r="V16" s="31" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>cash = GAAP less SBC. A: 02_panel_quarterly. E: 40_line_build base, carried in dollars (DEC-0022)</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>428</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>432</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>459</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>384</v>
+      </c>
+      <c r="G16" s="31" t="n">
+        <v>480</v>
+      </c>
+      <c r="H16" s="31" t="n">
+        <v>506</v>
+      </c>
+      <c r="I16" s="31" t="n">
+        <v>465</v>
+      </c>
+      <c r="J16" s="31" t="n">
+        <v>427</v>
+      </c>
+      <c r="K16" s="31" t="n">
+        <v>506</v>
+      </c>
+      <c r="L16" s="31" t="n">
+        <v>544</v>
+      </c>
+      <c r="M16" s="31" t="n">
+        <v>549</v>
+      </c>
+      <c r="N16" s="31" t="n">
+        <v>487</v>
+      </c>
+      <c r="O16" s="31" t="n">
+        <v>581</v>
+      </c>
+      <c r="P16" s="31" t="n">
+        <v>633</v>
+      </c>
+      <c r="Q16" s="31" t="n">
+        <v>640.7841188023608</v>
+      </c>
+      <c r="R16" s="31" t="n">
+        <v>578.0394574666427</v>
+      </c>
+      <c r="S16" s="31" t="n">
+        <v>706.0035882028698</v>
+      </c>
+      <c r="T16" s="31" t="n">
+        <v>727.2995429788907</v>
+      </c>
+      <c r="U16" s="31" t="n">
+        <v>699.4536785339944</v>
+      </c>
+      <c r="V16" s="31" t="n">
+        <v>626.8522820155006</v>
+      </c>
+      <c r="X16" s="32">
+        <f>SUM(C16:F16)</f>
+        <v/>
+      </c>
+      <c r="Y16" s="32">
+        <f>SUM(G16:J16)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="32">
+        <f>SUM(K16:N16)</f>
+        <v/>
+      </c>
+      <c r="AA16" s="32">
+        <f>SUM(O16:R16)</f>
+        <v/>
+      </c>
+      <c r="AB16" s="32">
+        <f>SUM(S16:V16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -13621,12 +13961,86 @@
           <t xml:space="preserve">    Operations &amp; support (cash)</t>
         </is>
       </c>
-      <c r="Q17" s="31" t="n"/>
-      <c r="R17" s="31" t="n"/>
-      <c r="S17" s="31" t="n"/>
-      <c r="T17" s="31" t="n"/>
-      <c r="U17" s="31" t="n"/>
-      <c r="V17" s="31" t="n"/>
+      <c r="C17" s="31" t="n">
+        <v>267</v>
+      </c>
+      <c r="D17" s="31" t="n">
+        <v>298</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <v>299</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>254</v>
+      </c>
+      <c r="G17" s="31" t="n">
+        <v>266</v>
+      </c>
+      <c r="H17" s="31" t="n">
+        <v>314</v>
+      </c>
+      <c r="I17" s="31" t="n">
+        <v>347</v>
+      </c>
+      <c r="J17" s="31" t="n">
+        <v>265</v>
+      </c>
+      <c r="K17" s="31" t="n">
+        <v>282</v>
+      </c>
+      <c r="L17" s="31" t="n">
+        <v>309</v>
+      </c>
+      <c r="M17" s="31" t="n">
+        <v>343</v>
+      </c>
+      <c r="N17" s="31" t="n">
+        <v>303</v>
+      </c>
+      <c r="O17" s="31" t="n">
+        <v>301</v>
+      </c>
+      <c r="P17" s="31" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q17" s="31" t="n">
+        <v>361.4430867108318</v>
+      </c>
+      <c r="R17" s="31" t="n">
+        <v>318.2870944871431</v>
+      </c>
+      <c r="S17" s="31" t="n">
+        <v>319.0860911068342</v>
+      </c>
+      <c r="T17" s="31" t="n">
+        <v>340.9682435981541</v>
+      </c>
+      <c r="U17" s="31" t="n">
+        <v>381.7590955367162</v>
+      </c>
+      <c r="V17" s="31" t="n">
+        <v>336.0624813662569</v>
+      </c>
+      <c r="X17" s="32">
+        <f>SUM(C17:F17)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="32">
+        <f>SUM(G17:J17)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="32">
+        <f>SUM(K17:N17)</f>
+        <v/>
+      </c>
+      <c r="AA17" s="32">
+        <f>SUM(O17:R17)</f>
+        <v/>
+      </c>
+      <c r="AB17" s="32">
+        <f>SUM(S17:V17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -13634,12 +14048,86 @@
           <t xml:space="preserve">    Product development (cash)</t>
         </is>
       </c>
-      <c r="Q18" s="31" t="n"/>
-      <c r="R18" s="31" t="n"/>
-      <c r="S18" s="31" t="n"/>
-      <c r="T18" s="31" t="n"/>
-      <c r="U18" s="31" t="n"/>
-      <c r="V18" s="31" t="n"/>
+      <c r="C18" s="31" t="n">
+        <v>271</v>
+      </c>
+      <c r="D18" s="31" t="n">
+        <v>260</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <v>244</v>
+      </c>
+      <c r="F18" s="31" t="n">
+        <v>253</v>
+      </c>
+      <c r="G18" s="31" t="n">
+        <v>290</v>
+      </c>
+      <c r="H18" s="31" t="n">
+        <v>280</v>
+      </c>
+      <c r="I18" s="31" t="n">
+        <v>294</v>
+      </c>
+      <c r="J18" s="31" t="n">
+        <v>306</v>
+      </c>
+      <c r="K18" s="31" t="n">
+        <v>338</v>
+      </c>
+      <c r="L18" s="31" t="n">
+        <v>331</v>
+      </c>
+      <c r="M18" s="31" t="n">
+        <v>333</v>
+      </c>
+      <c r="N18" s="31" t="n">
+        <v>335</v>
+      </c>
+      <c r="O18" s="31" t="n">
+        <v>375</v>
+      </c>
+      <c r="P18" s="31" t="n">
+        <v>374</v>
+      </c>
+      <c r="Q18" s="31" t="n">
+        <v>359.0948816686723</v>
+      </c>
+      <c r="R18" s="31" t="n">
+        <v>369.0251183313277</v>
+      </c>
+      <c r="S18" s="31" t="n">
+        <v>414.1237900800001</v>
+      </c>
+      <c r="T18" s="31" t="n">
+        <v>400.79641536</v>
+      </c>
+      <c r="U18" s="31" t="n">
+        <v>399.65871264</v>
+      </c>
+      <c r="V18" s="31" t="n">
+        <v>410.71068192</v>
+      </c>
+      <c r="X18" s="32">
+        <f>SUM(C18:F18)</f>
+        <v/>
+      </c>
+      <c r="Y18" s="32">
+        <f>SUM(G18:J18)</f>
+        <v/>
+      </c>
+      <c r="Z18" s="32">
+        <f>SUM(K18:N18)</f>
+        <v/>
+      </c>
+      <c r="AA18" s="32">
+        <f>SUM(O18:R18)</f>
+        <v/>
+      </c>
+      <c r="AB18" s="32">
+        <f>SUM(S18:V18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -13647,12 +14135,86 @@
           <t xml:space="preserve">    Sales &amp; marketing (cash)</t>
         </is>
       </c>
-      <c r="Q19" s="31" t="n"/>
-      <c r="R19" s="31" t="n"/>
-      <c r="S19" s="31" t="n"/>
-      <c r="T19" s="31" t="n"/>
-      <c r="U19" s="31" t="n"/>
-      <c r="V19" s="31" t="n"/>
+      <c r="C19" s="31" t="n">
+        <v>422</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>450</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>370</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>391</v>
+      </c>
+      <c r="G19" s="31" t="n">
+        <v>479</v>
+      </c>
+      <c r="H19" s="31" t="n">
+        <v>527</v>
+      </c>
+      <c r="I19" s="31" t="n">
+        <v>471</v>
+      </c>
+      <c r="J19" s="31" t="n">
+        <v>501</v>
+      </c>
+      <c r="K19" s="31" t="n">
+        <v>519</v>
+      </c>
+      <c r="L19" s="31" t="n">
+        <v>639</v>
+      </c>
+      <c r="M19" s="31" t="n">
+        <v>585</v>
+      </c>
+      <c r="N19" s="31" t="n">
+        <v>633</v>
+      </c>
+      <c r="O19" s="31" t="n">
+        <v>696</v>
+      </c>
+      <c r="P19" s="31" t="n">
+        <v>808</v>
+      </c>
+      <c r="Q19" s="31" t="n">
+        <v>778.3158128157291</v>
+      </c>
+      <c r="R19" s="31" t="n">
+        <v>758.1075295918367</v>
+      </c>
+      <c r="S19" s="31" t="n">
+        <v>829.2717874113573</v>
+      </c>
+      <c r="T19" s="31" t="n">
+        <v>935.1362709106796</v>
+      </c>
+      <c r="U19" s="31" t="n">
+        <v>819.9308035731818</v>
+      </c>
+      <c r="V19" s="31" t="n">
+        <v>875.2847818734812</v>
+      </c>
+      <c r="X19" s="32">
+        <f>SUM(C19:F19)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="32">
+        <f>SUM(G19:J19)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="32">
+        <f>SUM(K19:N19)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="32">
+        <f>SUM(O19:R19)</f>
+        <v/>
+      </c>
+      <c r="AB19" s="32">
+        <f>SUM(S19:V19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -13660,12 +14222,91 @@
           <t xml:space="preserve">    General &amp; administrative (cash, ex lodging-tax reserves)</t>
         </is>
       </c>
-      <c r="Q20" s="31" t="n"/>
-      <c r="R20" s="31" t="n"/>
-      <c r="S20" s="31" t="n"/>
-      <c r="T20" s="31" t="n"/>
-      <c r="U20" s="31" t="n"/>
-      <c r="V20" s="31" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>ex lodging/withholding-tax reserves (4Q23 carried $931m); reserves sit in the add-back row</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n">
+        <v>191</v>
+      </c>
+      <c r="D20" s="31" t="n">
+        <v>219</v>
+      </c>
+      <c r="E20" s="31" t="n">
+        <v>202</v>
+      </c>
+      <c r="F20" s="31" t="n">
+        <v>211</v>
+      </c>
+      <c r="G20" s="31" t="n">
+        <v>223</v>
+      </c>
+      <c r="H20" s="31" t="n">
+        <v>242</v>
+      </c>
+      <c r="I20" s="31" t="n">
+        <v>210</v>
+      </c>
+      <c r="J20" s="31" t="n">
+        <v>226</v>
+      </c>
+      <c r="K20" s="31" t="n">
+        <v>235</v>
+      </c>
+      <c r="L20" s="31" t="n">
+        <v>244</v>
+      </c>
+      <c r="M20" s="31" t="n">
+        <v>257</v>
+      </c>
+      <c r="N20" s="31" t="n">
+        <v>259</v>
+      </c>
+      <c r="O20" s="31" t="n">
+        <v>226</v>
+      </c>
+      <c r="P20" s="31" t="n">
+        <v>227</v>
+      </c>
+      <c r="Q20" s="31" t="n">
+        <v>265.3890706023136</v>
+      </c>
+      <c r="R20" s="31" t="n">
+        <v>276.4109293976865</v>
+      </c>
+      <c r="S20" s="31" t="n">
+        <v>249.227244</v>
+      </c>
+      <c r="T20" s="31" t="n">
+        <v>271.5804000000001</v>
+      </c>
+      <c r="U20" s="31" t="n">
+        <v>256.539024</v>
+      </c>
+      <c r="V20" s="31" t="n">
+        <v>267.1933320000001</v>
+      </c>
+      <c r="X20" s="32">
+        <f>SUM(C20:F20)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="32">
+        <f>SUM(G20:J20)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="32">
+        <f>SUM(K20:N20)</f>
+        <v/>
+      </c>
+      <c r="AA20" s="32">
+        <f>SUM(O20:R20)</f>
+        <v/>
+      </c>
+      <c r="AB20" s="32">
+        <f>SUM(S20:V20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -13673,12 +14314,106 @@
           <t>Total cash costs</t>
         </is>
       </c>
-      <c r="Q21" s="31" t="n"/>
-      <c r="R21" s="31" t="n"/>
-      <c r="S21" s="31" t="n"/>
-      <c r="T21" s="31" t="n"/>
-      <c r="U21" s="31" t="n"/>
-      <c r="V21" s="31" t="n"/>
+      <c r="C21" s="32">
+        <f>SUM(C16:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="32">
+        <f>SUM(D16:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="32">
+        <f>SUM(E16:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="32">
+        <f>SUM(F16:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="32">
+        <f>SUM(G16:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="32">
+        <f>SUM(H16:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="32">
+        <f>SUM(I16:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="32">
+        <f>SUM(J16:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="32">
+        <f>SUM(K16:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="32">
+        <f>SUM(L16:L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="32">
+        <f>SUM(M16:M20)</f>
+        <v/>
+      </c>
+      <c r="N21" s="32">
+        <f>SUM(N16:N20)</f>
+        <v/>
+      </c>
+      <c r="O21" s="32">
+        <f>SUM(O16:O20)</f>
+        <v/>
+      </c>
+      <c r="P21" s="32">
+        <f>SUM(P16:P20)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="32">
+        <f>SUM(Q16:Q20)</f>
+        <v/>
+      </c>
+      <c r="R21" s="32">
+        <f>SUM(R16:R20)</f>
+        <v/>
+      </c>
+      <c r="S21" s="32">
+        <f>SUM(S16:S20)</f>
+        <v/>
+      </c>
+      <c r="T21" s="32">
+        <f>SUM(T16:T20)</f>
+        <v/>
+      </c>
+      <c r="U21" s="32">
+        <f>SUM(U16:U20)</f>
+        <v/>
+      </c>
+      <c r="V21" s="32">
+        <f>SUM(V16:V20)</f>
+        <v/>
+      </c>
+      <c r="X21" s="32">
+        <f>SUM(C21:F21)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="32">
+        <f>SUM(G21:J21)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="32">
+        <f>SUM(K21:N21)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="32">
+        <f>SUM(O21:R21)</f>
+        <v/>
+      </c>
+      <c r="AB21" s="32">
+        <f>SUM(S21:V21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -13686,12 +14421,106 @@
           <t xml:space="preserve">    % of revenue</t>
         </is>
       </c>
-      <c r="Q22" s="31" t="n"/>
-      <c r="R22" s="31" t="n"/>
-      <c r="S22" s="31" t="n"/>
-      <c r="T22" s="31" t="n"/>
-      <c r="U22" s="31" t="n"/>
-      <c r="V22" s="31" t="n"/>
+      <c r="C22" s="10">
+        <f>C21/C12</f>
+        <v/>
+      </c>
+      <c r="D22" s="10">
+        <f>D21/D12</f>
+        <v/>
+      </c>
+      <c r="E22" s="10">
+        <f>E21/E12</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>F21/F12</f>
+        <v/>
+      </c>
+      <c r="G22" s="10">
+        <f>G21/G12</f>
+        <v/>
+      </c>
+      <c r="H22" s="10">
+        <f>H21/H12</f>
+        <v/>
+      </c>
+      <c r="I22" s="10">
+        <f>I21/I12</f>
+        <v/>
+      </c>
+      <c r="J22" s="10">
+        <f>J21/J12</f>
+        <v/>
+      </c>
+      <c r="K22" s="10">
+        <f>K21/K12</f>
+        <v/>
+      </c>
+      <c r="L22" s="10">
+        <f>L21/L12</f>
+        <v/>
+      </c>
+      <c r="M22" s="10">
+        <f>M21/M12</f>
+        <v/>
+      </c>
+      <c r="N22" s="10">
+        <f>N21/N12</f>
+        <v/>
+      </c>
+      <c r="O22" s="10">
+        <f>O21/O12</f>
+        <v/>
+      </c>
+      <c r="P22" s="10">
+        <f>P21/P12</f>
+        <v/>
+      </c>
+      <c r="Q22" s="10">
+        <f>Q21/Q12</f>
+        <v/>
+      </c>
+      <c r="R22" s="10">
+        <f>R21/R12</f>
+        <v/>
+      </c>
+      <c r="S22" s="10">
+        <f>S21/S12</f>
+        <v/>
+      </c>
+      <c r="T22" s="10">
+        <f>T21/T12</f>
+        <v/>
+      </c>
+      <c r="U22" s="10">
+        <f>U21/U12</f>
+        <v/>
+      </c>
+      <c r="V22" s="10">
+        <f>V21/V12</f>
+        <v/>
+      </c>
+      <c r="X22" s="10">
+        <f>X21/X12</f>
+        <v/>
+      </c>
+      <c r="Y22" s="10">
+        <f>Y21/Y12</f>
+        <v/>
+      </c>
+      <c r="Z22" s="10">
+        <f>Z21/Z12</f>
+        <v/>
+      </c>
+      <c r="AA22" s="10">
+        <f>AA21/AA12</f>
+        <v/>
+      </c>
+      <c r="AB22" s="10">
+        <f>AB21/AB12</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -13699,12 +14528,86 @@
           <t xml:space="preserve">    Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="Q23" s="31" t="n"/>
-      <c r="R23" s="31" t="n"/>
-      <c r="S23" s="31" t="n"/>
-      <c r="T23" s="31" t="n"/>
-      <c r="U23" s="31" t="n"/>
-      <c r="V23" s="31" t="n"/>
+      <c r="C23" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="D23" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="G23" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="H23" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="I23" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="J23" s="31" t="n">
+        <v>22</v>
+      </c>
+      <c r="K23" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="L23" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="M23" s="31" t="n">
+        <v>22</v>
+      </c>
+      <c r="N23" s="31" t="n">
+        <v>23</v>
+      </c>
+      <c r="O23" s="31" t="n">
+        <v>22</v>
+      </c>
+      <c r="P23" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q23" s="31" t="n">
+        <v>20.63397059990752</v>
+      </c>
+      <c r="R23" s="31" t="n">
+        <v>20.63397059990752</v>
+      </c>
+      <c r="S23" s="31" t="n">
+        <v>20.63397059990752</v>
+      </c>
+      <c r="T23" s="31" t="n">
+        <v>20.63397059990752</v>
+      </c>
+      <c r="U23" s="31" t="n">
+        <v>20.63397059990752</v>
+      </c>
+      <c r="V23" s="31" t="n">
+        <v>20.63397059990752</v>
+      </c>
+      <c r="X23" s="32">
+        <f>SUM(C23:F23)</f>
+        <v/>
+      </c>
+      <c r="Y23" s="32">
+        <f>SUM(G23:J23)</f>
+        <v/>
+      </c>
+      <c r="Z23" s="32">
+        <f>SUM(K23:N23)</f>
+        <v/>
+      </c>
+      <c r="AA23" s="32">
+        <f>SUM(O23:R23)</f>
+        <v/>
+      </c>
+      <c r="AB23" s="32">
+        <f>SUM(S23:V23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -13712,12 +14615,97 @@
           <t>Adjusted EBITDA</t>
         </is>
       </c>
-      <c r="Q24" s="31" t="n"/>
-      <c r="R24" s="31" t="n"/>
-      <c r="S24" s="31" t="n"/>
-      <c r="T24" s="31" t="n"/>
-      <c r="U24" s="31" t="n"/>
-      <c r="V24" s="31" t="n"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>A: as reported. E: = revenue - cash costs + D&amp;A + add-backs; margin is therefore an OUTPUT</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n">
+        <v>262</v>
+      </c>
+      <c r="D24" s="31" t="n">
+        <v>819</v>
+      </c>
+      <c r="E24" s="31" t="n">
+        <v>1834</v>
+      </c>
+      <c r="F24" s="31" t="n">
+        <v>738</v>
+      </c>
+      <c r="G24" s="31" t="n">
+        <v>424</v>
+      </c>
+      <c r="H24" s="31" t="n">
+        <v>894</v>
+      </c>
+      <c r="I24" s="31" t="n">
+        <v>1958</v>
+      </c>
+      <c r="J24" s="31" t="n">
+        <v>765</v>
+      </c>
+      <c r="K24" s="31" t="n">
+        <v>417</v>
+      </c>
+      <c r="L24" s="31" t="n">
+        <v>1043</v>
+      </c>
+      <c r="M24" s="31" t="n">
+        <v>2051</v>
+      </c>
+      <c r="N24" s="31" t="n">
+        <v>786</v>
+      </c>
+      <c r="O24" s="31" t="n">
+        <v>519</v>
+      </c>
+      <c r="P24" s="31" t="n">
+        <v>1261</v>
+      </c>
+      <c r="Q24" s="32">
+        <f>Q12-Q21+Q23+Q26</f>
+        <v/>
+      </c>
+      <c r="R24" s="32">
+        <f>R12-R21+R23+R26</f>
+        <v/>
+      </c>
+      <c r="S24" s="32">
+        <f>S12-S21+S23+S26</f>
+        <v/>
+      </c>
+      <c r="T24" s="32">
+        <f>T12-T21+T23+T26</f>
+        <v/>
+      </c>
+      <c r="U24" s="32">
+        <f>U12-U21+U23+U26</f>
+        <v/>
+      </c>
+      <c r="V24" s="32">
+        <f>V12-V21+V23+V26</f>
+        <v/>
+      </c>
+      <c r="X24" s="32">
+        <f>SUM(C24:F24)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="32">
+        <f>SUM(G24:J24)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="32">
+        <f>SUM(K24:N24)</f>
+        <v/>
+      </c>
+      <c r="AA24" s="32">
+        <f>SUM(O24:R24)</f>
+        <v/>
+      </c>
+      <c r="AB24" s="32">
+        <f>SUM(S24:V24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -13725,12 +14713,193 @@
           <t xml:space="preserve">    Adjusted EBITDA margin</t>
         </is>
       </c>
-      <c r="Q25" s="31" t="n"/>
-      <c r="R25" s="31" t="n"/>
-      <c r="S25" s="31" t="n"/>
-      <c r="T25" s="31" t="n"/>
-      <c r="U25" s="31" t="n"/>
-      <c r="V25" s="31" t="n"/>
+      <c r="C25" s="10">
+        <f>C24/C12</f>
+        <v/>
+      </c>
+      <c r="D25" s="10">
+        <f>D24/D12</f>
+        <v/>
+      </c>
+      <c r="E25" s="10">
+        <f>E24/E12</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>F24/F12</f>
+        <v/>
+      </c>
+      <c r="G25" s="10">
+        <f>G24/G12</f>
+        <v/>
+      </c>
+      <c r="H25" s="10">
+        <f>H24/H12</f>
+        <v/>
+      </c>
+      <c r="I25" s="10">
+        <f>I24/I12</f>
+        <v/>
+      </c>
+      <c r="J25" s="10">
+        <f>J24/J12</f>
+        <v/>
+      </c>
+      <c r="K25" s="10">
+        <f>K24/K12</f>
+        <v/>
+      </c>
+      <c r="L25" s="10">
+        <f>L24/L12</f>
+        <v/>
+      </c>
+      <c r="M25" s="10">
+        <f>M24/M12</f>
+        <v/>
+      </c>
+      <c r="N25" s="10">
+        <f>N24/N12</f>
+        <v/>
+      </c>
+      <c r="O25" s="10">
+        <f>O24/O12</f>
+        <v/>
+      </c>
+      <c r="P25" s="10">
+        <f>P24/P12</f>
+        <v/>
+      </c>
+      <c r="Q25" s="10">
+        <f>Q24/Q12</f>
+        <v/>
+      </c>
+      <c r="R25" s="10">
+        <f>R24/R12</f>
+        <v/>
+      </c>
+      <c r="S25" s="10">
+        <f>S24/S12</f>
+        <v/>
+      </c>
+      <c r="T25" s="10">
+        <f>T24/T12</f>
+        <v/>
+      </c>
+      <c r="U25" s="10">
+        <f>U24/U12</f>
+        <v/>
+      </c>
+      <c r="V25" s="10">
+        <f>V24/V12</f>
+        <v/>
+      </c>
+      <c r="X25" s="10">
+        <f>X24/X12</f>
+        <v/>
+      </c>
+      <c r="Y25" s="10">
+        <f>Y24/Y12</f>
+        <v/>
+      </c>
+      <c r="Z25" s="10">
+        <f>Z24/Z12</f>
+        <v/>
+      </c>
+      <c r="AA25" s="10">
+        <f>AA24/AA12</f>
+        <v/>
+      </c>
+      <c r="AB25" s="10">
+        <f>AB24/AB12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>memo, feeds Adj. EBITDA: lodging-tax reserves and other add-backs (acquisition, IPO, restructuring)</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" s="31" t="n">
+        <v>-15</v>
+      </c>
+      <c r="E26" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="31" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G26" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J26" s="31" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K26" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="31" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M26" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" s="31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P26" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="32">
+        <f>SUM(C26:F26)</f>
+        <v/>
+      </c>
+      <c r="Y26" s="32">
+        <f>SUM(G26:J26)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="32">
+        <f>SUM(K26:N26)</f>
+        <v/>
+      </c>
+      <c r="AA26" s="32">
+        <f>SUM(O26:R26)</f>
+        <v/>
+      </c>
+      <c r="AB26" s="32">
+        <f>SUM(S26:V26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -13738,12 +14907,91 @@
           <t xml:space="preserve">    Stock-based compensation</t>
         </is>
       </c>
-      <c r="Q27" s="31" t="n"/>
-      <c r="R27" s="31" t="n"/>
-      <c r="S27" s="31" t="n"/>
-      <c r="T27" s="31" t="n"/>
-      <c r="U27" s="31" t="n"/>
-      <c r="V27" s="31" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>A: income-statement footnote total. E: 40_line_build (SBC[q-4] x 1.1318, M7 parameter sheet)</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n">
+        <v>240</v>
+      </c>
+      <c r="D27" s="31" t="n">
+        <v>304</v>
+      </c>
+      <c r="E27" s="31" t="n">
+        <v>286</v>
+      </c>
+      <c r="F27" s="31" t="n">
+        <v>290</v>
+      </c>
+      <c r="G27" s="31" t="n">
+        <v>295</v>
+      </c>
+      <c r="H27" s="31" t="n">
+        <v>382</v>
+      </c>
+      <c r="I27" s="31" t="n">
+        <v>362</v>
+      </c>
+      <c r="J27" s="31" t="n">
+        <v>368</v>
+      </c>
+      <c r="K27" s="31" t="n">
+        <v>358</v>
+      </c>
+      <c r="L27" s="31" t="n">
+        <v>424</v>
+      </c>
+      <c r="M27" s="31" t="n">
+        <v>399</v>
+      </c>
+      <c r="N27" s="31" t="n">
+        <v>411</v>
+      </c>
+      <c r="O27" s="31" t="n">
+        <v>410</v>
+      </c>
+      <c r="P27" s="31" t="n">
+        <v>487</v>
+      </c>
+      <c r="Q27" s="31" t="n">
+        <v>451.5791856610708</v>
+      </c>
+      <c r="R27" s="31" t="n">
+        <v>465.1605145531331</v>
+      </c>
+      <c r="S27" s="31" t="n">
+        <v>464.0287371454613</v>
+      </c>
+      <c r="T27" s="31" t="n">
+        <v>551.1755975361942</v>
+      </c>
+      <c r="U27" s="31" t="n">
+        <v>511.0871201060549</v>
+      </c>
+      <c r="V27" s="31" t="n">
+        <v>526.4581613122519</v>
+      </c>
+      <c r="X27" s="32">
+        <f>SUM(C27:F27)</f>
+        <v/>
+      </c>
+      <c r="Y27" s="32">
+        <f>SUM(G27:J27)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="32">
+        <f>SUM(K27:N27)</f>
+        <v/>
+      </c>
+      <c r="AA27" s="32">
+        <f>SUM(O27:R27)</f>
+        <v/>
+      </c>
+      <c r="AB27" s="32">
+        <f>SUM(S27:V27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -13751,12 +14999,97 @@
           <t>Operating income (GAAP)</t>
         </is>
       </c>
-      <c r="Q28" s="31" t="n"/>
-      <c r="R28" s="31" t="n"/>
-      <c r="S28" s="31" t="n"/>
-      <c r="T28" s="31" t="n"/>
-      <c r="U28" s="31" t="n"/>
-      <c r="V28" s="31" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>A: reported GAAP. E: = Adj. EBITDA - D&amp;A - SBC (holds exactly in the line build)</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n">
+        <v>-5</v>
+      </c>
+      <c r="D28" s="31" t="n">
+        <v>523</v>
+      </c>
+      <c r="E28" s="31" t="n">
+        <v>1496</v>
+      </c>
+      <c r="F28" s="31" t="n">
+        <v>-496</v>
+      </c>
+      <c r="G28" s="31" t="n">
+        <v>101</v>
+      </c>
+      <c r="H28" s="31" t="n">
+        <v>497</v>
+      </c>
+      <c r="I28" s="31" t="n">
+        <v>1525</v>
+      </c>
+      <c r="J28" s="31" t="n">
+        <v>430</v>
+      </c>
+      <c r="K28" s="31" t="n">
+        <v>38</v>
+      </c>
+      <c r="L28" s="31" t="n">
+        <v>612</v>
+      </c>
+      <c r="M28" s="31" t="n">
+        <v>1625</v>
+      </c>
+      <c r="N28" s="31" t="n">
+        <v>269</v>
+      </c>
+      <c r="O28" s="31" t="n">
+        <v>86</v>
+      </c>
+      <c r="P28" s="31" t="n">
+        <v>758</v>
+      </c>
+      <c r="Q28" s="32">
+        <f>Q24-Q23-Q27</f>
+        <v/>
+      </c>
+      <c r="R28" s="32">
+        <f>R24-R23-R27</f>
+        <v/>
+      </c>
+      <c r="S28" s="32">
+        <f>S24-S23-S27</f>
+        <v/>
+      </c>
+      <c r="T28" s="32">
+        <f>T24-T23-T27</f>
+        <v/>
+      </c>
+      <c r="U28" s="32">
+        <f>U24-U23-U27</f>
+        <v/>
+      </c>
+      <c r="V28" s="32">
+        <f>V24-V23-V27</f>
+        <v/>
+      </c>
+      <c r="X28" s="32">
+        <f>SUM(C28:F28)</f>
+        <v/>
+      </c>
+      <c r="Y28" s="32">
+        <f>SUM(G28:J28)</f>
+        <v/>
+      </c>
+      <c r="Z28" s="32">
+        <f>SUM(K28:N28)</f>
+        <v/>
+      </c>
+      <c r="AA28" s="32">
+        <f>SUM(O28:R28)</f>
+        <v/>
+      </c>
+      <c r="AB28" s="32">
+        <f>SUM(S28:V28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -13764,12 +15097,86 @@
           <t xml:space="preserve">    Interest income</t>
         </is>
       </c>
-      <c r="Q29" s="31" t="n"/>
-      <c r="R29" s="31" t="n"/>
-      <c r="S29" s="31" t="n"/>
-      <c r="T29" s="31" t="n"/>
-      <c r="U29" s="31" t="n"/>
-      <c r="V29" s="31" t="n"/>
+      <c r="C29" s="31" t="n">
+        <v>146</v>
+      </c>
+      <c r="D29" s="31" t="n">
+        <v>191</v>
+      </c>
+      <c r="E29" s="31" t="n">
+        <v>192</v>
+      </c>
+      <c r="F29" s="31" t="n">
+        <v>192</v>
+      </c>
+      <c r="G29" s="31" t="n">
+        <v>202</v>
+      </c>
+      <c r="H29" s="31" t="n">
+        <v>226</v>
+      </c>
+      <c r="I29" s="31" t="n">
+        <v>207</v>
+      </c>
+      <c r="J29" s="31" t="n">
+        <v>183</v>
+      </c>
+      <c r="K29" s="31" t="n">
+        <v>173</v>
+      </c>
+      <c r="L29" s="31" t="n">
+        <v>190</v>
+      </c>
+      <c r="M29" s="31" t="n">
+        <v>180</v>
+      </c>
+      <c r="N29" s="31" t="n">
+        <v>162</v>
+      </c>
+      <c r="O29" s="31" t="n">
+        <v>155</v>
+      </c>
+      <c r="P29" s="31" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q29" s="31" t="n">
+        <v>183.5489337595264</v>
+      </c>
+      <c r="R29" s="31" t="n">
+        <v>165.4954652969192</v>
+      </c>
+      <c r="S29" s="31" t="n">
+        <v>180.2622584477442</v>
+      </c>
+      <c r="T29" s="31" t="n">
+        <v>202.8476930093186</v>
+      </c>
+      <c r="U29" s="31" t="n">
+        <v>191.1450853247752</v>
+      </c>
+      <c r="V29" s="31" t="n">
+        <v>171.1550764191038</v>
+      </c>
+      <c r="X29" s="32">
+        <f>SUM(C29:F29)</f>
+        <v/>
+      </c>
+      <c r="Y29" s="32">
+        <f>SUM(G29:J29)</f>
+        <v/>
+      </c>
+      <c r="Z29" s="32">
+        <f>SUM(K29:N29)</f>
+        <v/>
+      </c>
+      <c r="AA29" s="32">
+        <f>SUM(O29:R29)</f>
+        <v/>
+      </c>
+      <c r="AB29" s="32">
+        <f>SUM(S29:V29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -13777,12 +15184,86 @@
           <t xml:space="preserve">    Interest expense</t>
         </is>
       </c>
-      <c r="Q30" s="31" t="n"/>
-      <c r="R30" s="31" t="n"/>
-      <c r="S30" s="31" t="n"/>
-      <c r="T30" s="31" t="n"/>
-      <c r="U30" s="31" t="n"/>
-      <c r="V30" s="31" t="n"/>
+      <c r="C30" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" s="31" t="n">
+        <v>71</v>
+      </c>
+      <c r="G30" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="I30" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="K30" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="N30" s="31" t="n">
+        <v>26</v>
+      </c>
+      <c r="O30" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="P30" s="31" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q30" s="31" t="n">
+        <v>37</v>
+      </c>
+      <c r="R30" s="31" t="n">
+        <v>37</v>
+      </c>
+      <c r="S30" s="31" t="n">
+        <v>37</v>
+      </c>
+      <c r="T30" s="31" t="n">
+        <v>37</v>
+      </c>
+      <c r="U30" s="31" t="n">
+        <v>37</v>
+      </c>
+      <c r="V30" s="31" t="n">
+        <v>37</v>
+      </c>
+      <c r="X30" s="32">
+        <f>SUM(C30:F30)</f>
+        <v/>
+      </c>
+      <c r="Y30" s="32">
+        <f>SUM(G30:J30)</f>
+        <v/>
+      </c>
+      <c r="Z30" s="32">
+        <f>SUM(K30:N30)</f>
+        <v/>
+      </c>
+      <c r="AA30" s="32">
+        <f>SUM(O30:R30)</f>
+        <v/>
+      </c>
+      <c r="AB30" s="32">
+        <f>SUM(S30:V30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -13790,12 +15271,86 @@
           <t xml:space="preserve">    Other income / (expense), net</t>
         </is>
       </c>
-      <c r="Q31" s="31" t="n"/>
-      <c r="R31" s="31" t="n"/>
-      <c r="S31" s="31" t="n"/>
-      <c r="T31" s="31" t="n"/>
-      <c r="U31" s="31" t="n"/>
-      <c r="V31" s="31" t="n"/>
+      <c r="C31" s="31" t="n">
+        <v>-7</v>
+      </c>
+      <c r="D31" s="31" t="n">
+        <v>-36</v>
+      </c>
+      <c r="E31" s="31" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F31" s="31" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G31" s="31" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H31" s="31" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I31" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="K31" s="31" t="n">
+        <v>-33</v>
+      </c>
+      <c r="L31" s="31" t="n">
+        <v>-17</v>
+      </c>
+      <c r="M31" s="31" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N31" s="31" t="n">
+        <v>-12</v>
+      </c>
+      <c r="O31" s="31" t="n">
+        <v>61</v>
+      </c>
+      <c r="P31" s="31" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Q31" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R31" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S31" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T31" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U31" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V31" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X31" s="32">
+        <f>SUM(C31:F31)</f>
+        <v/>
+      </c>
+      <c r="Y31" s="32">
+        <f>SUM(G31:J31)</f>
+        <v/>
+      </c>
+      <c r="Z31" s="32">
+        <f>SUM(K31:N31)</f>
+        <v/>
+      </c>
+      <c r="AA31" s="32">
+        <f>SUM(O31:R31)</f>
+        <v/>
+      </c>
+      <c r="AB31" s="32">
+        <f>SUM(S31:V31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -13803,12 +15358,92 @@
           <t>Pre-tax income</t>
         </is>
       </c>
-      <c r="Q32" s="31" t="n"/>
-      <c r="R32" s="31" t="n"/>
-      <c r="S32" s="31" t="n"/>
-      <c r="T32" s="31" t="n"/>
-      <c r="U32" s="31" t="n"/>
-      <c r="V32" s="31" t="n"/>
+      <c r="C32" s="31" t="n">
+        <v>130</v>
+      </c>
+      <c r="D32" s="31" t="n">
+        <v>676</v>
+      </c>
+      <c r="E32" s="31" t="n">
+        <v>1679</v>
+      </c>
+      <c r="F32" s="31" t="n">
+        <v>-383</v>
+      </c>
+      <c r="G32" s="31" t="n">
+        <v>293</v>
+      </c>
+      <c r="H32" s="31" t="n">
+        <v>681</v>
+      </c>
+      <c r="I32" s="31" t="n">
+        <v>1735</v>
+      </c>
+      <c r="J32" s="31" t="n">
+        <v>622</v>
+      </c>
+      <c r="K32" s="31" t="n">
+        <v>173</v>
+      </c>
+      <c r="L32" s="31" t="n">
+        <v>779</v>
+      </c>
+      <c r="M32" s="31" t="n">
+        <v>1792</v>
+      </c>
+      <c r="N32" s="31" t="n">
+        <v>393</v>
+      </c>
+      <c r="O32" s="31" t="n">
+        <v>281</v>
+      </c>
+      <c r="P32" s="31" t="n">
+        <v>897</v>
+      </c>
+      <c r="Q32" s="32">
+        <f>Q28+Q29-Q30+Q31</f>
+        <v/>
+      </c>
+      <c r="R32" s="32">
+        <f>R28+R29-R30+R31</f>
+        <v/>
+      </c>
+      <c r="S32" s="32">
+        <f>S28+S29-S30+S31</f>
+        <v/>
+      </c>
+      <c r="T32" s="32">
+        <f>T28+T29-T30+T31</f>
+        <v/>
+      </c>
+      <c r="U32" s="32">
+        <f>U28+U29-U30+U31</f>
+        <v/>
+      </c>
+      <c r="V32" s="32">
+        <f>V28+V29-V30+V31</f>
+        <v/>
+      </c>
+      <c r="X32" s="32">
+        <f>SUM(C32:F32)</f>
+        <v/>
+      </c>
+      <c r="Y32" s="32">
+        <f>SUM(G32:J32)</f>
+        <v/>
+      </c>
+      <c r="Z32" s="32">
+        <f>SUM(K32:N32)</f>
+        <v/>
+      </c>
+      <c r="AA32" s="32">
+        <f>SUM(O32:R32)</f>
+        <v/>
+      </c>
+      <c r="AB32" s="32">
+        <f>SUM(S32:V32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -13816,12 +15451,97 @@
           <t xml:space="preserve">    Income tax</t>
         </is>
       </c>
-      <c r="Q33" s="31" t="n"/>
-      <c r="R33" s="31" t="n"/>
-      <c r="S33" s="31" t="n"/>
-      <c r="T33" s="31" t="n"/>
-      <c r="U33" s="31" t="n"/>
-      <c r="V33" s="31" t="n"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>E: effective rate 18.0% FY26 / 17.5% FY27 (M7 parameter sheet), applied to our own pre-tax</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="D33" s="31" t="n">
+        <v>26</v>
+      </c>
+      <c r="E33" s="31" t="n">
+        <v>-2695</v>
+      </c>
+      <c r="F33" s="31" t="n">
+        <v>-34</v>
+      </c>
+      <c r="G33" s="31" t="n">
+        <v>29</v>
+      </c>
+      <c r="H33" s="31" t="n">
+        <v>126</v>
+      </c>
+      <c r="I33" s="31" t="n">
+        <v>367</v>
+      </c>
+      <c r="J33" s="31" t="n">
+        <v>161</v>
+      </c>
+      <c r="K33" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="L33" s="31" t="n">
+        <v>137</v>
+      </c>
+      <c r="M33" s="31" t="n">
+        <v>418</v>
+      </c>
+      <c r="N33" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="O33" s="31" t="n">
+        <v>121</v>
+      </c>
+      <c r="P33" s="31" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q33" s="32">
+        <f>Q32*0.18</f>
+        <v/>
+      </c>
+      <c r="R33" s="32">
+        <f>R32*0.18</f>
+        <v/>
+      </c>
+      <c r="S33" s="32">
+        <f>S32*0.175</f>
+        <v/>
+      </c>
+      <c r="T33" s="32">
+        <f>T32*0.175</f>
+        <v/>
+      </c>
+      <c r="U33" s="32">
+        <f>U32*0.175</f>
+        <v/>
+      </c>
+      <c r="V33" s="32">
+        <f>V32*0.175</f>
+        <v/>
+      </c>
+      <c r="X33" s="32">
+        <f>SUM(C33:F33)</f>
+        <v/>
+      </c>
+      <c r="Y33" s="32">
+        <f>SUM(G33:J33)</f>
+        <v/>
+      </c>
+      <c r="Z33" s="32">
+        <f>SUM(K33:N33)</f>
+        <v/>
+      </c>
+      <c r="AA33" s="32">
+        <f>SUM(O33:R33)</f>
+        <v/>
+      </c>
+      <c r="AB33" s="32">
+        <f>SUM(S33:V33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -13829,12 +15549,92 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="Q34" s="31" t="n"/>
-      <c r="R34" s="31" t="n"/>
-      <c r="S34" s="31" t="n"/>
-      <c r="T34" s="31" t="n"/>
-      <c r="U34" s="31" t="n"/>
-      <c r="V34" s="31" t="n"/>
+      <c r="C34" s="31" t="n">
+        <v>117</v>
+      </c>
+      <c r="D34" s="31" t="n">
+        <v>650</v>
+      </c>
+      <c r="E34" s="31" t="n">
+        <v>4374</v>
+      </c>
+      <c r="F34" s="31" t="n">
+        <v>-349</v>
+      </c>
+      <c r="G34" s="31" t="n">
+        <v>264</v>
+      </c>
+      <c r="H34" s="31" t="n">
+        <v>555</v>
+      </c>
+      <c r="I34" s="31" t="n">
+        <v>1368</v>
+      </c>
+      <c r="J34" s="31" t="n">
+        <v>461</v>
+      </c>
+      <c r="K34" s="31" t="n">
+        <v>154</v>
+      </c>
+      <c r="L34" s="31" t="n">
+        <v>642</v>
+      </c>
+      <c r="M34" s="31" t="n">
+        <v>1374</v>
+      </c>
+      <c r="N34" s="31" t="n">
+        <v>341</v>
+      </c>
+      <c r="O34" s="31" t="n">
+        <v>160</v>
+      </c>
+      <c r="P34" s="31" t="n">
+        <v>816</v>
+      </c>
+      <c r="Q34" s="32">
+        <f>Q32-Q33</f>
+        <v/>
+      </c>
+      <c r="R34" s="32">
+        <f>R32-R33</f>
+        <v/>
+      </c>
+      <c r="S34" s="32">
+        <f>S32-S33</f>
+        <v/>
+      </c>
+      <c r="T34" s="32">
+        <f>T32-T33</f>
+        <v/>
+      </c>
+      <c r="U34" s="32">
+        <f>U32-U33</f>
+        <v/>
+      </c>
+      <c r="V34" s="32">
+        <f>V32-V33</f>
+        <v/>
+      </c>
+      <c r="X34" s="32">
+        <f>SUM(C34:F34)</f>
+        <v/>
+      </c>
+      <c r="Y34" s="32">
+        <f>SUM(G34:J34)</f>
+        <v/>
+      </c>
+      <c r="Z34" s="32">
+        <f>SUM(K34:N34)</f>
+        <v/>
+      </c>
+      <c r="AA34" s="32">
+        <f>SUM(O34:R34)</f>
+        <v/>
+      </c>
+      <c r="AB34" s="32">
+        <f>SUM(S34:V34)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -13842,12 +15642,86 @@
           <t xml:space="preserve">    Diluted shares (m)</t>
         </is>
       </c>
-      <c r="Q35" s="31" t="n"/>
-      <c r="R35" s="31" t="n"/>
-      <c r="S35" s="31" t="n"/>
-      <c r="T35" s="31" t="n"/>
-      <c r="U35" s="31" t="n"/>
-      <c r="V35" s="31" t="n"/>
+      <c r="C35" s="9" t="n">
+        <v>670</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>665</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>660</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>640</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>654</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>649</v>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>642</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>636</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>632</v>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>626</v>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>621</v>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>614</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>608</v>
+      </c>
+      <c r="P35" s="9" t="n">
+        <v>597</v>
+      </c>
+      <c r="Q35" s="9" t="n">
+        <v>591.6758133819055</v>
+      </c>
+      <c r="R35" s="9" t="n">
+        <v>586.3516267638111</v>
+      </c>
+      <c r="S35" s="9" t="n">
+        <v>581.0274401457166</v>
+      </c>
+      <c r="T35" s="9" t="n">
+        <v>575.7032535276221</v>
+      </c>
+      <c r="U35" s="9" t="n">
+        <v>570.3790669095276</v>
+      </c>
+      <c r="V35" s="9" t="n">
+        <v>565.0548802914332</v>
+      </c>
+      <c r="X35" s="22">
+        <f>AVERAGE(C35:F35)</f>
+        <v/>
+      </c>
+      <c r="Y35" s="22">
+        <f>AVERAGE(G35:J35)</f>
+        <v/>
+      </c>
+      <c r="Z35" s="22">
+        <f>AVERAGE(K35:N35)</f>
+        <v/>
+      </c>
+      <c r="AA35" s="22">
+        <f>AVERAGE(O35:R35)</f>
+        <v/>
+      </c>
+      <c r="AB35" s="22">
+        <f>AVERAGE(S35:V35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -13855,12 +15729,365 @@
           <t>Diluted EPS ($)</t>
         </is>
       </c>
-      <c r="Q36" s="31" t="n"/>
-      <c r="R36" s="31" t="n"/>
-      <c r="S36" s="31" t="n"/>
-      <c r="T36" s="31" t="n"/>
-      <c r="U36" s="31" t="n"/>
-      <c r="V36" s="31" t="n"/>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>E: = net income / diluted shares; shares -5.324m per quarter (M7)</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H36" s="11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K36" s="11" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L36" s="11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M36" s="11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="N36" s="11" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O36" s="11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P36" s="11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q36" s="15">
+        <f>Q34/Q35</f>
+        <v/>
+      </c>
+      <c r="R36" s="15">
+        <f>R34/R35</f>
+        <v/>
+      </c>
+      <c r="S36" s="15">
+        <f>S34/S35</f>
+        <v/>
+      </c>
+      <c r="T36" s="15">
+        <f>T34/T35</f>
+        <v/>
+      </c>
+      <c r="U36" s="15">
+        <f>U34/U35</f>
+        <v/>
+      </c>
+      <c r="V36" s="15">
+        <f>V34/V35</f>
+        <v/>
+      </c>
+      <c r="X36" s="15">
+        <f>X34/X35</f>
+        <v/>
+      </c>
+      <c r="Y36" s="15">
+        <f>Y34/Y35</f>
+        <v/>
+      </c>
+      <c r="Z36" s="15">
+        <f>Z34/Z35</f>
+        <v/>
+      </c>
+      <c r="AA36" s="15">
+        <f>AA34/AA35</f>
+        <v/>
+      </c>
+      <c r="AB36" s="15">
+        <f>AB34/AB35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Cross-checks against the Street, and the open choices this line does not settle (memo rows - none of these feed the statement above)</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
+      <c r="Q38" s="5" t="n"/>
+      <c r="R38" s="5" t="n"/>
+      <c r="S38" s="5" t="n"/>
+      <c r="T38" s="5" t="n"/>
+      <c r="U38" s="5" t="n"/>
+      <c r="V38" s="5" t="n"/>
+      <c r="W38" s="5" t="n"/>
+      <c r="X38" s="5" t="n"/>
+      <c r="Y38" s="5" t="n"/>
+      <c r="Z38" s="5" t="n"/>
+      <c r="AA38" s="5" t="n"/>
+      <c r="AB38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Street revenue ($m)</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>LSEG 06_consensus_quarterly_2027.csv, 13 Sep 2026 pull</t>
+        </is>
+      </c>
+      <c r="Q39" s="31" t="n">
+        <v>4744.32</v>
+      </c>
+      <c r="R39" s="31" t="n">
+        <v>3161.82</v>
+      </c>
+      <c r="S39" s="31" t="n">
+        <v>3010.32</v>
+      </c>
+      <c r="T39" s="31" t="n">
+        <v>4036.94</v>
+      </c>
+      <c r="U39" s="31" t="n">
+        <v>5269.97</v>
+      </c>
+      <c r="V39" s="31" t="n">
+        <v>3528.92</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ours vs Street</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>negative = our nights/ADR lines sit below consensus</t>
+        </is>
+      </c>
+      <c r="Q40" s="33">
+        <f>Q12/Q39-1</f>
+        <v/>
+      </c>
+      <c r="R40" s="33">
+        <f>R12/R39-1</f>
+        <v/>
+      </c>
+      <c r="S40" s="33">
+        <f>S12/S39-1</f>
+        <v/>
+      </c>
+      <c r="T40" s="33">
+        <f>T12/T39-1</f>
+        <v/>
+      </c>
+      <c r="U40" s="33">
+        <f>U12/U39-1</f>
+        <v/>
+      </c>
+      <c r="V40" s="33">
+        <f>V12/V39-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Street adj. EBITDA ($m)</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>LSEG; n 36-37 for 3Q26/4Q26, n 17-19 for 2027</t>
+        </is>
+      </c>
+      <c r="Q41" s="31" t="n">
+        <v>2361.52</v>
+      </c>
+      <c r="R41" s="31" t="n">
+        <v>913.6799999999999</v>
+      </c>
+      <c r="S41" s="31" t="n">
+        <v>610.73</v>
+      </c>
+      <c r="T41" s="31" t="n">
+        <v>1451.71</v>
+      </c>
+      <c r="U41" s="31" t="n">
+        <v>2695.55</v>
+      </c>
+      <c r="V41" s="31" t="n">
+        <v>1068.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ours vs Street</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>wider than the revenue gap because cost dollars are carried flat</t>
+        </is>
+      </c>
+      <c r="Q42" s="33">
+        <f>Q24/Q41-1</f>
+        <v/>
+      </c>
+      <c r="R42" s="33">
+        <f>R24/R41-1</f>
+        <v/>
+      </c>
+      <c r="S42" s="33">
+        <f>S24/S41-1</f>
+        <v/>
+      </c>
+      <c r="T42" s="33">
+        <f>T24/T41-1</f>
+        <v/>
+      </c>
+      <c r="U42" s="33">
+        <f>U24/U41-1</f>
+        <v/>
+      </c>
+      <c r="V42" s="33">
+        <f>V24/V41-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>memo: adj. EBITDA if costs flexed to hold the line build's own margin</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>DEC-0022 carries dollars flat; C4 asks whether management's margin sentence is a budget (costs flex) or a floor</t>
+        </is>
+      </c>
+      <c r="Q43" s="32">
+        <f>Q12*0.5036687385012039</f>
+        <v/>
+      </c>
+      <c r="R43" s="32">
+        <f>R12*0.2828323322844086</f>
+        <v/>
+      </c>
+      <c r="S43" s="32">
+        <f>S12*0.18212486768865177</f>
+        <v/>
+      </c>
+      <c r="T43" s="32">
+        <f>T12*0.34098793219639467</f>
+        <v/>
+      </c>
+      <c r="U43" s="32">
+        <f>U12*0.5196296453789346</f>
+        <v/>
+      </c>
+      <c r="V43" s="32">
+        <f>V12*0.2799655381693949</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    difference vs the statement above</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>the cost of the flat-dollar assumption, in EBITDA $m</t>
+        </is>
+      </c>
+      <c r="Q44" s="32">
+        <f>Q43-Q24</f>
+        <v/>
+      </c>
+      <c r="R44" s="32">
+        <f>R43-R24</f>
+        <v/>
+      </c>
+      <c r="S44" s="32">
+        <f>S43-S24</f>
+        <v/>
+      </c>
+      <c r="T44" s="32">
+        <f>T43-T24</f>
+        <v/>
+      </c>
+      <c r="U44" s="32">
+        <f>U43-U24</f>
+        <v/>
+      </c>
+      <c r="V44" s="32">
+        <f>V43-V24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>memo: DEC-0023 hosting step, B08 alternative ($85.0m/q vs the $100.21m/$111.71m plugged)</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>NOT CHOSEN - both sides on record; positive = EBITDA if the lower B08 hosting number is right</t>
+        </is>
+      </c>
+      <c r="Q45" s="31" t="n">
+        <v>15.20793246038539</v>
+      </c>
+      <c r="R45" s="31" t="n">
+        <v>15.20793246038539</v>
+      </c>
+      <c r="S45" s="31" t="n">
+        <v>26.70793246038539</v>
+      </c>
+      <c r="T45" s="31" t="n">
+        <v>26.70793246038539</v>
+      </c>
+      <c r="U45" s="31" t="n">
+        <v>26.70793246038539</v>
+      </c>
+      <c r="V45" s="31" t="n">
+        <v>26.70793246038539</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/model/ABNB_official_model.xlsx
+++ b/model/ABNB_official_model.xlsx
@@ -15702,17 +15702,14 @@
       <c r="V35" s="9" t="n">
         <v>565.0548802914332</v>
       </c>
-      <c r="X35" s="22">
-        <f>AVERAGE(C35:F35)</f>
-        <v/>
-      </c>
-      <c r="Y35" s="22">
-        <f>AVERAGE(G35:J35)</f>
-        <v/>
-      </c>
-      <c r="Z35" s="22">
-        <f>AVERAGE(K35:N35)</f>
-        <v/>
+      <c r="X35" s="9" t="n">
+        <v>662</v>
+      </c>
+      <c r="Y35" s="9" t="n">
+        <v>645</v>
+      </c>
+      <c r="Z35" s="9" t="n">
+        <v>623</v>
       </c>
       <c r="AA35" s="22">
         <f>AVERAGE(O35:R35)</f>
@@ -15800,17 +15797,14 @@
         <f>V34/V35</f>
         <v/>
       </c>
-      <c r="X36" s="15">
-        <f>X34/X35</f>
-        <v/>
-      </c>
-      <c r="Y36" s="15">
-        <f>Y34/Y35</f>
-        <v/>
-      </c>
-      <c r="Z36" s="15">
-        <f>Z34/Z35</f>
-        <v/>
+      <c r="X36" s="11" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="Y36" s="11" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="Z36" s="11" t="n">
+        <v>4.03</v>
       </c>
       <c r="AA36" s="15">
         <f>AA34/AA35</f>
